--- a/codelists/antipsychotics_raw.xlsx
+++ b/codelists/antipsychotics_raw.xlsx
@@ -410,7 +410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O515"/>
+  <dimension ref="A1:R515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.48" customWidth="1" min="1" max="1"/>
@@ -428,6 +428,9 @@
     <col width="13.8" customWidth="1" min="13" max="13"/>
     <col width="23.92" customWidth="1" min="14" max="14"/>
     <col width="11.04" customWidth="1" min="15" max="15"/>
+    <col width="22.08" customWidth="1" min="16" max="16"/>
+    <col width="22.08" customWidth="1" min="17" max="17"/>
+    <col width="21.16" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,6 +509,21 @@
           <t>lshtm_2796</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>oc_opensafely_1stgenAP</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>oc_opensafely_2ndgenAP</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>oc_opensafely_depotAP</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -569,6 +587,11 @@
       <c r="O2" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -632,6 +655,11 @@
       <c r="O3" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P3" s="1" t="n"/>
+      <c r="Q3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -695,6 +723,11 @@
       <c r="O4" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P4" s="1" t="n"/>
+      <c r="Q4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -758,6 +791,11 @@
       <c r="O5" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P5" s="1" t="n"/>
+      <c r="Q5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -829,6 +867,11 @@
       <c r="O6" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P6" s="1" t="n"/>
+      <c r="Q6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -896,6 +939,11 @@
       <c r="O7" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P7" s="1" t="n"/>
+      <c r="Q7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -963,6 +1011,11 @@
       <c r="O8" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P8" s="1" t="n"/>
+      <c r="Q8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1034,6 +1087,11 @@
       <c r="O9" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P9" s="1" t="n"/>
+      <c r="Q9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1105,6 +1163,11 @@
       <c r="O10" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P10" s="1" t="n"/>
+      <c r="Q10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1172,6 +1235,11 @@
       <c r="O11" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P11" s="1" t="n"/>
+      <c r="Q11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1239,6 +1307,11 @@
       <c r="O12" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P12" s="1" t="n"/>
+      <c r="Q12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1306,6 +1379,11 @@
       <c r="O13" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P13" s="1" t="n"/>
+      <c r="Q13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1369,6 +1447,11 @@
       <c r="O14" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P14" s="1" t="n"/>
+      <c r="Q14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1432,6 +1515,11 @@
       <c r="O15" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P15" s="1" t="n"/>
+      <c r="Q15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1495,6 +1583,11 @@
       <c r="O16" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P16" s="1" t="n"/>
+      <c r="Q16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1558,6 +1651,11 @@
       <c r="O17" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P17" s="1" t="n"/>
+      <c r="Q17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1621,6 +1719,11 @@
       <c r="O18" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P18" s="1" t="n"/>
+      <c r="Q18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="1" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1692,6 +1795,11 @@
       <c r="O19" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P19" s="1" t="n"/>
+      <c r="Q19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="1" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1763,6 +1871,11 @@
       <c r="O20" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P20" s="1" t="n"/>
+      <c r="Q20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="1" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1834,6 +1947,11 @@
       <c r="O21" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P21" s="1" t="n"/>
+      <c r="Q21" s="1" t="n"/>
+      <c r="R21" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1901,6 +2019,11 @@
       <c r="O22" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P22" s="1" t="n"/>
+      <c r="Q22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="1" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1968,6 +2091,11 @@
       <c r="O23" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P23" s="1" t="n"/>
+      <c r="Q23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="1" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2039,6 +2167,11 @@
       <c r="O24" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P24" s="1" t="n"/>
+      <c r="Q24" s="1" t="n"/>
+      <c r="R24" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2106,6 +2239,11 @@
       <c r="O25" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P25" s="1" t="n"/>
+      <c r="Q25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="1" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2177,6 +2315,11 @@
       <c r="O26" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P26" s="1" t="n"/>
+      <c r="Q26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" s="1" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2244,6 +2387,11 @@
       <c r="O27" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P27" s="1" t="n"/>
+      <c r="Q27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2311,6 +2459,11 @@
       <c r="O28" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P28" s="1" t="n"/>
+      <c r="Q28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" s="1" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2378,6 +2531,11 @@
       <c r="O29" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P29" s="1" t="n"/>
+      <c r="Q29" s="1" t="n"/>
+      <c r="R29" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2445,6 +2603,11 @@
       <c r="O30" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P30" s="1" t="n"/>
+      <c r="Q30" s="1" t="n"/>
+      <c r="R30" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2512,6 +2675,11 @@
       <c r="O31" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P31" s="1" t="n"/>
+      <c r="Q31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2579,6 +2747,11 @@
       <c r="O32" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P32" s="1" t="n"/>
+      <c r="Q32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2650,6 +2823,11 @@
       <c r="O33" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P33" s="1" t="n"/>
+      <c r="Q33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" s="1" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2717,6 +2895,11 @@
       <c r="O34" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P34" s="1" t="n"/>
+      <c r="Q34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2784,6 +2967,11 @@
       <c r="O35" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P35" s="1" t="n"/>
+      <c r="Q35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" s="1" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2851,6 +3039,11 @@
       <c r="O36" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P36" s="1" t="n"/>
+      <c r="Q36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2912,6 +3105,11 @@
         </is>
       </c>
       <c r="O37" s="1" t="n"/>
+      <c r="P37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="1" t="n"/>
+      <c r="R37" s="1" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2977,6 +3175,11 @@
         </is>
       </c>
       <c r="O38" s="1" t="n"/>
+      <c r="P38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="1" t="n"/>
+      <c r="R38" s="1" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3046,6 +3249,11 @@
         </is>
       </c>
       <c r="O39" s="1" t="n"/>
+      <c r="P39" s="1" t="n"/>
+      <c r="Q39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" s="1" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3115,6 +3323,11 @@
         </is>
       </c>
       <c r="O40" s="1" t="n"/>
+      <c r="P40" s="1" t="n"/>
+      <c r="Q40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" s="1" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3184,6 +3397,11 @@
         </is>
       </c>
       <c r="O41" s="1" t="n"/>
+      <c r="P41" s="1" t="n"/>
+      <c r="Q41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" s="1" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3253,6 +3471,11 @@
         </is>
       </c>
       <c r="O42" s="1" t="n"/>
+      <c r="P42" s="1" t="n"/>
+      <c r="Q42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" s="1" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3318,6 +3541,11 @@
         </is>
       </c>
       <c r="O43" s="1" t="n"/>
+      <c r="P43" s="1" t="n"/>
+      <c r="Q43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" s="1" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3379,6 +3607,11 @@
         </is>
       </c>
       <c r="O44" s="1" t="n"/>
+      <c r="P44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="1" t="n"/>
+      <c r="R44" s="1" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3440,6 +3673,11 @@
         </is>
       </c>
       <c r="O45" s="1" t="n"/>
+      <c r="P45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="1" t="n"/>
+      <c r="R45" s="1" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3501,6 +3739,11 @@
         </is>
       </c>
       <c r="O46" s="1" t="n"/>
+      <c r="P46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="1" t="n"/>
+      <c r="R46" s="1" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3562,6 +3805,11 @@
         </is>
       </c>
       <c r="O47" s="1" t="n"/>
+      <c r="P47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="1" t="n"/>
+      <c r="R47" s="1" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3631,6 +3879,11 @@
         </is>
       </c>
       <c r="O48" s="1" t="n"/>
+      <c r="P48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="1" t="n"/>
+      <c r="R48" s="1" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3696,6 +3949,11 @@
         </is>
       </c>
       <c r="O49" s="1" t="n"/>
+      <c r="P49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="1" t="n"/>
+      <c r="R49" s="1" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3761,6 +4019,11 @@
         </is>
       </c>
       <c r="O50" s="1" t="n"/>
+      <c r="P50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="1" t="n"/>
+      <c r="R50" s="1" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3826,6 +4089,11 @@
         </is>
       </c>
       <c r="O51" s="1" t="n"/>
+      <c r="P51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="1" t="n"/>
+      <c r="R51" s="1" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3895,6 +4163,11 @@
         </is>
       </c>
       <c r="O52" s="1" t="n"/>
+      <c r="P52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="1" t="n"/>
+      <c r="R52" s="1" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3964,6 +4237,11 @@
         </is>
       </c>
       <c r="O53" s="1" t="n"/>
+      <c r="P53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="1" t="n"/>
+      <c r="R53" s="1" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4029,6 +4307,11 @@
         </is>
       </c>
       <c r="O54" s="1" t="n"/>
+      <c r="P54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="1" t="n"/>
+      <c r="R54" s="1" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4094,6 +4377,11 @@
         </is>
       </c>
       <c r="O55" s="1" t="n"/>
+      <c r="P55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="1" t="n"/>
+      <c r="R55" s="1" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4163,6 +4451,11 @@
         </is>
       </c>
       <c r="O56" s="1" t="n"/>
+      <c r="P56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="1" t="n"/>
+      <c r="R56" s="1" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4228,6 +4521,11 @@
         </is>
       </c>
       <c r="O57" s="1" t="n"/>
+      <c r="P57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="1" t="n"/>
+      <c r="R57" s="1" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4297,6 +4595,11 @@
         </is>
       </c>
       <c r="O58" s="1" t="n"/>
+      <c r="P58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="1" t="n"/>
+      <c r="R58" s="1" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4362,6 +4665,11 @@
         </is>
       </c>
       <c r="O59" s="1" t="n"/>
+      <c r="P59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="1" t="n"/>
+      <c r="R59" s="1" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4395,6 +4703,9 @@
         </is>
       </c>
       <c r="O60" s="1" t="n"/>
+      <c r="P60" s="1" t="n"/>
+      <c r="Q60" s="1" t="n"/>
+      <c r="R60" s="1" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4464,6 +4775,11 @@
         </is>
       </c>
       <c r="O61" s="1" t="n"/>
+      <c r="P61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="1" t="n"/>
+      <c r="R61" s="1" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4497,6 +4813,9 @@
         </is>
       </c>
       <c r="O62" s="1" t="n"/>
+      <c r="P62" s="1" t="n"/>
+      <c r="Q62" s="1" t="n"/>
+      <c r="R62" s="1" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4530,6 +4849,9 @@
         </is>
       </c>
       <c r="O63" s="1" t="n"/>
+      <c r="P63" s="1" t="n"/>
+      <c r="Q63" s="1" t="n"/>
+      <c r="R63" s="1" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4563,6 +4885,9 @@
         </is>
       </c>
       <c r="O64" s="1" t="n"/>
+      <c r="P64" s="1" t="n"/>
+      <c r="Q64" s="1" t="n"/>
+      <c r="R64" s="1" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4632,6 +4957,11 @@
         </is>
       </c>
       <c r="O65" s="1" t="n"/>
+      <c r="P65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="1" t="n"/>
+      <c r="R65" s="1" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4701,6 +5031,11 @@
         </is>
       </c>
       <c r="O66" s="1" t="n"/>
+      <c r="P66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="1" t="n"/>
+      <c r="R66" s="1" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4734,6 +5069,9 @@
         </is>
       </c>
       <c r="O67" s="1" t="n"/>
+      <c r="P67" s="1" t="n"/>
+      <c r="Q67" s="1" t="n"/>
+      <c r="R67" s="1" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4795,6 +5133,11 @@
         </is>
       </c>
       <c r="O68" s="1" t="n"/>
+      <c r="P68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="1" t="n"/>
+      <c r="R68" s="1" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4856,6 +5199,11 @@
         </is>
       </c>
       <c r="O69" s="1" t="n"/>
+      <c r="P69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="1" t="n"/>
+      <c r="R69" s="1" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4919,6 +5267,11 @@
       <c r="O70" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P70" s="1" t="n"/>
+      <c r="Q70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" s="1" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4982,6 +5335,11 @@
       <c r="O71" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P71" s="1" t="n"/>
+      <c r="Q71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" s="1" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5049,6 +5407,11 @@
       <c r="O72" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P72" s="1" t="n"/>
+      <c r="Q72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" s="1" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5120,6 +5483,11 @@
       <c r="O73" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P73" s="1" t="n"/>
+      <c r="Q73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" s="1" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5183,6 +5551,11 @@
       <c r="O74" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P74" s="1" t="n"/>
+      <c r="Q74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" s="1" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5250,6 +5623,11 @@
       <c r="O75" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P75" s="1" t="n"/>
+      <c r="Q75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" s="1" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5317,6 +5695,11 @@
       <c r="O76" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P76" s="1" t="n"/>
+      <c r="Q76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" s="1" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5384,6 +5767,11 @@
       <c r="O77" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P77" s="1" t="n"/>
+      <c r="Q77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R77" s="1" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5455,6 +5843,11 @@
       <c r="O78" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P78" s="1" t="n"/>
+      <c r="Q78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" s="1" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5522,6 +5915,11 @@
       <c r="O79" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P79" s="1" t="n"/>
+      <c r="Q79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" s="1" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5589,6 +5987,11 @@
       <c r="O80" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P80" s="1" t="n"/>
+      <c r="Q80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" s="1" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5660,6 +6063,11 @@
       <c r="O81" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P81" s="1" t="n"/>
+      <c r="Q81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R81" s="1" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5731,6 +6139,11 @@
       <c r="O82" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P82" s="1" t="n"/>
+      <c r="Q82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" s="1" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5798,6 +6211,11 @@
       <c r="O83" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P83" s="1" t="n"/>
+      <c r="Q83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R83" s="1" t="n"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5869,6 +6287,11 @@
       <c r="O84" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P84" s="1" t="n"/>
+      <c r="Q84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" s="1" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5936,6 +6359,11 @@
       <c r="O85" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P85" s="1" t="n"/>
+      <c r="Q85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R85" s="1" t="n"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6003,6 +6431,11 @@
       <c r="O86" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P86" s="1" t="n"/>
+      <c r="Q86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R86" s="1" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6074,6 +6507,11 @@
       <c r="O87" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P87" s="1" t="n"/>
+      <c r="Q87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R87" s="1" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6145,6 +6583,11 @@
       <c r="O88" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P88" s="1" t="n"/>
+      <c r="Q88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" s="1" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6212,6 +6655,11 @@
       <c r="O89" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P89" s="1" t="n"/>
+      <c r="Q89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R89" s="1" t="n"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6279,6 +6727,11 @@
       <c r="O90" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P90" s="1" t="n"/>
+      <c r="Q90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R90" s="1" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6312,6 +6765,9 @@
         </is>
       </c>
       <c r="O91" s="1" t="n"/>
+      <c r="P91" s="1" t="n"/>
+      <c r="Q91" s="1" t="n"/>
+      <c r="R91" s="1" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6345,6 +6801,9 @@
         </is>
       </c>
       <c r="O92" s="1" t="n"/>
+      <c r="P92" s="1" t="n"/>
+      <c r="Q92" s="1" t="n"/>
+      <c r="R92" s="1" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6378,6 +6837,9 @@
         </is>
       </c>
       <c r="O93" s="1" t="n"/>
+      <c r="P93" s="1" t="n"/>
+      <c r="Q93" s="1" t="n"/>
+      <c r="R93" s="1" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6439,6 +6901,9 @@
         </is>
       </c>
       <c r="O94" s="1" t="n"/>
+      <c r="P94" s="1" t="n"/>
+      <c r="Q94" s="1" t="n"/>
+      <c r="R94" s="1" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6508,6 +6973,11 @@
         </is>
       </c>
       <c r="O95" s="1" t="n"/>
+      <c r="P95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="1" t="n"/>
+      <c r="R95" s="1" t="n"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6577,6 +7047,11 @@
         </is>
       </c>
       <c r="O96" s="1" t="n"/>
+      <c r="P96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q96" s="1" t="n"/>
+      <c r="R96" s="1" t="n"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6642,6 +7117,11 @@
         </is>
       </c>
       <c r="O97" s="1" t="n"/>
+      <c r="P97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q97" s="1" t="n"/>
+      <c r="R97" s="1" t="n"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6707,6 +7187,11 @@
         </is>
       </c>
       <c r="O98" s="1" t="n"/>
+      <c r="P98" s="1" t="n"/>
+      <c r="Q98" s="1" t="n"/>
+      <c r="R98" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6772,6 +7257,11 @@
         </is>
       </c>
       <c r="O99" s="1" t="n"/>
+      <c r="P99" s="1" t="n"/>
+      <c r="Q99" s="1" t="n"/>
+      <c r="R99" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6837,6 +7327,11 @@
         </is>
       </c>
       <c r="O100" s="1" t="n"/>
+      <c r="P100" s="1" t="n"/>
+      <c r="Q100" s="1" t="n"/>
+      <c r="R100" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6906,6 +7401,11 @@
         </is>
       </c>
       <c r="O101" s="1" t="n"/>
+      <c r="P101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" s="1" t="n"/>
+      <c r="R101" s="1" t="n"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6971,6 +7471,11 @@
         </is>
       </c>
       <c r="O102" s="1" t="n"/>
+      <c r="P102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" s="1" t="n"/>
+      <c r="R102" s="1" t="n"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7040,6 +7545,11 @@
         </is>
       </c>
       <c r="O103" s="1" t="n"/>
+      <c r="P103" s="1" t="n"/>
+      <c r="Q103" s="1" t="n"/>
+      <c r="R103" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7109,6 +7619,11 @@
         </is>
       </c>
       <c r="O104" s="1" t="n"/>
+      <c r="P104" s="1" t="n"/>
+      <c r="Q104" s="1" t="n"/>
+      <c r="R104" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7178,6 +7693,11 @@
         </is>
       </c>
       <c r="O105" s="1" t="n"/>
+      <c r="P105" s="1" t="n"/>
+      <c r="Q105" s="1" t="n"/>
+      <c r="R105" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7243,6 +7763,11 @@
         </is>
       </c>
       <c r="O106" s="1" t="n"/>
+      <c r="P106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q106" s="1" t="n"/>
+      <c r="R106" s="1" t="n"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7308,6 +7833,11 @@
         </is>
       </c>
       <c r="O107" s="1" t="n"/>
+      <c r="P107" s="1" t="n"/>
+      <c r="Q107" s="1" t="n"/>
+      <c r="R107" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7377,6 +7907,11 @@
         </is>
       </c>
       <c r="O108" s="1" t="n"/>
+      <c r="P108" s="1" t="n"/>
+      <c r="Q108" s="1" t="n"/>
+      <c r="R108" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7442,6 +7977,11 @@
         </is>
       </c>
       <c r="O109" s="1" t="n"/>
+      <c r="P109" s="1" t="n"/>
+      <c r="Q109" s="1" t="n"/>
+      <c r="R109" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7511,6 +8051,11 @@
         </is>
       </c>
       <c r="O110" s="1" t="n"/>
+      <c r="P110" s="1" t="n"/>
+      <c r="Q110" s="1" t="n"/>
+      <c r="R110" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7544,6 +8089,9 @@
         </is>
       </c>
       <c r="O111" s="1" t="n"/>
+      <c r="P111" s="1" t="n"/>
+      <c r="Q111" s="1" t="n"/>
+      <c r="R111" s="1" t="n"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7577,6 +8125,9 @@
         </is>
       </c>
       <c r="O112" s="1" t="n"/>
+      <c r="P112" s="1" t="n"/>
+      <c r="Q112" s="1" t="n"/>
+      <c r="R112" s="1" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7610,6 +8161,9 @@
         </is>
       </c>
       <c r="O113" s="1" t="n"/>
+      <c r="P113" s="1" t="n"/>
+      <c r="Q113" s="1" t="n"/>
+      <c r="R113" s="1" t="n"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7643,6 +8197,9 @@
         </is>
       </c>
       <c r="O114" s="1" t="n"/>
+      <c r="P114" s="1" t="n"/>
+      <c r="Q114" s="1" t="n"/>
+      <c r="R114" s="1" t="n"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7708,6 +8265,11 @@
         </is>
       </c>
       <c r="O115" s="1" t="n"/>
+      <c r="P115" s="1" t="n"/>
+      <c r="Q115" s="1" t="n"/>
+      <c r="R115" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7773,6 +8335,11 @@
         </is>
       </c>
       <c r="O116" s="1" t="n"/>
+      <c r="P116" s="1" t="n"/>
+      <c r="Q116" s="1" t="n"/>
+      <c r="R116" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7838,6 +8405,11 @@
         </is>
       </c>
       <c r="O117" s="1" t="n"/>
+      <c r="P117" s="1" t="n"/>
+      <c r="Q117" s="1" t="n"/>
+      <c r="R117" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7907,6 +8479,11 @@
         </is>
       </c>
       <c r="O118" s="1" t="n"/>
+      <c r="P118" s="1" t="n"/>
+      <c r="Q118" s="1" t="n"/>
+      <c r="R118" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7968,6 +8545,9 @@
         </is>
       </c>
       <c r="O119" s="1" t="n"/>
+      <c r="P119" s="1" t="n"/>
+      <c r="Q119" s="1" t="n"/>
+      <c r="R119" s="1" t="n"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8037,6 +8617,11 @@
         </is>
       </c>
       <c r="O120" s="1" t="n"/>
+      <c r="P120" s="1" t="n"/>
+      <c r="Q120" s="1" t="n"/>
+      <c r="R120" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8102,6 +8687,11 @@
         </is>
       </c>
       <c r="O121" s="1" t="n"/>
+      <c r="P121" s="1" t="n"/>
+      <c r="Q121" s="1" t="n"/>
+      <c r="R121" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8167,6 +8757,11 @@
         </is>
       </c>
       <c r="O122" s="1" t="n"/>
+      <c r="P122" s="1" t="n"/>
+      <c r="Q122" s="1" t="n"/>
+      <c r="R122" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8232,6 +8827,11 @@
         </is>
       </c>
       <c r="O123" s="1" t="n"/>
+      <c r="P123" s="1" t="n"/>
+      <c r="Q123" s="1" t="n"/>
+      <c r="R123" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8301,6 +8901,11 @@
         </is>
       </c>
       <c r="O124" s="1" t="n"/>
+      <c r="P124" s="1" t="n"/>
+      <c r="Q124" s="1" t="n"/>
+      <c r="R124" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8366,6 +8971,9 @@
         </is>
       </c>
       <c r="O125" s="1" t="n"/>
+      <c r="P125" s="1" t="n"/>
+      <c r="Q125" s="1" t="n"/>
+      <c r="R125" s="1" t="n"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8435,6 +9043,11 @@
         </is>
       </c>
       <c r="O126" s="1" t="n"/>
+      <c r="P126" s="1" t="n"/>
+      <c r="Q126" s="1" t="n"/>
+      <c r="R126" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8500,6 +9113,11 @@
         </is>
       </c>
       <c r="O127" s="1" t="n"/>
+      <c r="P127" s="1" t="n"/>
+      <c r="Q127" s="1" t="n"/>
+      <c r="R127" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8569,6 +9187,11 @@
         </is>
       </c>
       <c r="O128" s="1" t="n"/>
+      <c r="P128" s="1" t="n"/>
+      <c r="Q128" s="1" t="n"/>
+      <c r="R128" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8630,6 +9253,9 @@
         </is>
       </c>
       <c r="O129" s="1" t="n"/>
+      <c r="P129" s="1" t="n"/>
+      <c r="Q129" s="1" t="n"/>
+      <c r="R129" s="1" t="n"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8691,6 +9317,9 @@
         </is>
       </c>
       <c r="O130" s="1" t="n"/>
+      <c r="P130" s="1" t="n"/>
+      <c r="Q130" s="1" t="n"/>
+      <c r="R130" s="1" t="n"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8756,6 +9385,11 @@
         </is>
       </c>
       <c r="O131" s="1" t="n"/>
+      <c r="P131" s="1" t="n"/>
+      <c r="Q131" s="1" t="n"/>
+      <c r="R131" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8821,6 +9455,9 @@
         </is>
       </c>
       <c r="O132" s="1" t="n"/>
+      <c r="P132" s="1" t="n"/>
+      <c r="Q132" s="1" t="n"/>
+      <c r="R132" s="1" t="n"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8890,6 +9527,11 @@
         </is>
       </c>
       <c r="O133" s="1" t="n"/>
+      <c r="P133" s="1" t="n"/>
+      <c r="Q133" s="1" t="n"/>
+      <c r="R133" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8955,6 +9597,9 @@
         </is>
       </c>
       <c r="O134" s="1" t="n"/>
+      <c r="P134" s="1" t="n"/>
+      <c r="Q134" s="1" t="n"/>
+      <c r="R134" s="1" t="n"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9024,6 +9669,11 @@
         </is>
       </c>
       <c r="O135" s="1" t="n"/>
+      <c r="P135" s="1" t="n"/>
+      <c r="Q135" s="1" t="n"/>
+      <c r="R135" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9057,6 +9707,9 @@
         </is>
       </c>
       <c r="O136" s="1" t="n"/>
+      <c r="P136" s="1" t="n"/>
+      <c r="Q136" s="1" t="n"/>
+      <c r="R136" s="1" t="n"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9090,6 +9743,9 @@
         </is>
       </c>
       <c r="O137" s="1" t="n"/>
+      <c r="P137" s="1" t="n"/>
+      <c r="Q137" s="1" t="n"/>
+      <c r="R137" s="1" t="n"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9155,6 +9811,11 @@
         </is>
       </c>
       <c r="O138" s="1" t="n"/>
+      <c r="P138" s="1" t="n"/>
+      <c r="Q138" s="1" t="n"/>
+      <c r="R138" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9224,6 +9885,11 @@
         </is>
       </c>
       <c r="O139" s="1" t="n"/>
+      <c r="P139" s="1" t="n"/>
+      <c r="Q139" s="1" t="n"/>
+      <c r="R139" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9285,6 +9951,9 @@
         </is>
       </c>
       <c r="O140" s="1" t="n"/>
+      <c r="P140" s="1" t="n"/>
+      <c r="Q140" s="1" t="n"/>
+      <c r="R140" s="1" t="n"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9346,6 +10015,9 @@
         </is>
       </c>
       <c r="O141" s="1" t="n"/>
+      <c r="P141" s="1" t="n"/>
+      <c r="Q141" s="1" t="n"/>
+      <c r="R141" s="1" t="n"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9407,6 +10079,11 @@
         </is>
       </c>
       <c r="O142" s="1" t="n"/>
+      <c r="P142" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q142" s="1" t="n"/>
+      <c r="R142" s="1" t="n"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9468,6 +10145,11 @@
         </is>
       </c>
       <c r="O143" s="1" t="n"/>
+      <c r="P143" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q143" s="1" t="n"/>
+      <c r="R143" s="1" t="n"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9529,6 +10211,11 @@
         </is>
       </c>
       <c r="O144" s="1" t="n"/>
+      <c r="P144" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q144" s="1" t="n"/>
+      <c r="R144" s="1" t="n"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9590,6 +10277,11 @@
         </is>
       </c>
       <c r="O145" s="1" t="n"/>
+      <c r="P145" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q145" s="1" t="n"/>
+      <c r="R145" s="1" t="n"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9651,6 +10343,11 @@
         </is>
       </c>
       <c r="O146" s="1" t="n"/>
+      <c r="P146" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q146" s="1" t="n"/>
+      <c r="R146" s="1" t="n"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9720,6 +10417,11 @@
         </is>
       </c>
       <c r="O147" s="1" t="n"/>
+      <c r="P147" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q147" s="1" t="n"/>
+      <c r="R147" s="1" t="n"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9781,6 +10483,11 @@
         </is>
       </c>
       <c r="O148" s="1" t="n"/>
+      <c r="P148" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q148" s="1" t="n"/>
+      <c r="R148" s="1" t="n"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9842,6 +10549,11 @@
         </is>
       </c>
       <c r="O149" s="1" t="n"/>
+      <c r="P149" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q149" s="1" t="n"/>
+      <c r="R149" s="1" t="n"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9875,6 +10587,9 @@
         </is>
       </c>
       <c r="O150" s="1" t="n"/>
+      <c r="P150" s="1" t="n"/>
+      <c r="Q150" s="1" t="n"/>
+      <c r="R150" s="1" t="n"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9944,6 +10659,11 @@
         </is>
       </c>
       <c r="O151" s="1" t="n"/>
+      <c r="P151" s="1" t="n"/>
+      <c r="Q151" s="1" t="n"/>
+      <c r="R151" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10009,6 +10729,11 @@
         </is>
       </c>
       <c r="O152" s="1" t="n"/>
+      <c r="P152" s="1" t="n"/>
+      <c r="Q152" s="1" t="n"/>
+      <c r="R152" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10074,6 +10799,11 @@
         </is>
       </c>
       <c r="O153" s="1" t="n"/>
+      <c r="P153" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q153" s="1" t="n"/>
+      <c r="R153" s="1" t="n"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10143,6 +10873,11 @@
         </is>
       </c>
       <c r="O154" s="1" t="n"/>
+      <c r="P154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q154" s="1" t="n"/>
+      <c r="R154" s="1" t="n"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10204,6 +10939,11 @@
         </is>
       </c>
       <c r="O155" s="1" t="n"/>
+      <c r="P155" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q155" s="1" t="n"/>
+      <c r="R155" s="1" t="n"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10273,6 +11013,11 @@
         </is>
       </c>
       <c r="O156" s="1" t="n"/>
+      <c r="P156" s="1" t="n"/>
+      <c r="Q156" s="1" t="n"/>
+      <c r="R156" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10338,6 +11083,11 @@
         </is>
       </c>
       <c r="O157" s="1" t="n"/>
+      <c r="P157" s="1" t="n"/>
+      <c r="Q157" s="1" t="n"/>
+      <c r="R157" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10371,6 +11121,9 @@
         </is>
       </c>
       <c r="O158" s="1" t="n"/>
+      <c r="P158" s="1" t="n"/>
+      <c r="Q158" s="1" t="n"/>
+      <c r="R158" s="1" t="n"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10436,6 +11189,11 @@
         </is>
       </c>
       <c r="O159" s="1" t="n"/>
+      <c r="P159" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q159" s="1" t="n"/>
+      <c r="R159" s="1" t="n"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10501,6 +11259,11 @@
         </is>
       </c>
       <c r="O160" s="1" t="n"/>
+      <c r="P160" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q160" s="1" t="n"/>
+      <c r="R160" s="1" t="n"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10566,6 +11329,11 @@
         </is>
       </c>
       <c r="O161" s="1" t="n"/>
+      <c r="P161" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q161" s="1" t="n"/>
+      <c r="R161" s="1" t="n"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10631,6 +11399,11 @@
         </is>
       </c>
       <c r="O162" s="1" t="n"/>
+      <c r="P162" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q162" s="1" t="n"/>
+      <c r="R162" s="1" t="n"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10700,6 +11473,11 @@
         </is>
       </c>
       <c r="O163" s="1" t="n"/>
+      <c r="P163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q163" s="1" t="n"/>
+      <c r="R163" s="1" t="n"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10765,6 +11543,11 @@
         </is>
       </c>
       <c r="O164" s="1" t="n"/>
+      <c r="P164" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q164" s="1" t="n"/>
+      <c r="R164" s="1" t="n"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10834,6 +11617,11 @@
         </is>
       </c>
       <c r="O165" s="1" t="n"/>
+      <c r="P165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q165" s="1" t="n"/>
+      <c r="R165" s="1" t="n"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10867,6 +11655,9 @@
         </is>
       </c>
       <c r="O166" s="1" t="n"/>
+      <c r="P166" s="1" t="n"/>
+      <c r="Q166" s="1" t="n"/>
+      <c r="R166" s="1" t="n"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10932,6 +11723,11 @@
         </is>
       </c>
       <c r="O167" s="1" t="n"/>
+      <c r="P167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q167" s="1" t="n"/>
+      <c r="R167" s="1" t="n"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11001,6 +11797,11 @@
         </is>
       </c>
       <c r="O168" s="1" t="n"/>
+      <c r="P168" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q168" s="1" t="n"/>
+      <c r="R168" s="1" t="n"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11066,6 +11867,11 @@
         </is>
       </c>
       <c r="O169" s="1" t="n"/>
+      <c r="P169" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q169" s="1" t="n"/>
+      <c r="R169" s="1" t="n"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11131,6 +11937,11 @@
         </is>
       </c>
       <c r="O170" s="1" t="n"/>
+      <c r="P170" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q170" s="1" t="n"/>
+      <c r="R170" s="1" t="n"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11196,6 +12007,11 @@
         </is>
       </c>
       <c r="O171" s="1" t="n"/>
+      <c r="P171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q171" s="1" t="n"/>
+      <c r="R171" s="1" t="n"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11229,6 +12045,9 @@
         </is>
       </c>
       <c r="O172" s="1" t="n"/>
+      <c r="P172" s="1" t="n"/>
+      <c r="Q172" s="1" t="n"/>
+      <c r="R172" s="1" t="n"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11262,6 +12081,9 @@
         </is>
       </c>
       <c r="O173" s="1" t="n"/>
+      <c r="P173" s="1" t="n"/>
+      <c r="Q173" s="1" t="n"/>
+      <c r="R173" s="1" t="n"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11327,6 +12149,11 @@
         </is>
       </c>
       <c r="O174" s="1" t="n"/>
+      <c r="P174" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q174" s="1" t="n"/>
+      <c r="R174" s="1" t="n"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11396,6 +12223,11 @@
         </is>
       </c>
       <c r="O175" s="1" t="n"/>
+      <c r="P175" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q175" s="1" t="n"/>
+      <c r="R175" s="1" t="n"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11461,6 +12293,11 @@
         </is>
       </c>
       <c r="O176" s="1" t="n"/>
+      <c r="P176" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q176" s="1" t="n"/>
+      <c r="R176" s="1" t="n"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11494,6 +12331,9 @@
         </is>
       </c>
       <c r="O177" s="1" t="n"/>
+      <c r="P177" s="1" t="n"/>
+      <c r="Q177" s="1" t="n"/>
+      <c r="R177" s="1" t="n"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11563,6 +12403,11 @@
         </is>
       </c>
       <c r="O178" s="1" t="n"/>
+      <c r="P178" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q178" s="1" t="n"/>
+      <c r="R178" s="1" t="n"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11632,6 +12477,11 @@
         </is>
       </c>
       <c r="O179" s="1" t="n"/>
+      <c r="P179" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q179" s="1" t="n"/>
+      <c r="R179" s="1" t="n"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11701,6 +12551,11 @@
         </is>
       </c>
       <c r="O180" s="1" t="n"/>
+      <c r="P180" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q180" s="1" t="n"/>
+      <c r="R180" s="1" t="n"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11770,6 +12625,11 @@
         </is>
       </c>
       <c r="O181" s="1" t="n"/>
+      <c r="P181" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q181" s="1" t="n"/>
+      <c r="R181" s="1" t="n"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11835,6 +12695,11 @@
         </is>
       </c>
       <c r="O182" s="1" t="n"/>
+      <c r="P182" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q182" s="1" t="n"/>
+      <c r="R182" s="1" t="n"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11904,6 +12769,11 @@
         </is>
       </c>
       <c r="O183" s="1" t="n"/>
+      <c r="P183" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q183" s="1" t="n"/>
+      <c r="R183" s="1" t="n"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11973,6 +12843,11 @@
         </is>
       </c>
       <c r="O184" s="1" t="n"/>
+      <c r="P184" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q184" s="1" t="n"/>
+      <c r="R184" s="1" t="n"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12006,6 +12881,9 @@
         </is>
       </c>
       <c r="O185" s="1" t="n"/>
+      <c r="P185" s="1" t="n"/>
+      <c r="Q185" s="1" t="n"/>
+      <c r="R185" s="1" t="n"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12075,6 +12953,11 @@
         </is>
       </c>
       <c r="O186" s="1" t="n"/>
+      <c r="P186" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q186" s="1" t="n"/>
+      <c r="R186" s="1" t="n"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12140,6 +13023,11 @@
         </is>
       </c>
       <c r="O187" s="1" t="n"/>
+      <c r="P187" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q187" s="1" t="n"/>
+      <c r="R187" s="1" t="n"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12173,6 +13061,9 @@
         </is>
       </c>
       <c r="O188" s="1" t="n"/>
+      <c r="P188" s="1" t="n"/>
+      <c r="Q188" s="1" t="n"/>
+      <c r="R188" s="1" t="n"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12242,6 +13133,9 @@
         </is>
       </c>
       <c r="O189" s="1" t="n"/>
+      <c r="P189" s="1" t="n"/>
+      <c r="Q189" s="1" t="n"/>
+      <c r="R189" s="1" t="n"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12303,6 +13197,11 @@
         </is>
       </c>
       <c r="O190" s="1" t="n"/>
+      <c r="P190" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q190" s="1" t="n"/>
+      <c r="R190" s="1" t="n"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12368,6 +13267,9 @@
         </is>
       </c>
       <c r="O191" s="1" t="n"/>
+      <c r="P191" s="1" t="n"/>
+      <c r="Q191" s="1" t="n"/>
+      <c r="R191" s="1" t="n"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12437,6 +13339,11 @@
         </is>
       </c>
       <c r="O192" s="1" t="n"/>
+      <c r="P192" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q192" s="1" t="n"/>
+      <c r="R192" s="1" t="n"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12502,6 +13409,11 @@
         </is>
       </c>
       <c r="O193" s="1" t="n"/>
+      <c r="P193" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q193" s="1" t="n"/>
+      <c r="R193" s="1" t="n"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12571,6 +13483,11 @@
         </is>
       </c>
       <c r="O194" s="1" t="n"/>
+      <c r="P194" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q194" s="1" t="n"/>
+      <c r="R194" s="1" t="n"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12640,6 +13557,9 @@
         </is>
       </c>
       <c r="O195" s="1" t="n"/>
+      <c r="P195" s="1" t="n"/>
+      <c r="Q195" s="1" t="n"/>
+      <c r="R195" s="1" t="n"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12705,6 +13625,11 @@
         </is>
       </c>
       <c r="O196" s="1" t="n"/>
+      <c r="P196" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q196" s="1" t="n"/>
+      <c r="R196" s="1" t="n"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12774,6 +13699,11 @@
         </is>
       </c>
       <c r="O197" s="1" t="n"/>
+      <c r="P197" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q197" s="1" t="n"/>
+      <c r="R197" s="1" t="n"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12843,6 +13773,11 @@
         </is>
       </c>
       <c r="O198" s="1" t="n"/>
+      <c r="P198" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q198" s="1" t="n"/>
+      <c r="R198" s="1" t="n"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12900,6 +13835,9 @@
         </is>
       </c>
       <c r="O199" s="1" t="n"/>
+      <c r="P199" s="1" t="n"/>
+      <c r="Q199" s="1" t="n"/>
+      <c r="R199" s="1" t="n"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12969,6 +13907,9 @@
         </is>
       </c>
       <c r="O200" s="1" t="n"/>
+      <c r="P200" s="1" t="n"/>
+      <c r="Q200" s="1" t="n"/>
+      <c r="R200" s="1" t="n"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13038,6 +13979,11 @@
         </is>
       </c>
       <c r="O201" s="1" t="n"/>
+      <c r="P201" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q201" s="1" t="n"/>
+      <c r="R201" s="1" t="n"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13107,6 +14053,11 @@
         </is>
       </c>
       <c r="O202" s="1" t="n"/>
+      <c r="P202" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q202" s="1" t="n"/>
+      <c r="R202" s="1" t="n"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13176,6 +14127,11 @@
         </is>
       </c>
       <c r="O203" s="1" t="n"/>
+      <c r="P203" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q203" s="1" t="n"/>
+      <c r="R203" s="1" t="n"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13241,6 +14197,11 @@
         </is>
       </c>
       <c r="O204" s="1" t="n"/>
+      <c r="P204" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q204" s="1" t="n"/>
+      <c r="R204" s="1" t="n"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13306,6 +14267,11 @@
         </is>
       </c>
       <c r="O205" s="1" t="n"/>
+      <c r="P205" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q205" s="1" t="n"/>
+      <c r="R205" s="1" t="n"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13371,6 +14337,11 @@
         </is>
       </c>
       <c r="O206" s="1" t="n"/>
+      <c r="P206" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q206" s="1" t="n"/>
+      <c r="R206" s="1" t="n"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13442,6 +14413,11 @@
       <c r="O207" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P207" s="1" t="n"/>
+      <c r="Q207" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R207" s="1" t="n"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13513,6 +14489,11 @@
       <c r="O208" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P208" s="1" t="n"/>
+      <c r="Q208" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R208" s="1" t="n"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13584,6 +14565,11 @@
       <c r="O209" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P209" s="1" t="n"/>
+      <c r="Q209" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R209" s="1" t="n"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13651,6 +14637,11 @@
       <c r="O210" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P210" s="1" t="n"/>
+      <c r="Q210" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R210" s="1" t="n"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13718,6 +14709,11 @@
       <c r="O211" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P211" s="1" t="n"/>
+      <c r="Q211" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R211" s="1" t="n"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13785,6 +14781,11 @@
       <c r="O212" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P212" s="1" t="n"/>
+      <c r="Q212" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R212" s="1" t="n"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13854,6 +14855,9 @@
         </is>
       </c>
       <c r="O213" s="1" t="n"/>
+      <c r="P213" s="1" t="n"/>
+      <c r="Q213" s="1" t="n"/>
+      <c r="R213" s="1" t="n"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -13917,6 +14921,11 @@
       <c r="O214" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P214" s="1" t="n"/>
+      <c r="Q214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R214" s="1" t="n"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13980,6 +14989,11 @@
       <c r="O215" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P215" s="1" t="n"/>
+      <c r="Q215" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R215" s="1" t="n"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -14043,6 +15057,11 @@
       <c r="O216" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P216" s="1" t="n"/>
+      <c r="Q216" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R216" s="1" t="n"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -14106,6 +15125,11 @@
       <c r="O217" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P217" s="1" t="n"/>
+      <c r="Q217" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R217" s="1" t="n"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -14169,6 +15193,11 @@
       <c r="O218" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P218" s="1" t="n"/>
+      <c r="Q218" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R218" s="1" t="n"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -14232,6 +15261,11 @@
       <c r="O219" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P219" s="1" t="n"/>
+      <c r="Q219" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R219" s="1" t="n"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14295,6 +15329,11 @@
       <c r="O220" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P220" s="1" t="n"/>
+      <c r="Q220" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R220" s="1" t="n"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -14358,6 +15397,11 @@
       <c r="O221" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P221" s="1" t="n"/>
+      <c r="Q221" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R221" s="1" t="n"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14429,6 +15473,11 @@
       <c r="O222" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P222" s="1" t="n"/>
+      <c r="Q222" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R222" s="1" t="n"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14500,6 +15549,11 @@
       <c r="O223" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P223" s="1" t="n"/>
+      <c r="Q223" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R223" s="1" t="n"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14571,6 +15625,11 @@
       <c r="O224" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P224" s="1" t="n"/>
+      <c r="Q224" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R224" s="1" t="n"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14642,6 +15701,11 @@
       <c r="O225" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P225" s="1" t="n"/>
+      <c r="Q225" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R225" s="1" t="n"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14705,6 +15769,11 @@
       <c r="O226" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P226" s="1" t="n"/>
+      <c r="Q226" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R226" s="1" t="n"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -14776,6 +15845,11 @@
       <c r="O227" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P227" s="1" t="n"/>
+      <c r="Q227" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R227" s="1" t="n"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -14847,6 +15921,11 @@
       <c r="O228" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P228" s="1" t="n"/>
+      <c r="Q228" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R228" s="1" t="n"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -14918,6 +15997,11 @@
       <c r="O229" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P229" s="1" t="n"/>
+      <c r="Q229" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R229" s="1" t="n"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14989,6 +16073,11 @@
       <c r="O230" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P230" s="1" t="n"/>
+      <c r="Q230" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R230" s="1" t="n"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -15060,6 +16149,11 @@
       <c r="O231" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P231" s="1" t="n"/>
+      <c r="Q231" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R231" s="1" t="n"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -15127,6 +16221,11 @@
       <c r="O232" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P232" s="1" t="n"/>
+      <c r="Q232" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R232" s="1" t="n"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -15194,6 +16293,11 @@
       <c r="O233" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P233" s="1" t="n"/>
+      <c r="Q233" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R233" s="1" t="n"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -15261,6 +16365,11 @@
       <c r="O234" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P234" s="1" t="n"/>
+      <c r="Q234" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R234" s="1" t="n"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -15328,6 +16437,11 @@
       <c r="O235" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P235" s="1" t="n"/>
+      <c r="Q235" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R235" s="1" t="n"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -15395,6 +16509,11 @@
       <c r="O236" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P236" s="1" t="n"/>
+      <c r="Q236" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R236" s="1" t="n"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -15462,6 +16581,11 @@
       <c r="O237" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P237" s="1" t="n"/>
+      <c r="Q237" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R237" s="1" t="n"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -15529,6 +16653,11 @@
       <c r="O238" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P238" s="1" t="n"/>
+      <c r="Q238" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R238" s="1" t="n"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -15596,6 +16725,11 @@
       <c r="O239" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P239" s="1" t="n"/>
+      <c r="Q239" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R239" s="1" t="n"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -15667,6 +16801,11 @@
       <c r="O240" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P240" s="1" t="n"/>
+      <c r="Q240" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R240" s="1" t="n"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -15734,6 +16873,11 @@
       <c r="O241" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P241" s="1" t="n"/>
+      <c r="Q241" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R241" s="1" t="n"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -15801,6 +16945,11 @@
       <c r="O242" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P242" s="1" t="n"/>
+      <c r="Q242" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R242" s="1" t="n"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -15872,6 +17021,11 @@
       <c r="O243" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P243" s="1" t="n"/>
+      <c r="Q243" s="1" t="n"/>
+      <c r="R243" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -15943,6 +17097,11 @@
       <c r="O244" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P244" s="1" t="n"/>
+      <c r="Q244" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R244" s="1" t="n"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -16014,6 +17173,11 @@
       <c r="O245" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P245" s="1" t="n"/>
+      <c r="Q245" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R245" s="1" t="n"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -16085,6 +17249,11 @@
       <c r="O246" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P246" s="1" t="n"/>
+      <c r="Q246" s="1" t="n"/>
+      <c r="R246" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -16156,6 +17325,11 @@
       <c r="O247" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P247" s="1" t="n"/>
+      <c r="Q247" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R247" s="1" t="n"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -16227,6 +17401,11 @@
       <c r="O248" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P248" s="1" t="n"/>
+      <c r="Q248" s="1" t="n"/>
+      <c r="R248" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -16294,6 +17473,11 @@
       <c r="O249" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P249" s="1" t="n"/>
+      <c r="Q249" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R249" s="1" t="n"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -16361,6 +17545,11 @@
       <c r="O250" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P250" s="1" t="n"/>
+      <c r="Q250" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R250" s="1" t="n"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -16432,6 +17621,11 @@
       <c r="O251" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P251" s="1" t="n"/>
+      <c r="Q251" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R251" s="1" t="n"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -16499,6 +17693,11 @@
       <c r="O252" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P252" s="1" t="n"/>
+      <c r="Q252" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R252" s="1" t="n"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -16566,6 +17765,11 @@
       <c r="O253" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P253" s="1" t="n"/>
+      <c r="Q253" s="1" t="n"/>
+      <c r="R253" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -16633,6 +17837,11 @@
       <c r="O254" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P254" s="1" t="n"/>
+      <c r="Q254" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R254" s="1" t="n"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -16700,6 +17909,11 @@
       <c r="O255" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P255" s="1" t="n"/>
+      <c r="Q255" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R255" s="1" t="n"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -16767,6 +17981,11 @@
       <c r="O256" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P256" s="1" t="n"/>
+      <c r="Q256" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R256" s="1" t="n"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -16834,6 +18053,11 @@
       <c r="O257" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P257" s="1" t="n"/>
+      <c r="Q257" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R257" s="1" t="n"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -16901,6 +18125,11 @@
       <c r="O258" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P258" s="1" t="n"/>
+      <c r="Q258" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R258" s="1" t="n"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -16966,6 +18195,11 @@
         </is>
       </c>
       <c r="O259" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P259" s="1" t="n"/>
+      <c r="Q259" s="1" t="n"/>
+      <c r="R259" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17029,6 +18263,9 @@
         </is>
       </c>
       <c r="O260" s="1" t="n"/>
+      <c r="P260" s="1" t="n"/>
+      <c r="Q260" s="1" t="n"/>
+      <c r="R260" s="1" t="n"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -17090,6 +18327,9 @@
         </is>
       </c>
       <c r="O261" s="1" t="n"/>
+      <c r="P261" s="1" t="n"/>
+      <c r="Q261" s="1" t="n"/>
+      <c r="R261" s="1" t="n"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -17155,6 +18395,9 @@
         </is>
       </c>
       <c r="O262" s="1" t="n"/>
+      <c r="P262" s="1" t="n"/>
+      <c r="Q262" s="1" t="n"/>
+      <c r="R262" s="1" t="n"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -17188,6 +18431,9 @@
         </is>
       </c>
       <c r="O263" s="1" t="n"/>
+      <c r="P263" s="1" t="n"/>
+      <c r="Q263" s="1" t="n"/>
+      <c r="R263" s="1" t="n"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -17259,6 +18505,11 @@
       <c r="O264" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P264" s="1" t="n"/>
+      <c r="Q264" s="1" t="n"/>
+      <c r="R264" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -17330,6 +18581,11 @@
       <c r="O265" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P265" s="1" t="n"/>
+      <c r="Q265" s="1" t="n"/>
+      <c r="R265" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -17401,6 +18657,11 @@
       <c r="O266" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P266" s="1" t="n"/>
+      <c r="Q266" s="1" t="n"/>
+      <c r="R266" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -17472,6 +18733,11 @@
       <c r="O267" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P267" s="1" t="n"/>
+      <c r="Q267" s="1" t="n"/>
+      <c r="R267" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -17543,6 +18809,11 @@
       <c r="O268" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P268" s="1" t="n"/>
+      <c r="Q268" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R268" s="1" t="n"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -17614,6 +18885,11 @@
       <c r="O269" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P269" s="1" t="n"/>
+      <c r="Q269" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R269" s="1" t="n"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -17685,6 +18961,11 @@
       <c r="O270" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P270" s="1" t="n"/>
+      <c r="Q270" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R270" s="1" t="n"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -17752,6 +19033,11 @@
       <c r="O271" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P271" s="1" t="n"/>
+      <c r="Q271" s="1" t="n"/>
+      <c r="R271" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -17819,6 +19105,11 @@
       <c r="O272" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P272" s="1" t="n"/>
+      <c r="Q272" s="1" t="n"/>
+      <c r="R272" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -17886,6 +19177,11 @@
       <c r="O273" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P273" s="1" t="n"/>
+      <c r="Q273" s="1" t="n"/>
+      <c r="R273" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -17953,6 +19249,11 @@
       <c r="O274" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P274" s="1" t="n"/>
+      <c r="Q274" s="1" t="n"/>
+      <c r="R274" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -18024,6 +19325,11 @@
       <c r="O275" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P275" s="1" t="n"/>
+      <c r="Q275" s="1" t="n"/>
+      <c r="R275" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -18095,6 +19401,11 @@
       <c r="O276" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P276" s="1" t="n"/>
+      <c r="Q276" s="1" t="n"/>
+      <c r="R276" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -18166,6 +19477,11 @@
       <c r="O277" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P277" s="1" t="n"/>
+      <c r="Q277" s="1" t="n"/>
+      <c r="R277" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -18233,6 +19549,11 @@
       <c r="O278" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P278" s="1" t="n"/>
+      <c r="Q278" s="1" t="n"/>
+      <c r="R278" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -18300,6 +19621,11 @@
       <c r="O279" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P279" s="1" t="n"/>
+      <c r="Q279" s="1" t="n"/>
+      <c r="R279" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -18367,6 +19693,11 @@
       <c r="O280" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P280" s="1" t="n"/>
+      <c r="Q280" s="1" t="n"/>
+      <c r="R280" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -18434,6 +19765,11 @@
       <c r="O281" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P281" s="1" t="n"/>
+      <c r="Q281" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R281" s="1" t="n"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -18505,6 +19841,11 @@
       <c r="O282" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P282" s="1" t="n"/>
+      <c r="Q282" s="1" t="n"/>
+      <c r="R282" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -18572,6 +19913,11 @@
       <c r="O283" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P283" s="1" t="n"/>
+      <c r="Q283" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R283" s="1" t="n"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -18639,6 +19985,11 @@
       <c r="O284" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P284" s="1" t="n"/>
+      <c r="Q284" s="1" t="n"/>
+      <c r="R284" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -18706,6 +20057,11 @@
       <c r="O285" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P285" s="1" t="n"/>
+      <c r="Q285" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R285" s="1" t="n"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -18771,6 +20127,9 @@
         </is>
       </c>
       <c r="O286" s="1" t="n"/>
+      <c r="P286" s="1" t="n"/>
+      <c r="Q286" s="1" t="n"/>
+      <c r="R286" s="1" t="n"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -18836,6 +20195,9 @@
         </is>
       </c>
       <c r="O287" s="1" t="n"/>
+      <c r="P287" s="1" t="n"/>
+      <c r="Q287" s="1" t="n"/>
+      <c r="R287" s="1" t="n"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -18897,6 +20259,11 @@
         </is>
       </c>
       <c r="O288" s="1" t="n"/>
+      <c r="P288" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q288" s="1" t="n"/>
+      <c r="R288" s="1" t="n"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -18958,6 +20325,11 @@
         </is>
       </c>
       <c r="O289" s="1" t="n"/>
+      <c r="P289" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q289" s="1" t="n"/>
+      <c r="R289" s="1" t="n"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -19027,6 +20399,11 @@
         </is>
       </c>
       <c r="O290" s="1" t="n"/>
+      <c r="P290" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q290" s="1" t="n"/>
+      <c r="R290" s="1" t="n"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -19092,6 +20469,11 @@
         </is>
       </c>
       <c r="O291" s="1" t="n"/>
+      <c r="P291" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q291" s="1" t="n"/>
+      <c r="R291" s="1" t="n"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -19157,6 +20539,11 @@
         </is>
       </c>
       <c r="O292" s="1" t="n"/>
+      <c r="P292" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q292" s="1" t="n"/>
+      <c r="R292" s="1" t="n"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -19222,6 +20609,11 @@
         </is>
       </c>
       <c r="O293" s="1" t="n"/>
+      <c r="P293" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q293" s="1" t="n"/>
+      <c r="R293" s="1" t="n"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -19255,6 +20647,9 @@
         </is>
       </c>
       <c r="O294" s="1" t="n"/>
+      <c r="P294" s="1" t="n"/>
+      <c r="Q294" s="1" t="n"/>
+      <c r="R294" s="1" t="n"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -19288,6 +20683,9 @@
         </is>
       </c>
       <c r="O295" s="1" t="n"/>
+      <c r="P295" s="1" t="n"/>
+      <c r="Q295" s="1" t="n"/>
+      <c r="R295" s="1" t="n"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -19353,6 +20751,9 @@
         </is>
       </c>
       <c r="O296" s="1" t="n"/>
+      <c r="P296" s="1" t="n"/>
+      <c r="Q296" s="1" t="n"/>
+      <c r="R296" s="1" t="n"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -19418,6 +20819,9 @@
         </is>
       </c>
       <c r="O297" s="1" t="n"/>
+      <c r="P297" s="1" t="n"/>
+      <c r="Q297" s="1" t="n"/>
+      <c r="R297" s="1" t="n"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -19479,6 +20883,9 @@
         </is>
       </c>
       <c r="O298" s="1" t="n"/>
+      <c r="P298" s="1" t="n"/>
+      <c r="Q298" s="1" t="n"/>
+      <c r="R298" s="1" t="n"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -19540,6 +20947,9 @@
         </is>
       </c>
       <c r="O299" s="1" t="n"/>
+      <c r="P299" s="1" t="n"/>
+      <c r="Q299" s="1" t="n"/>
+      <c r="R299" s="1" t="n"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -19605,6 +21015,9 @@
         </is>
       </c>
       <c r="O300" s="1" t="n"/>
+      <c r="P300" s="1" t="n"/>
+      <c r="Q300" s="1" t="n"/>
+      <c r="R300" s="1" t="n"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -19674,6 +21087,9 @@
         </is>
       </c>
       <c r="O301" s="1" t="n"/>
+      <c r="P301" s="1" t="n"/>
+      <c r="Q301" s="1" t="n"/>
+      <c r="R301" s="1" t="n"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -19739,6 +21155,9 @@
         </is>
       </c>
       <c r="O302" s="1" t="n"/>
+      <c r="P302" s="1" t="n"/>
+      <c r="Q302" s="1" t="n"/>
+      <c r="R302" s="1" t="n"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -19808,6 +21227,9 @@
         </is>
       </c>
       <c r="O303" s="1" t="n"/>
+      <c r="P303" s="1" t="n"/>
+      <c r="Q303" s="1" t="n"/>
+      <c r="R303" s="1" t="n"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -19841,11 +21263,14 @@
         </is>
       </c>
       <c r="O304" s="1" t="n"/>
+      <c r="P304" s="1" t="n"/>
+      <c r="Q304" s="1" t="n"/>
+      <c r="R304" s="1" t="n"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>567141000033111</t>
+          <t>571141000033114</t>
         </is>
       </c>
       <c r="B305" s="1" t="n">
@@ -19854,7 +21279,7 @@
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Fentazin  Injection  5 mg/ml</t>
+          <t>Fentazin  Tablets  8 mg</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -19874,11 +21299,14 @@
         </is>
       </c>
       <c r="O305" s="1" t="n"/>
+      <c r="P305" s="1" t="n"/>
+      <c r="Q305" s="1" t="n"/>
+      <c r="R305" s="1" t="n"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>571141000033114</t>
+          <t>567141000033111</t>
         </is>
       </c>
       <c r="B306" s="1" t="n">
@@ -19887,7 +21315,7 @@
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Fentazin  Tablets  8 mg</t>
+          <t>Fentazin  Injection  5 mg/ml</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -19907,6 +21335,9 @@
         </is>
       </c>
       <c r="O306" s="1" t="n"/>
+      <c r="P306" s="1" t="n"/>
+      <c r="Q306" s="1" t="n"/>
+      <c r="R306" s="1" t="n"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -19940,6 +21371,9 @@
         </is>
       </c>
       <c r="O307" s="1" t="n"/>
+      <c r="P307" s="1" t="n"/>
+      <c r="Q307" s="1" t="n"/>
+      <c r="R307" s="1" t="n"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -20001,6 +21435,11 @@
         </is>
       </c>
       <c r="O308" s="1" t="n"/>
+      <c r="P308" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q308" s="1" t="n"/>
+      <c r="R308" s="1" t="n"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -20062,6 +21501,11 @@
         </is>
       </c>
       <c r="O309" s="1" t="n"/>
+      <c r="P309" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q309" s="1" t="n"/>
+      <c r="R309" s="1" t="n"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -20127,6 +21571,11 @@
         </is>
       </c>
       <c r="O310" s="1" t="n"/>
+      <c r="P310" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q310" s="1" t="n"/>
+      <c r="R310" s="1" t="n"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -20192,6 +21641,11 @@
         </is>
       </c>
       <c r="O311" s="1" t="n"/>
+      <c r="P311" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q311" s="1" t="n"/>
+      <c r="R311" s="1" t="n"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -20225,6 +21679,9 @@
         </is>
       </c>
       <c r="O312" s="1" t="n"/>
+      <c r="P312" s="1" t="n"/>
+      <c r="Q312" s="1" t="n"/>
+      <c r="R312" s="1" t="n"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -20258,6 +21715,9 @@
         </is>
       </c>
       <c r="O313" s="1" t="n"/>
+      <c r="P313" s="1" t="n"/>
+      <c r="Q313" s="1" t="n"/>
+      <c r="R313" s="1" t="n"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -20327,6 +21787,11 @@
         </is>
       </c>
       <c r="O314" s="1" t="n"/>
+      <c r="P314" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q314" s="1" t="n"/>
+      <c r="R314" s="1" t="n"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -20396,6 +21861,11 @@
         </is>
       </c>
       <c r="O315" s="1" t="n"/>
+      <c r="P315" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q315" s="1" t="n"/>
+      <c r="R315" s="1" t="n"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -20457,6 +21927,11 @@
         </is>
       </c>
       <c r="O316" s="1" t="n"/>
+      <c r="P316" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q316" s="1" t="n"/>
+      <c r="R316" s="1" t="n"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -20518,6 +21993,11 @@
         </is>
       </c>
       <c r="O317" s="1" t="n"/>
+      <c r="P317" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q317" s="1" t="n"/>
+      <c r="R317" s="1" t="n"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -20587,6 +22067,11 @@
         </is>
       </c>
       <c r="O318" s="1" t="n"/>
+      <c r="P318" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q318" s="1" t="n"/>
+      <c r="R318" s="1" t="n"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -20620,6 +22105,9 @@
         </is>
       </c>
       <c r="O319" s="1" t="n"/>
+      <c r="P319" s="1" t="n"/>
+      <c r="Q319" s="1" t="n"/>
+      <c r="R319" s="1" t="n"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -20653,6 +22141,9 @@
         </is>
       </c>
       <c r="O320" s="1" t="n"/>
+      <c r="P320" s="1" t="n"/>
+      <c r="Q320" s="1" t="n"/>
+      <c r="R320" s="1" t="n"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -20686,6 +22177,9 @@
         </is>
       </c>
       <c r="O321" s="1" t="n"/>
+      <c r="P321" s="1" t="n"/>
+      <c r="Q321" s="1" t="n"/>
+      <c r="R321" s="1" t="n"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -20719,6 +22213,9 @@
         </is>
       </c>
       <c r="O322" s="1" t="n"/>
+      <c r="P322" s="1" t="n"/>
+      <c r="Q322" s="1" t="n"/>
+      <c r="R322" s="1" t="n"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -20780,6 +22277,11 @@
         </is>
       </c>
       <c r="O323" s="1" t="n"/>
+      <c r="P323" s="1" t="n"/>
+      <c r="Q323" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R323" s="1" t="n"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -20841,6 +22343,11 @@
         </is>
       </c>
       <c r="O324" s="1" t="n"/>
+      <c r="P324" s="1" t="n"/>
+      <c r="Q324" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R324" s="1" t="n"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -20902,6 +22409,11 @@
         </is>
       </c>
       <c r="O325" s="1" t="n"/>
+      <c r="P325" s="1" t="n"/>
+      <c r="Q325" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R325" s="1" t="n"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -20971,6 +22483,11 @@
         </is>
       </c>
       <c r="O326" s="1" t="n"/>
+      <c r="P326" s="1" t="n"/>
+      <c r="Q326" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R326" s="1" t="n"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -21032,6 +22549,11 @@
         </is>
       </c>
       <c r="O327" s="1" t="n"/>
+      <c r="P327" s="1" t="n"/>
+      <c r="Q327" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R327" s="1" t="n"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -21093,6 +22615,11 @@
         </is>
       </c>
       <c r="O328" s="1" t="n"/>
+      <c r="P328" s="1" t="n"/>
+      <c r="Q328" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R328" s="1" t="n"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -21162,6 +22689,11 @@
         </is>
       </c>
       <c r="O329" s="1" t="n"/>
+      <c r="P329" s="1" t="n"/>
+      <c r="Q329" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R329" s="1" t="n"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -21223,6 +22755,11 @@
         </is>
       </c>
       <c r="O330" s="1" t="n"/>
+      <c r="P330" s="1" t="n"/>
+      <c r="Q330" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R330" s="1" t="n"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -21284,6 +22821,11 @@
         </is>
       </c>
       <c r="O331" s="1" t="n"/>
+      <c r="P331" s="1" t="n"/>
+      <c r="Q331" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R331" s="1" t="n"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -21353,6 +22895,11 @@
         </is>
       </c>
       <c r="O332" s="1" t="n"/>
+      <c r="P332" s="1" t="n"/>
+      <c r="Q332" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R332" s="1" t="n"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -21418,6 +22965,11 @@
         </is>
       </c>
       <c r="O333" s="1" t="n"/>
+      <c r="P333" s="1" t="n"/>
+      <c r="Q333" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R333" s="1" t="n"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -21483,6 +23035,11 @@
         </is>
       </c>
       <c r="O334" s="1" t="n"/>
+      <c r="P334" s="1" t="n"/>
+      <c r="Q334" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R334" s="1" t="n"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -21548,6 +23105,11 @@
         </is>
       </c>
       <c r="O335" s="1" t="n"/>
+      <c r="P335" s="1" t="n"/>
+      <c r="Q335" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R335" s="1" t="n"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -21613,6 +23175,11 @@
         </is>
       </c>
       <c r="O336" s="1" t="n"/>
+      <c r="P336" s="1" t="n"/>
+      <c r="Q336" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R336" s="1" t="n"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -21678,6 +23245,11 @@
         </is>
       </c>
       <c r="O337" s="1" t="n"/>
+      <c r="P337" s="1" t="n"/>
+      <c r="Q337" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R337" s="1" t="n"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -21743,6 +23315,11 @@
         </is>
       </c>
       <c r="O338" s="1" t="n"/>
+      <c r="P338" s="1" t="n"/>
+      <c r="Q338" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R338" s="1" t="n"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -21808,6 +23385,11 @@
         </is>
       </c>
       <c r="O339" s="1" t="n"/>
+      <c r="P339" s="1" t="n"/>
+      <c r="Q339" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R339" s="1" t="n"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -21873,6 +23455,11 @@
         </is>
       </c>
       <c r="O340" s="1" t="n"/>
+      <c r="P340" s="1" t="n"/>
+      <c r="Q340" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R340" s="1" t="n"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -21938,6 +23525,11 @@
         </is>
       </c>
       <c r="O341" s="1" t="n"/>
+      <c r="P341" s="1" t="n"/>
+      <c r="Q341" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R341" s="1" t="n"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -22003,6 +23595,11 @@
         </is>
       </c>
       <c r="O342" s="1" t="n"/>
+      <c r="P342" s="1" t="n"/>
+      <c r="Q342" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R342" s="1" t="n"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -22068,6 +23665,11 @@
         </is>
       </c>
       <c r="O343" s="1" t="n"/>
+      <c r="P343" s="1" t="n"/>
+      <c r="Q343" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R343" s="1" t="n"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -22133,6 +23735,11 @@
         </is>
       </c>
       <c r="O344" s="1" t="n"/>
+      <c r="P344" s="1" t="n"/>
+      <c r="Q344" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R344" s="1" t="n"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -22198,6 +23805,11 @@
         </is>
       </c>
       <c r="O345" s="1" t="n"/>
+      <c r="P345" s="1" t="n"/>
+      <c r="Q345" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R345" s="1" t="n"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -22263,6 +23875,11 @@
         </is>
       </c>
       <c r="O346" s="1" t="n"/>
+      <c r="P346" s="1" t="n"/>
+      <c r="Q346" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R346" s="1" t="n"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -22328,6 +23945,11 @@
         </is>
       </c>
       <c r="O347" s="1" t="n"/>
+      <c r="P347" s="1" t="n"/>
+      <c r="Q347" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R347" s="1" t="n"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -22393,6 +24015,11 @@
         </is>
       </c>
       <c r="O348" s="1" t="n"/>
+      <c r="P348" s="1" t="n"/>
+      <c r="Q348" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R348" s="1" t="n"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -22458,6 +24085,11 @@
         </is>
       </c>
       <c r="O349" s="1" t="n"/>
+      <c r="P349" s="1" t="n"/>
+      <c r="Q349" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R349" s="1" t="n"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -22523,6 +24155,11 @@
         </is>
       </c>
       <c r="O350" s="1" t="n"/>
+      <c r="P350" s="1" t="n"/>
+      <c r="Q350" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R350" s="1" t="n"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -22588,6 +24225,11 @@
         </is>
       </c>
       <c r="O351" s="1" t="n"/>
+      <c r="P351" s="1" t="n"/>
+      <c r="Q351" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R351" s="1" t="n"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -22653,6 +24295,11 @@
         </is>
       </c>
       <c r="O352" s="1" t="n"/>
+      <c r="P352" s="1" t="n"/>
+      <c r="Q352" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R352" s="1" t="n"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -22718,6 +24365,11 @@
         </is>
       </c>
       <c r="O353" s="1" t="n"/>
+      <c r="P353" s="1" t="n"/>
+      <c r="Q353" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R353" s="1" t="n"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -22783,6 +24435,11 @@
         </is>
       </c>
       <c r="O354" s="1" t="n"/>
+      <c r="P354" s="1" t="n"/>
+      <c r="Q354" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R354" s="1" t="n"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -22848,6 +24505,11 @@
         </is>
       </c>
       <c r="O355" s="1" t="n"/>
+      <c r="P355" s="1" t="n"/>
+      <c r="Q355" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R355" s="1" t="n"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -22913,6 +24575,11 @@
         </is>
       </c>
       <c r="O356" s="1" t="n"/>
+      <c r="P356" s="1" t="n"/>
+      <c r="Q356" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R356" s="1" t="n"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -22978,6 +24645,11 @@
         </is>
       </c>
       <c r="O357" s="1" t="n"/>
+      <c r="P357" s="1" t="n"/>
+      <c r="Q357" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R357" s="1" t="n"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -23043,6 +24715,11 @@
         </is>
       </c>
       <c r="O358" s="1" t="n"/>
+      <c r="P358" s="1" t="n"/>
+      <c r="Q358" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R358" s="1" t="n"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -23112,6 +24789,11 @@
         </is>
       </c>
       <c r="O359" s="1" t="n"/>
+      <c r="P359" s="1" t="n"/>
+      <c r="Q359" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R359" s="1" t="n"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -23177,6 +24859,11 @@
         </is>
       </c>
       <c r="O360" s="1" t="n"/>
+      <c r="P360" s="1" t="n"/>
+      <c r="Q360" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R360" s="1" t="n"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -23242,6 +24929,11 @@
         </is>
       </c>
       <c r="O361" s="1" t="n"/>
+      <c r="P361" s="1" t="n"/>
+      <c r="Q361" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R361" s="1" t="n"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -23307,6 +24999,11 @@
         </is>
       </c>
       <c r="O362" s="1" t="n"/>
+      <c r="P362" s="1" t="n"/>
+      <c r="Q362" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R362" s="1" t="n"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -23372,6 +25069,11 @@
         </is>
       </c>
       <c r="O363" s="1" t="n"/>
+      <c r="P363" s="1" t="n"/>
+      <c r="Q363" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R363" s="1" t="n"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -23405,6 +25107,9 @@
         </is>
       </c>
       <c r="O364" s="1" t="n"/>
+      <c r="P364" s="1" t="n"/>
+      <c r="Q364" s="1" t="n"/>
+      <c r="R364" s="1" t="n"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -23470,6 +25175,11 @@
         </is>
       </c>
       <c r="O365" s="1" t="n"/>
+      <c r="P365" s="1" t="n"/>
+      <c r="Q365" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R365" s="1" t="n"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -23535,6 +25245,11 @@
         </is>
       </c>
       <c r="O366" s="1" t="n"/>
+      <c r="P366" s="1" t="n"/>
+      <c r="Q366" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R366" s="1" t="n"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -23604,6 +25319,11 @@
         </is>
       </c>
       <c r="O367" s="1" t="n"/>
+      <c r="P367" s="1" t="n"/>
+      <c r="Q367" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R367" s="1" t="n"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -23669,6 +25389,11 @@
         </is>
       </c>
       <c r="O368" s="1" t="n"/>
+      <c r="P368" s="1" t="n"/>
+      <c r="Q368" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R368" s="1" t="n"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -23734,6 +25459,11 @@
         </is>
       </c>
       <c r="O369" s="1" t="n"/>
+      <c r="P369" s="1" t="n"/>
+      <c r="Q369" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R369" s="1" t="n"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -23799,6 +25529,11 @@
         </is>
       </c>
       <c r="O370" s="1" t="n"/>
+      <c r="P370" s="1" t="n"/>
+      <c r="Q370" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R370" s="1" t="n"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -23868,6 +25603,9 @@
         </is>
       </c>
       <c r="O371" s="1" t="n"/>
+      <c r="P371" s="1" t="n"/>
+      <c r="Q371" s="1" t="n"/>
+      <c r="R371" s="1" t="n"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -23933,6 +25671,11 @@
         </is>
       </c>
       <c r="O372" s="1" t="n"/>
+      <c r="P372" s="1" t="n"/>
+      <c r="Q372" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R372" s="1" t="n"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -23998,6 +25741,11 @@
         </is>
       </c>
       <c r="O373" s="1" t="n"/>
+      <c r="P373" s="1" t="n"/>
+      <c r="Q373" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R373" s="1" t="n"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -24063,6 +25811,11 @@
         </is>
       </c>
       <c r="O374" s="1" t="n"/>
+      <c r="P374" s="1" t="n"/>
+      <c r="Q374" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R374" s="1" t="n"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -24132,6 +25885,11 @@
         </is>
       </c>
       <c r="O375" s="1" t="n"/>
+      <c r="P375" s="1" t="n"/>
+      <c r="Q375" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R375" s="1" t="n"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -24201,6 +25959,11 @@
         </is>
       </c>
       <c r="O376" s="1" t="n"/>
+      <c r="P376" s="1" t="n"/>
+      <c r="Q376" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R376" s="1" t="n"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -24270,6 +26033,11 @@
         </is>
       </c>
       <c r="O377" s="1" t="n"/>
+      <c r="P377" s="1" t="n"/>
+      <c r="Q377" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R377" s="1" t="n"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -24335,6 +26103,11 @@
         </is>
       </c>
       <c r="O378" s="1" t="n"/>
+      <c r="P378" s="1" t="n"/>
+      <c r="Q378" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R378" s="1" t="n"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -24368,6 +26141,9 @@
         </is>
       </c>
       <c r="O379" s="1" t="n"/>
+      <c r="P379" s="1" t="n"/>
+      <c r="Q379" s="1" t="n"/>
+      <c r="R379" s="1" t="n"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -24437,6 +26213,11 @@
         </is>
       </c>
       <c r="O380" s="1" t="n"/>
+      <c r="P380" s="1" t="n"/>
+      <c r="Q380" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R380" s="1" t="n"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -24506,6 +26287,11 @@
         </is>
       </c>
       <c r="O381" s="1" t="n"/>
+      <c r="P381" s="1" t="n"/>
+      <c r="Q381" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R381" s="1" t="n"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -24571,6 +26357,11 @@
         </is>
       </c>
       <c r="O382" s="1" t="n"/>
+      <c r="P382" s="1" t="n"/>
+      <c r="Q382" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R382" s="1" t="n"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -24636,6 +26427,9 @@
         </is>
       </c>
       <c r="O383" s="1" t="n"/>
+      <c r="P383" s="1" t="n"/>
+      <c r="Q383" s="1" t="n"/>
+      <c r="R383" s="1" t="n"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -24701,6 +26495,11 @@
         </is>
       </c>
       <c r="O384" s="1" t="n"/>
+      <c r="P384" s="1" t="n"/>
+      <c r="Q384" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R384" s="1" t="n"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -24766,6 +26565,11 @@
         </is>
       </c>
       <c r="O385" s="1" t="n"/>
+      <c r="P385" s="1" t="n"/>
+      <c r="Q385" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R385" s="1" t="n"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -24835,6 +26639,11 @@
         </is>
       </c>
       <c r="O386" s="1" t="n"/>
+      <c r="P386" s="1" t="n"/>
+      <c r="Q386" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R386" s="1" t="n"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -24904,6 +26713,11 @@
         </is>
       </c>
       <c r="O387" s="1" t="n"/>
+      <c r="P387" s="1" t="n"/>
+      <c r="Q387" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R387" s="1" t="n"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -24969,6 +26783,11 @@
         </is>
       </c>
       <c r="O388" s="1" t="n"/>
+      <c r="P388" s="1" t="n"/>
+      <c r="Q388" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R388" s="1" t="n"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -25034,6 +26853,11 @@
         </is>
       </c>
       <c r="O389" s="1" t="n"/>
+      <c r="P389" s="1" t="n"/>
+      <c r="Q389" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R389" s="1" t="n"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -25067,6 +26891,9 @@
         </is>
       </c>
       <c r="O390" s="1" t="n"/>
+      <c r="P390" s="1" t="n"/>
+      <c r="Q390" s="1" t="n"/>
+      <c r="R390" s="1" t="n"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -25136,6 +26963,11 @@
         </is>
       </c>
       <c r="O391" s="1" t="n"/>
+      <c r="P391" s="1" t="n"/>
+      <c r="Q391" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R391" s="1" t="n"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -25169,6 +27001,9 @@
         </is>
       </c>
       <c r="O392" s="1" t="n"/>
+      <c r="P392" s="1" t="n"/>
+      <c r="Q392" s="1" t="n"/>
+      <c r="R392" s="1" t="n"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -25234,6 +27069,11 @@
         </is>
       </c>
       <c r="O393" s="1" t="n"/>
+      <c r="P393" s="1" t="n"/>
+      <c r="Q393" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R393" s="1" t="n"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -25299,6 +27139,11 @@
         </is>
       </c>
       <c r="O394" s="1" t="n"/>
+      <c r="P394" s="1" t="n"/>
+      <c r="Q394" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R394" s="1" t="n"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -25332,6 +27177,9 @@
         </is>
       </c>
       <c r="O395" s="1" t="n"/>
+      <c r="P395" s="1" t="n"/>
+      <c r="Q395" s="1" t="n"/>
+      <c r="R395" s="1" t="n"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -25397,6 +27245,11 @@
         </is>
       </c>
       <c r="O396" s="1" t="n"/>
+      <c r="P396" s="1" t="n"/>
+      <c r="Q396" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R396" s="1" t="n"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -25462,6 +27315,11 @@
         </is>
       </c>
       <c r="O397" s="1" t="n"/>
+      <c r="P397" s="1" t="n"/>
+      <c r="Q397" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R397" s="1" t="n"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -25527,6 +27385,11 @@
         </is>
       </c>
       <c r="O398" s="1" t="n"/>
+      <c r="P398" s="1" t="n"/>
+      <c r="Q398" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R398" s="1" t="n"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -25592,6 +27455,11 @@
         </is>
       </c>
       <c r="O399" s="1" t="n"/>
+      <c r="P399" s="1" t="n"/>
+      <c r="Q399" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R399" s="1" t="n"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -25657,6 +27525,11 @@
         </is>
       </c>
       <c r="O400" s="1" t="n"/>
+      <c r="P400" s="1" t="n"/>
+      <c r="Q400" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R400" s="1" t="n"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -25722,6 +27595,11 @@
         </is>
       </c>
       <c r="O401" s="1" t="n"/>
+      <c r="P401" s="1" t="n"/>
+      <c r="Q401" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R401" s="1" t="n"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -25787,6 +27665,11 @@
         </is>
       </c>
       <c r="O402" s="1" t="n"/>
+      <c r="P402" s="1" t="n"/>
+      <c r="Q402" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R402" s="1" t="n"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -25852,6 +27735,11 @@
         </is>
       </c>
       <c r="O403" s="1" t="n"/>
+      <c r="P403" s="1" t="n"/>
+      <c r="Q403" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R403" s="1" t="n"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -25917,6 +27805,11 @@
         </is>
       </c>
       <c r="O404" s="1" t="n"/>
+      <c r="P404" s="1" t="n"/>
+      <c r="Q404" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R404" s="1" t="n"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -25982,6 +27875,11 @@
         </is>
       </c>
       <c r="O405" s="1" t="n"/>
+      <c r="P405" s="1" t="n"/>
+      <c r="Q405" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R405" s="1" t="n"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -26045,6 +27943,11 @@
       <c r="O406" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P406" s="1" t="n"/>
+      <c r="Q406" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R406" s="1" t="n"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -26108,6 +28011,11 @@
       <c r="O407" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P407" s="1" t="n"/>
+      <c r="Q407" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R407" s="1" t="n"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -26171,6 +28079,11 @@
       <c r="O408" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P408" s="1" t="n"/>
+      <c r="Q408" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R408" s="1" t="n"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -26234,6 +28147,11 @@
       <c r="O409" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P409" s="1" t="n"/>
+      <c r="Q409" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R409" s="1" t="n"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -26297,6 +28215,11 @@
       <c r="O410" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P410" s="1" t="n"/>
+      <c r="Q410" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R410" s="1" t="n"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -26360,6 +28283,11 @@
       <c r="O411" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P411" s="1" t="n"/>
+      <c r="Q411" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R411" s="1" t="n"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -26423,6 +28351,11 @@
       <c r="O412" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P412" s="1" t="n"/>
+      <c r="Q412" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R412" s="1" t="n"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -26494,6 +28427,11 @@
       <c r="O413" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P413" s="1" t="n"/>
+      <c r="Q413" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R413" s="1" t="n"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -26561,6 +28499,11 @@
       <c r="O414" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P414" s="1" t="n"/>
+      <c r="Q414" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R414" s="1" t="n"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -26628,6 +28571,11 @@
       <c r="O415" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P415" s="1" t="n"/>
+      <c r="Q415" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R415" s="1" t="n"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -26699,6 +28647,11 @@
       <c r="O416" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P416" s="1" t="n"/>
+      <c r="Q416" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R416" s="1" t="n"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -26770,6 +28723,11 @@
       <c r="O417" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P417" s="1" t="n"/>
+      <c r="Q417" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R417" s="1" t="n"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -26841,6 +28799,11 @@
       <c r="O418" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P418" s="1" t="n"/>
+      <c r="Q418" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R418" s="1" t="n"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -26908,6 +28871,11 @@
       <c r="O419" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P419" s="1" t="n"/>
+      <c r="Q419" s="1" t="n"/>
+      <c r="R419" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -26975,6 +28943,11 @@
       <c r="O420" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P420" s="1" t="n"/>
+      <c r="Q420" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R420" s="1" t="n"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -27042,6 +29015,11 @@
       <c r="O421" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P421" s="1" t="n"/>
+      <c r="Q421" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R421" s="1" t="n"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -27109,6 +29087,11 @@
       <c r="O422" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P422" s="1" t="n"/>
+      <c r="Q422" s="1" t="n"/>
+      <c r="R422" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -27180,6 +29163,11 @@
       <c r="O423" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P423" s="1" t="n"/>
+      <c r="Q423" s="1" t="n"/>
+      <c r="R423" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -27251,6 +29239,11 @@
       <c r="O424" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P424" s="1" t="n"/>
+      <c r="Q424" s="1" t="n"/>
+      <c r="R424" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -27318,6 +29311,11 @@
       <c r="O425" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P425" s="1" t="n"/>
+      <c r="Q425" s="1" t="n"/>
+      <c r="R425" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -27389,6 +29387,11 @@
       <c r="O426" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P426" s="1" t="n"/>
+      <c r="Q426" s="1" t="n"/>
+      <c r="R426" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -27456,6 +29459,11 @@
       <c r="O427" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P427" s="1" t="n"/>
+      <c r="Q427" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R427" s="1" t="n"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -27527,6 +29535,11 @@
       <c r="O428" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P428" s="1" t="n"/>
+      <c r="Q428" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R428" s="1" t="n"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -27598,6 +29611,11 @@
       <c r="O429" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P429" s="1" t="n"/>
+      <c r="Q429" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R429" s="1" t="n"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -27665,6 +29683,11 @@
       <c r="O430" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P430" s="1" t="n"/>
+      <c r="Q430" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R430" s="1" t="n"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -27732,6 +29755,11 @@
       <c r="O431" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P431" s="1" t="n"/>
+      <c r="Q431" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R431" s="1" t="n"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -27799,6 +29827,11 @@
       <c r="O432" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P432" s="1" t="n"/>
+      <c r="Q432" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R432" s="1" t="n"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -27866,6 +29899,11 @@
       <c r="O433" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P433" s="1" t="n"/>
+      <c r="Q433" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R433" s="1" t="n"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -27933,6 +29971,11 @@
       <c r="O434" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P434" s="1" t="n"/>
+      <c r="Q434" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R434" s="1" t="n"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -28000,6 +30043,11 @@
       <c r="O435" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P435" s="1" t="n"/>
+      <c r="Q435" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R435" s="1" t="n"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -28067,6 +30115,11 @@
       <c r="O436" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P436" s="1" t="n"/>
+      <c r="Q436" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R436" s="1" t="n"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -28132,6 +30185,9 @@
         </is>
       </c>
       <c r="O437" s="1" t="n"/>
+      <c r="P437" s="1" t="n"/>
+      <c r="Q437" s="1" t="n"/>
+      <c r="R437" s="1" t="n"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -28203,6 +30259,9 @@
       <c r="O438" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P438" s="1" t="n"/>
+      <c r="Q438" s="1" t="n"/>
+      <c r="R438" s="1" t="n"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -28274,6 +30333,9 @@
       <c r="O439" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P439" s="1" t="n"/>
+      <c r="Q439" s="1" t="n"/>
+      <c r="R439" s="1" t="n"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -28337,6 +30399,9 @@
       <c r="O440" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P440" s="1" t="n"/>
+      <c r="Q440" s="1" t="n"/>
+      <c r="R440" s="1" t="n"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -28408,6 +30473,9 @@
       <c r="O441" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P441" s="1" t="n"/>
+      <c r="Q441" s="1" t="n"/>
+      <c r="R441" s="1" t="n"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -28479,6 +30547,9 @@
       <c r="O442" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P442" s="1" t="n"/>
+      <c r="Q442" s="1" t="n"/>
+      <c r="R442" s="1" t="n"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -28542,6 +30613,9 @@
       <c r="O443" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P443" s="1" t="n"/>
+      <c r="Q443" s="1" t="n"/>
+      <c r="R443" s="1" t="n"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -28605,6 +30679,9 @@
       <c r="O444" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P444" s="1" t="n"/>
+      <c r="Q444" s="1" t="n"/>
+      <c r="R444" s="1" t="n"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -28668,6 +30745,9 @@
       <c r="O445" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P445" s="1" t="n"/>
+      <c r="Q445" s="1" t="n"/>
+      <c r="R445" s="1" t="n"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -28729,6 +30809,11 @@
         </is>
       </c>
       <c r="O446" s="1" t="n"/>
+      <c r="P446" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q446" s="1" t="n"/>
+      <c r="R446" s="1" t="n"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -28790,6 +30875,11 @@
         </is>
       </c>
       <c r="O447" s="1" t="n"/>
+      <c r="P447" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q447" s="1" t="n"/>
+      <c r="R447" s="1" t="n"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -28859,6 +30949,11 @@
         </is>
       </c>
       <c r="O448" s="1" t="n"/>
+      <c r="P448" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q448" s="1" t="n"/>
+      <c r="R448" s="1" t="n"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -28924,6 +31019,11 @@
         </is>
       </c>
       <c r="O449" s="1" t="n"/>
+      <c r="P449" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q449" s="1" t="n"/>
+      <c r="R449" s="1" t="n"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -28989,6 +31089,11 @@
         </is>
       </c>
       <c r="O450" s="1" t="n"/>
+      <c r="P450" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q450" s="1" t="n"/>
+      <c r="R450" s="1" t="n"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -29054,6 +31159,11 @@
         </is>
       </c>
       <c r="O451" s="1" t="n"/>
+      <c r="P451" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q451" s="1" t="n"/>
+      <c r="R451" s="1" t="n"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -29119,6 +31229,11 @@
         </is>
       </c>
       <c r="O452" s="1" t="n"/>
+      <c r="P452" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q452" s="1" t="n"/>
+      <c r="R452" s="1" t="n"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -29180,6 +31295,9 @@
         </is>
       </c>
       <c r="O453" s="1" t="n"/>
+      <c r="P453" s="1" t="n"/>
+      <c r="Q453" s="1" t="n"/>
+      <c r="R453" s="1" t="n"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -29241,6 +31359,9 @@
         </is>
       </c>
       <c r="O454" s="1" t="n"/>
+      <c r="P454" s="1" t="n"/>
+      <c r="Q454" s="1" t="n"/>
+      <c r="R454" s="1" t="n"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -29302,6 +31423,9 @@
         </is>
       </c>
       <c r="O455" s="1" t="n"/>
+      <c r="P455" s="1" t="n"/>
+      <c r="Q455" s="1" t="n"/>
+      <c r="R455" s="1" t="n"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -29367,6 +31491,9 @@
         </is>
       </c>
       <c r="O456" s="1" t="n"/>
+      <c r="P456" s="1" t="n"/>
+      <c r="Q456" s="1" t="n"/>
+      <c r="R456" s="1" t="n"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -29432,6 +31559,9 @@
         </is>
       </c>
       <c r="O457" s="1" t="n"/>
+      <c r="P457" s="1" t="n"/>
+      <c r="Q457" s="1" t="n"/>
+      <c r="R457" s="1" t="n"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -29493,6 +31623,9 @@
         </is>
       </c>
       <c r="O458" s="1" t="n"/>
+      <c r="P458" s="1" t="n"/>
+      <c r="Q458" s="1" t="n"/>
+      <c r="R458" s="1" t="n"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -29554,6 +31687,9 @@
         </is>
       </c>
       <c r="O459" s="1" t="n"/>
+      <c r="P459" s="1" t="n"/>
+      <c r="Q459" s="1" t="n"/>
+      <c r="R459" s="1" t="n"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -29619,6 +31755,9 @@
         </is>
       </c>
       <c r="O460" s="1" t="n"/>
+      <c r="P460" s="1" t="n"/>
+      <c r="Q460" s="1" t="n"/>
+      <c r="R460" s="1" t="n"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -29680,6 +31819,9 @@
         </is>
       </c>
       <c r="O461" s="1" t="n"/>
+      <c r="P461" s="1" t="n"/>
+      <c r="Q461" s="1" t="n"/>
+      <c r="R461" s="1" t="n"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -29745,6 +31887,9 @@
         </is>
       </c>
       <c r="O462" s="1" t="n"/>
+      <c r="P462" s="1" t="n"/>
+      <c r="Q462" s="1" t="n"/>
+      <c r="R462" s="1" t="n"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -29810,6 +31955,9 @@
         </is>
       </c>
       <c r="O463" s="1" t="n"/>
+      <c r="P463" s="1" t="n"/>
+      <c r="Q463" s="1" t="n"/>
+      <c r="R463" s="1" t="n"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -29875,6 +32023,9 @@
         </is>
       </c>
       <c r="O464" s="1" t="n"/>
+      <c r="P464" s="1" t="n"/>
+      <c r="Q464" s="1" t="n"/>
+      <c r="R464" s="1" t="n"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -29908,6 +32059,9 @@
         </is>
       </c>
       <c r="O465" s="1" t="n"/>
+      <c r="P465" s="1" t="n"/>
+      <c r="Q465" s="1" t="n"/>
+      <c r="R465" s="1" t="n"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -29969,6 +32123,9 @@
         </is>
       </c>
       <c r="O466" s="1" t="n"/>
+      <c r="P466" s="1" t="n"/>
+      <c r="Q466" s="1" t="n"/>
+      <c r="R466" s="1" t="n"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -30034,6 +32191,9 @@
         </is>
       </c>
       <c r="O467" s="1" t="n"/>
+      <c r="P467" s="1" t="n"/>
+      <c r="Q467" s="1" t="n"/>
+      <c r="R467" s="1" t="n"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -30067,6 +32227,9 @@
         </is>
       </c>
       <c r="O468" s="1" t="n"/>
+      <c r="P468" s="1" t="n"/>
+      <c r="Q468" s="1" t="n"/>
+      <c r="R468" s="1" t="n"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -30136,6 +32299,11 @@
         </is>
       </c>
       <c r="O469" s="1" t="n"/>
+      <c r="P469" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q469" s="1" t="n"/>
+      <c r="R469" s="1" t="n"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -30205,6 +32373,11 @@
         </is>
       </c>
       <c r="O470" s="1" t="n"/>
+      <c r="P470" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q470" s="1" t="n"/>
+      <c r="R470" s="1" t="n"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -30270,6 +32443,11 @@
         </is>
       </c>
       <c r="O471" s="1" t="n"/>
+      <c r="P471" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q471" s="1" t="n"/>
+      <c r="R471" s="1" t="n"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -30339,6 +32517,11 @@
         </is>
       </c>
       <c r="O472" s="1" t="n"/>
+      <c r="P472" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q472" s="1" t="n"/>
+      <c r="R472" s="1" t="n"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -30404,6 +32587,11 @@
         </is>
       </c>
       <c r="O473" s="1" t="n"/>
+      <c r="P473" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q473" s="1" t="n"/>
+      <c r="R473" s="1" t="n"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -30473,6 +32661,11 @@
         </is>
       </c>
       <c r="O474" s="1" t="n"/>
+      <c r="P474" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q474" s="1" t="n"/>
+      <c r="R474" s="1" t="n"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -30538,6 +32731,11 @@
         </is>
       </c>
       <c r="O475" s="1" t="n"/>
+      <c r="P475" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q475" s="1" t="n"/>
+      <c r="R475" s="1" t="n"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -30607,6 +32805,11 @@
         </is>
       </c>
       <c r="O476" s="1" t="n"/>
+      <c r="P476" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q476" s="1" t="n"/>
+      <c r="R476" s="1" t="n"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -30676,6 +32879,11 @@
         </is>
       </c>
       <c r="O477" s="1" t="n"/>
+      <c r="P477" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q477" s="1" t="n"/>
+      <c r="R477" s="1" t="n"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -30741,6 +32949,11 @@
         </is>
       </c>
       <c r="O478" s="1" t="n"/>
+      <c r="P478" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q478" s="1" t="n"/>
+      <c r="R478" s="1" t="n"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -30810,6 +33023,11 @@
         </is>
       </c>
       <c r="O479" s="1" t="n"/>
+      <c r="P479" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q479" s="1" t="n"/>
+      <c r="R479" s="1" t="n"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -30875,6 +33093,11 @@
         </is>
       </c>
       <c r="O480" s="1" t="n"/>
+      <c r="P480" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q480" s="1" t="n"/>
+      <c r="R480" s="1" t="n"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -30940,6 +33163,11 @@
         </is>
       </c>
       <c r="O481" s="1" t="n"/>
+      <c r="P481" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q481" s="1" t="n"/>
+      <c r="R481" s="1" t="n"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -30973,6 +33201,9 @@
         </is>
       </c>
       <c r="O482" s="1" t="n"/>
+      <c r="P482" s="1" t="n"/>
+      <c r="Q482" s="1" t="n"/>
+      <c r="R482" s="1" t="n"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -31006,6 +33237,9 @@
         </is>
       </c>
       <c r="O483" s="1" t="n"/>
+      <c r="P483" s="1" t="n"/>
+      <c r="Q483" s="1" t="n"/>
+      <c r="R483" s="1" t="n"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -31039,6 +33273,9 @@
         </is>
       </c>
       <c r="O484" s="1" t="n"/>
+      <c r="P484" s="1" t="n"/>
+      <c r="Q484" s="1" t="n"/>
+      <c r="R484" s="1" t="n"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -31072,6 +33309,9 @@
         </is>
       </c>
       <c r="O485" s="1" t="n"/>
+      <c r="P485" s="1" t="n"/>
+      <c r="Q485" s="1" t="n"/>
+      <c r="R485" s="1" t="n"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -31137,6 +33377,11 @@
         </is>
       </c>
       <c r="O486" s="1" t="n"/>
+      <c r="P486" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q486" s="1" t="n"/>
+      <c r="R486" s="1" t="n"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -31206,6 +33451,9 @@
         </is>
       </c>
       <c r="O487" s="1" t="n"/>
+      <c r="P487" s="1" t="n"/>
+      <c r="Q487" s="1" t="n"/>
+      <c r="R487" s="1" t="n"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -31269,6 +33517,9 @@
       <c r="O488" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P488" s="1" t="n"/>
+      <c r="Q488" s="1" t="n"/>
+      <c r="R488" s="1" t="n"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -31332,6 +33583,9 @@
       <c r="O489" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P489" s="1" t="n"/>
+      <c r="Q489" s="1" t="n"/>
+      <c r="R489" s="1" t="n"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -31395,6 +33649,9 @@
       <c r="O490" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P490" s="1" t="n"/>
+      <c r="Q490" s="1" t="n"/>
+      <c r="R490" s="1" t="n"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -31462,6 +33719,9 @@
       <c r="O491" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P491" s="1" t="n"/>
+      <c r="Q491" s="1" t="n"/>
+      <c r="R491" s="1" t="n"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -31529,6 +33789,9 @@
       <c r="O492" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P492" s="1" t="n"/>
+      <c r="Q492" s="1" t="n"/>
+      <c r="R492" s="1" t="n"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -31596,6 +33859,9 @@
       <c r="O493" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P493" s="1" t="n"/>
+      <c r="Q493" s="1" t="n"/>
+      <c r="R493" s="1" t="n"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -31665,6 +33931,11 @@
         </is>
       </c>
       <c r="O494" s="1" t="n"/>
+      <c r="P494" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q494" s="1" t="n"/>
+      <c r="R494" s="1" t="n"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -31730,6 +34001,11 @@
         </is>
       </c>
       <c r="O495" s="1" t="n"/>
+      <c r="P495" s="1" t="n"/>
+      <c r="Q495" s="1" t="n"/>
+      <c r="R495" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -31799,6 +34075,11 @@
         </is>
       </c>
       <c r="O496" s="1" t="n"/>
+      <c r="P496" s="1" t="n"/>
+      <c r="Q496" s="1" t="n"/>
+      <c r="R496" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -31868,6 +34149,11 @@
         </is>
       </c>
       <c r="O497" s="1" t="n"/>
+      <c r="P497" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q497" s="1" t="n"/>
+      <c r="R497" s="1" t="n"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -31933,6 +34219,11 @@
         </is>
       </c>
       <c r="O498" s="1" t="n"/>
+      <c r="P498" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q498" s="1" t="n"/>
+      <c r="R498" s="1" t="n"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -32002,6 +34293,11 @@
         </is>
       </c>
       <c r="O499" s="1" t="n"/>
+      <c r="P499" s="1" t="n"/>
+      <c r="Q499" s="1" t="n"/>
+      <c r="R499" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -32067,6 +34363,11 @@
         </is>
       </c>
       <c r="O500" s="1" t="n"/>
+      <c r="P500" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q500" s="1" t="n"/>
+      <c r="R500" s="1" t="n"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -32132,6 +34433,11 @@
         </is>
       </c>
       <c r="O501" s="1" t="n"/>
+      <c r="P501" s="1" t="n"/>
+      <c r="Q501" s="1" t="n"/>
+      <c r="R501" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -32201,6 +34507,11 @@
         </is>
       </c>
       <c r="O502" s="1" t="n"/>
+      <c r="P502" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q502" s="1" t="n"/>
+      <c r="R502" s="1" t="n"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -32266,6 +34577,11 @@
         </is>
       </c>
       <c r="O503" s="1" t="n"/>
+      <c r="P503" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q503" s="1" t="n"/>
+      <c r="R503" s="1" t="n"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -32335,6 +34651,11 @@
         </is>
       </c>
       <c r="O504" s="1" t="n"/>
+      <c r="P504" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q504" s="1" t="n"/>
+      <c r="R504" s="1" t="n"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -32404,6 +34725,11 @@
         </is>
       </c>
       <c r="O505" s="1" t="n"/>
+      <c r="P505" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q505" s="1" t="n"/>
+      <c r="R505" s="1" t="n"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -32469,6 +34795,11 @@
         </is>
       </c>
       <c r="O506" s="1" t="n"/>
+      <c r="P506" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q506" s="1" t="n"/>
+      <c r="R506" s="1" t="n"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -32534,6 +34865,11 @@
         </is>
       </c>
       <c r="O507" s="1" t="n"/>
+      <c r="P507" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q507" s="1" t="n"/>
+      <c r="R507" s="1" t="n"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -32599,6 +34935,11 @@
         </is>
       </c>
       <c r="O508" s="1" t="n"/>
+      <c r="P508" s="1" t="n"/>
+      <c r="Q508" s="1" t="n"/>
+      <c r="R508" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -32668,6 +35009,9 @@
         </is>
       </c>
       <c r="O509" s="1" t="n"/>
+      <c r="P509" s="1" t="n"/>
+      <c r="Q509" s="1" t="n"/>
+      <c r="R509" s="1" t="n"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -32733,6 +35077,11 @@
         </is>
       </c>
       <c r="O510" s="1" t="n"/>
+      <c r="P510" s="1" t="n"/>
+      <c r="Q510" s="1" t="n"/>
+      <c r="R510" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -32802,6 +35151,9 @@
         </is>
       </c>
       <c r="O511" s="1" t="n"/>
+      <c r="P511" s="1" t="n"/>
+      <c r="Q511" s="1" t="n"/>
+      <c r="R511" s="1" t="n"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -32871,6 +35223,11 @@
         </is>
       </c>
       <c r="O512" s="1" t="n"/>
+      <c r="P512" s="1" t="n"/>
+      <c r="Q512" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R512" s="1" t="n"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -32940,6 +35297,11 @@
         </is>
       </c>
       <c r="O513" s="1" t="n"/>
+      <c r="P513" s="1" t="n"/>
+      <c r="Q513" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R513" s="1" t="n"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -33005,6 +35367,11 @@
         </is>
       </c>
       <c r="O514" s="1" t="n"/>
+      <c r="P514" s="1" t="n"/>
+      <c r="Q514" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R514" s="1" t="n"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -33070,6 +35437,11 @@
         </is>
       </c>
       <c r="O515" s="1" t="n"/>
+      <c r="P515" s="1" t="n"/>
+      <c r="Q515" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R515" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/codelists/antipsychotics_raw.xlsx
+++ b/codelists/antipsychotics_raw.xlsx
@@ -21270,7 +21270,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>571141000033114</t>
+          <t>567141000033111</t>
         </is>
       </c>
       <c r="B305" s="1" t="n">
@@ -21279,7 +21279,7 @@
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Fentazin  Tablets  8 mg</t>
+          <t>Fentazin  Injection  5 mg/ml</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -21306,7 +21306,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>567141000033111</t>
+          <t>571141000033114</t>
         </is>
       </c>
       <c r="B306" s="1" t="n">
@@ -21315,7 +21315,7 @@
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Fentazin  Injection  5 mg/ml</t>
+          <t>Fentazin  Tablets  8 mg</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>

--- a/codelists/antipsychotics_raw.xlsx
+++ b/codelists/antipsychotics_raw.xlsx
@@ -410,7 +410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R515"/>
+  <dimension ref="A1:X515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.48" customWidth="1" min="1" max="1"/>
@@ -431,6 +431,12 @@
     <col width="22.08" customWidth="1" min="16" max="16"/>
     <col width="22.08" customWidth="1" min="17" max="17"/>
     <col width="21.16" customWidth="1" min="18" max="18"/>
+    <col width="9.200000000000001" customWidth="1" min="19" max="19"/>
+    <col width="9.200000000000001" customWidth="1" min="20" max="20"/>
+    <col width="9.200000000000001" customWidth="1" min="21" max="21"/>
+    <col width="11.96" customWidth="1" min="22" max="22"/>
+    <col width="18.4" customWidth="1" min="23" max="23"/>
+    <col width="11.96" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,6 +530,36 @@
           <t>oc_opensafely_depotAP</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>injected</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>solution</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>strength_mg</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>strength_mg_per_ml</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ap_strength</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -592,6 +628,16 @@
         <v>1</v>
       </c>
       <c r="R2" s="1" t="n"/>
+      <c r="S2" s="1" t="n"/>
+      <c r="T2" s="1" t="n"/>
+      <c r="U2" s="1" t="n"/>
+      <c r="V2" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W2" s="1" t="n"/>
+      <c r="X2" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -660,6 +706,16 @@
         <v>1</v>
       </c>
       <c r="R3" s="1" t="n"/>
+      <c r="S3" s="1" t="n"/>
+      <c r="T3" s="1" t="n"/>
+      <c r="U3" s="1" t="n"/>
+      <c r="V3" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W3" s="1" t="n"/>
+      <c r="X3" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -728,6 +784,16 @@
         <v>1</v>
       </c>
       <c r="R4" s="1" t="n"/>
+      <c r="S4" s="1" t="n"/>
+      <c r="T4" s="1" t="n"/>
+      <c r="U4" s="1" t="n"/>
+      <c r="V4" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W4" s="1" t="n"/>
+      <c r="X4" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -796,6 +862,16 @@
         <v>1</v>
       </c>
       <c r="R5" s="1" t="n"/>
+      <c r="S5" s="1" t="n"/>
+      <c r="T5" s="1" t="n"/>
+      <c r="U5" s="1" t="n"/>
+      <c r="V5" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W5" s="1" t="n"/>
+      <c r="X5" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -872,6 +948,18 @@
         <v>1</v>
       </c>
       <c r="R6" s="1" t="n"/>
+      <c r="S6" s="1" t="n"/>
+      <c r="T6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="1" t="n"/>
+      <c r="V6" s="1" t="n"/>
+      <c r="W6" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -944,6 +1032,16 @@
         <v>1</v>
       </c>
       <c r="R7" s="1" t="n"/>
+      <c r="S7" s="1" t="n"/>
+      <c r="T7" s="1" t="n"/>
+      <c r="U7" s="1" t="n"/>
+      <c r="V7" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W7" s="1" t="n"/>
+      <c r="X7" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1016,6 +1114,16 @@
         <v>1</v>
       </c>
       <c r="R8" s="1" t="n"/>
+      <c r="S8" s="1" t="n"/>
+      <c r="T8" s="1" t="n"/>
+      <c r="U8" s="1" t="n"/>
+      <c r="V8" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W8" s="1" t="n"/>
+      <c r="X8" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1092,6 +1200,18 @@
         <v>1</v>
       </c>
       <c r="R9" s="1" t="n"/>
+      <c r="S9" s="1" t="n"/>
+      <c r="T9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="1" t="n"/>
+      <c r="V9" s="1" t="n"/>
+      <c r="W9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1168,6 +1288,18 @@
         <v>1</v>
       </c>
       <c r="R10" s="1" t="n"/>
+      <c r="S10" s="1" t="n"/>
+      <c r="T10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" s="1" t="n"/>
+      <c r="V10" s="1" t="n"/>
+      <c r="W10" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1240,6 +1372,16 @@
         <v>1</v>
       </c>
       <c r="R11" s="1" t="n"/>
+      <c r="S11" s="1" t="n"/>
+      <c r="T11" s="1" t="n"/>
+      <c r="U11" s="1" t="n"/>
+      <c r="V11" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W11" s="1" t="n"/>
+      <c r="X11" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1312,6 +1454,18 @@
         <v>1</v>
       </c>
       <c r="R12" s="1" t="n"/>
+      <c r="S12" s="1" t="n"/>
+      <c r="T12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="1" t="n"/>
+      <c r="V12" s="1" t="n"/>
+      <c r="W12" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1384,6 +1538,16 @@
         <v>1</v>
       </c>
       <c r="R13" s="1" t="n"/>
+      <c r="S13" s="1" t="n"/>
+      <c r="T13" s="1" t="n"/>
+      <c r="U13" s="1" t="n"/>
+      <c r="V13" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W13" s="1" t="n"/>
+      <c r="X13" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1452,6 +1616,16 @@
         <v>1</v>
       </c>
       <c r="R14" s="1" t="n"/>
+      <c r="S14" s="1" t="n"/>
+      <c r="T14" s="1" t="n"/>
+      <c r="U14" s="1" t="n"/>
+      <c r="V14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W14" s="1" t="n"/>
+      <c r="X14" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1520,6 +1694,16 @@
         <v>1</v>
       </c>
       <c r="R15" s="1" t="n"/>
+      <c r="S15" s="1" t="n"/>
+      <c r="T15" s="1" t="n"/>
+      <c r="U15" s="1" t="n"/>
+      <c r="V15" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W15" s="1" t="n"/>
+      <c r="X15" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1588,6 +1772,16 @@
         <v>1</v>
       </c>
       <c r="R16" s="1" t="n"/>
+      <c r="S16" s="1" t="n"/>
+      <c r="T16" s="1" t="n"/>
+      <c r="U16" s="1" t="n"/>
+      <c r="V16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W16" s="1" t="n"/>
+      <c r="X16" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1656,6 +1850,16 @@
         <v>1</v>
       </c>
       <c r="R17" s="1" t="n"/>
+      <c r="S17" s="1" t="n"/>
+      <c r="T17" s="1" t="n"/>
+      <c r="U17" s="1" t="n"/>
+      <c r="V17" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="W17" s="1" t="n"/>
+      <c r="X17" s="1" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1724,6 +1928,18 @@
         <v>1</v>
       </c>
       <c r="R18" s="1" t="n"/>
+      <c r="S18" s="1" t="n"/>
+      <c r="T18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="1" t="n"/>
+      <c r="V18" s="1" t="n"/>
+      <c r="W18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1800,6 +2016,16 @@
         <v>1</v>
       </c>
       <c r="R19" s="1" t="n"/>
+      <c r="S19" s="1" t="n"/>
+      <c r="T19" s="1" t="n"/>
+      <c r="U19" s="1" t="n"/>
+      <c r="V19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W19" s="1" t="n"/>
+      <c r="X19" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1876,6 +2102,16 @@
         <v>1</v>
       </c>
       <c r="R20" s="1" t="n"/>
+      <c r="S20" s="1" t="n"/>
+      <c r="T20" s="1" t="n"/>
+      <c r="U20" s="1" t="n"/>
+      <c r="V20" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W20" s="1" t="n"/>
+      <c r="X20" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1952,6 +2188,18 @@
       <c r="R21" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="1" t="n"/>
+      <c r="U21" s="1" t="n"/>
+      <c r="V21" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W21" s="1" t="n"/>
+      <c r="X21" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2024,6 +2272,16 @@
         <v>1</v>
       </c>
       <c r="R22" s="1" t="n"/>
+      <c r="S22" s="1" t="n"/>
+      <c r="T22" s="1" t="n"/>
+      <c r="U22" s="1" t="n"/>
+      <c r="V22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W22" s="1" t="n"/>
+      <c r="X22" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2096,6 +2354,16 @@
         <v>1</v>
       </c>
       <c r="R23" s="1" t="n"/>
+      <c r="S23" s="1" t="n"/>
+      <c r="T23" s="1" t="n"/>
+      <c r="U23" s="1" t="n"/>
+      <c r="V23" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W23" s="1" t="n"/>
+      <c r="X23" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2172,6 +2440,18 @@
       <c r="R24" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" s="1" t="n"/>
+      <c r="U24" s="1" t="n"/>
+      <c r="V24" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W24" s="1" t="n"/>
+      <c r="X24" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2244,6 +2524,16 @@
         <v>1</v>
       </c>
       <c r="R25" s="1" t="n"/>
+      <c r="S25" s="1" t="n"/>
+      <c r="T25" s="1" t="n"/>
+      <c r="U25" s="1" t="n"/>
+      <c r="V25" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W25" s="1" t="n"/>
+      <c r="X25" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2320,6 +2610,18 @@
         <v>1</v>
       </c>
       <c r="R26" s="1" t="n"/>
+      <c r="S26" s="1" t="n"/>
+      <c r="T26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" s="1" t="n"/>
+      <c r="V26" s="1" t="n"/>
+      <c r="W26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2392,6 +2694,18 @@
         <v>1</v>
       </c>
       <c r="R27" s="1" t="n"/>
+      <c r="S27" s="1" t="n"/>
+      <c r="T27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" s="1" t="n"/>
+      <c r="V27" s="1" t="n"/>
+      <c r="W27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2464,6 +2778,16 @@
         <v>1</v>
       </c>
       <c r="R28" s="1" t="n"/>
+      <c r="S28" s="1" t="n"/>
+      <c r="T28" s="1" t="n"/>
+      <c r="U28" s="1" t="n"/>
+      <c r="V28" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="W28" s="1" t="n"/>
+      <c r="X28" s="1" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2536,6 +2860,18 @@
       <c r="R29" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="1" t="n"/>
+      <c r="U29" s="1" t="n"/>
+      <c r="V29" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W29" s="1" t="n"/>
+      <c r="X29" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2608,6 +2944,18 @@
       <c r="R30" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" s="1" t="n"/>
+      <c r="U30" s="1" t="n"/>
+      <c r="V30" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W30" s="1" t="n"/>
+      <c r="X30" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2680,6 +3028,16 @@
         <v>1</v>
       </c>
       <c r="R31" s="1" t="n"/>
+      <c r="S31" s="1" t="n"/>
+      <c r="T31" s="1" t="n"/>
+      <c r="U31" s="1" t="n"/>
+      <c r="V31" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W31" s="1" t="n"/>
+      <c r="X31" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2752,6 +3110,16 @@
         <v>1</v>
       </c>
       <c r="R32" s="1" t="n"/>
+      <c r="S32" s="1" t="n"/>
+      <c r="T32" s="1" t="n"/>
+      <c r="U32" s="1" t="n"/>
+      <c r="V32" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W32" s="1" t="n"/>
+      <c r="X32" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2828,6 +3196,20 @@
         <v>1</v>
       </c>
       <c r="R33" s="1" t="n"/>
+      <c r="S33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" s="1" t="n"/>
+      <c r="V33" s="1" t="n"/>
+      <c r="W33" s="1" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="X33" s="1" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2900,6 +3282,16 @@
         <v>1</v>
       </c>
       <c r="R34" s="1" t="n"/>
+      <c r="S34" s="1" t="n"/>
+      <c r="T34" s="1" t="n"/>
+      <c r="U34" s="1" t="n"/>
+      <c r="V34" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W34" s="1" t="n"/>
+      <c r="X34" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2972,6 +3364,16 @@
         <v>1</v>
       </c>
       <c r="R35" s="1" t="n"/>
+      <c r="S35" s="1" t="n"/>
+      <c r="T35" s="1" t="n"/>
+      <c r="U35" s="1" t="n"/>
+      <c r="V35" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W35" s="1" t="n"/>
+      <c r="X35" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3044,6 +3446,20 @@
         <v>1</v>
       </c>
       <c r="R36" s="1" t="n"/>
+      <c r="S36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" s="1" t="n"/>
+      <c r="V36" s="1" t="n"/>
+      <c r="W36" s="1" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="X36" s="1" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3110,6 +3526,16 @@
       </c>
       <c r="Q37" s="1" t="n"/>
       <c r="R37" s="1" t="n"/>
+      <c r="S37" s="1" t="n"/>
+      <c r="T37" s="1" t="n"/>
+      <c r="U37" s="1" t="n"/>
+      <c r="V37" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="W37" s="1" t="n"/>
+      <c r="X37" s="1" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3180,6 +3606,16 @@
       </c>
       <c r="Q38" s="1" t="n"/>
       <c r="R38" s="1" t="n"/>
+      <c r="S38" s="1" t="n"/>
+      <c r="T38" s="1" t="n"/>
+      <c r="U38" s="1" t="n"/>
+      <c r="V38" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="W38" s="1" t="n"/>
+      <c r="X38" s="1" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3254,6 +3690,16 @@
         <v>1</v>
       </c>
       <c r="R39" s="1" t="n"/>
+      <c r="S39" s="1" t="n"/>
+      <c r="T39" s="1" t="n"/>
+      <c r="U39" s="1" t="n"/>
+      <c r="V39" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="W39" s="1" t="n"/>
+      <c r="X39" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3328,6 +3774,16 @@
         <v>1</v>
       </c>
       <c r="R40" s="1" t="n"/>
+      <c r="S40" s="1" t="n"/>
+      <c r="T40" s="1" t="n"/>
+      <c r="U40" s="1" t="n"/>
+      <c r="V40" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W40" s="1" t="n"/>
+      <c r="X40" s="1" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3402,6 +3858,16 @@
         <v>1</v>
       </c>
       <c r="R41" s="1" t="n"/>
+      <c r="S41" s="1" t="n"/>
+      <c r="T41" s="1" t="n"/>
+      <c r="U41" s="1" t="n"/>
+      <c r="V41" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="W41" s="1" t="n"/>
+      <c r="X41" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3476,6 +3942,16 @@
         <v>1</v>
       </c>
       <c r="R42" s="1" t="n"/>
+      <c r="S42" s="1" t="n"/>
+      <c r="T42" s="1" t="n"/>
+      <c r="U42" s="1" t="n"/>
+      <c r="V42" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W42" s="1" t="n"/>
+      <c r="X42" s="1" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3546,6 +4022,16 @@
         <v>1</v>
       </c>
       <c r="R43" s="1" t="n"/>
+      <c r="S43" s="1" t="n"/>
+      <c r="T43" s="1" t="n"/>
+      <c r="U43" s="1" t="n"/>
+      <c r="V43" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="W43" s="1" t="n"/>
+      <c r="X43" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3612,6 +4098,16 @@
       </c>
       <c r="Q44" s="1" t="n"/>
       <c r="R44" s="1" t="n"/>
+      <c r="S44" s="1" t="n"/>
+      <c r="T44" s="1" t="n"/>
+      <c r="U44" s="1" t="n"/>
+      <c r="V44" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W44" s="1" t="n"/>
+      <c r="X44" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3678,6 +4174,16 @@
       </c>
       <c r="Q45" s="1" t="n"/>
       <c r="R45" s="1" t="n"/>
+      <c r="S45" s="1" t="n"/>
+      <c r="T45" s="1" t="n"/>
+      <c r="U45" s="1" t="n"/>
+      <c r="V45" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W45" s="1" t="n"/>
+      <c r="X45" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3744,6 +4250,16 @@
       </c>
       <c r="Q46" s="1" t="n"/>
       <c r="R46" s="1" t="n"/>
+      <c r="S46" s="1" t="n"/>
+      <c r="T46" s="1" t="n"/>
+      <c r="U46" s="1" t="n"/>
+      <c r="V46" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W46" s="1" t="n"/>
+      <c r="X46" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3810,6 +4326,16 @@
       </c>
       <c r="Q47" s="1" t="n"/>
       <c r="R47" s="1" t="n"/>
+      <c r="S47" s="1" t="n"/>
+      <c r="T47" s="1" t="n"/>
+      <c r="U47" s="1" t="n"/>
+      <c r="V47" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W47" s="1" t="n"/>
+      <c r="X47" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3884,6 +4410,18 @@
       </c>
       <c r="Q48" s="1" t="n"/>
       <c r="R48" s="1" t="n"/>
+      <c r="S48" s="1" t="n"/>
+      <c r="T48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" s="1" t="n"/>
+      <c r="V48" s="1" t="n"/>
+      <c r="W48" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X48" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3954,6 +4492,16 @@
       </c>
       <c r="Q49" s="1" t="n"/>
       <c r="R49" s="1" t="n"/>
+      <c r="S49" s="1" t="n"/>
+      <c r="T49" s="1" t="n"/>
+      <c r="U49" s="1" t="n"/>
+      <c r="V49" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W49" s="1" t="n"/>
+      <c r="X49" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4024,6 +4572,16 @@
       </c>
       <c r="Q50" s="1" t="n"/>
       <c r="R50" s="1" t="n"/>
+      <c r="S50" s="1" t="n"/>
+      <c r="T50" s="1" t="n"/>
+      <c r="U50" s="1" t="n"/>
+      <c r="V50" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W50" s="1" t="n"/>
+      <c r="X50" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4094,6 +4652,16 @@
       </c>
       <c r="Q51" s="1" t="n"/>
       <c r="R51" s="1" t="n"/>
+      <c r="S51" s="1" t="n"/>
+      <c r="T51" s="1" t="n"/>
+      <c r="U51" s="1" t="n"/>
+      <c r="V51" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W51" s="1" t="n"/>
+      <c r="X51" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4168,6 +4736,18 @@
       </c>
       <c r="Q52" s="1" t="n"/>
       <c r="R52" s="1" t="n"/>
+      <c r="S52" s="1" t="n"/>
+      <c r="T52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" s="1" t="n"/>
+      <c r="V52" s="1" t="n"/>
+      <c r="W52" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X52" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4242,6 +4822,18 @@
       </c>
       <c r="Q53" s="1" t="n"/>
       <c r="R53" s="1" t="n"/>
+      <c r="S53" s="1" t="n"/>
+      <c r="T53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" s="1" t="n"/>
+      <c r="V53" s="1" t="n"/>
+      <c r="W53" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X53" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4312,6 +4904,16 @@
       </c>
       <c r="Q54" s="1" t="n"/>
       <c r="R54" s="1" t="n"/>
+      <c r="S54" s="1" t="n"/>
+      <c r="T54" s="1" t="n"/>
+      <c r="U54" s="1" t="n"/>
+      <c r="V54" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W54" s="1" t="n"/>
+      <c r="X54" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4382,6 +4984,18 @@
       </c>
       <c r="Q55" s="1" t="n"/>
       <c r="R55" s="1" t="n"/>
+      <c r="S55" s="1" t="n"/>
+      <c r="T55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" s="1" t="n"/>
+      <c r="V55" s="1" t="n"/>
+      <c r="W55" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X55" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4456,6 +5070,18 @@
       </c>
       <c r="Q56" s="1" t="n"/>
       <c r="R56" s="1" t="n"/>
+      <c r="S56" s="1" t="n"/>
+      <c r="T56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" s="1" t="n"/>
+      <c r="V56" s="1" t="n"/>
+      <c r="W56" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X56" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4526,6 +5152,18 @@
       </c>
       <c r="Q57" s="1" t="n"/>
       <c r="R57" s="1" t="n"/>
+      <c r="S57" s="1" t="n"/>
+      <c r="T57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" s="1" t="n"/>
+      <c r="V57" s="1" t="n"/>
+      <c r="W57" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X57" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4600,6 +5238,18 @@
       </c>
       <c r="Q58" s="1" t="n"/>
       <c r="R58" s="1" t="n"/>
+      <c r="S58" s="1" t="n"/>
+      <c r="T58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" s="1" t="n"/>
+      <c r="V58" s="1" t="n"/>
+      <c r="W58" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X58" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4670,6 +5320,20 @@
       </c>
       <c r="Q59" s="1" t="n"/>
       <c r="R59" s="1" t="n"/>
+      <c r="S59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" s="1" t="n"/>
+      <c r="V59" s="1" t="n"/>
+      <c r="W59" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X59" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4706,6 +5370,20 @@
       <c r="P60" s="1" t="n"/>
       <c r="Q60" s="1" t="n"/>
       <c r="R60" s="1" t="n"/>
+      <c r="S60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" s="1" t="n"/>
+      <c r="V60" s="1" t="n"/>
+      <c r="W60" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X60" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4780,6 +5458,20 @@
       </c>
       <c r="Q61" s="1" t="n"/>
       <c r="R61" s="1" t="n"/>
+      <c r="S61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" s="1" t="n"/>
+      <c r="V61" s="1" t="n"/>
+      <c r="W61" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X61" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4816,6 +5508,16 @@
       <c r="P62" s="1" t="n"/>
       <c r="Q62" s="1" t="n"/>
       <c r="R62" s="1" t="n"/>
+      <c r="S62" s="1" t="n"/>
+      <c r="T62" s="1" t="n"/>
+      <c r="U62" s="1" t="n"/>
+      <c r="V62" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W62" s="1" t="n"/>
+      <c r="X62" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4852,6 +5554,16 @@
       <c r="P63" s="1" t="n"/>
       <c r="Q63" s="1" t="n"/>
       <c r="R63" s="1" t="n"/>
+      <c r="S63" s="1" t="n"/>
+      <c r="T63" s="1" t="n"/>
+      <c r="U63" s="1" t="n"/>
+      <c r="V63" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W63" s="1" t="n"/>
+      <c r="X63" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4888,6 +5600,20 @@
       <c r="P64" s="1" t="n"/>
       <c r="Q64" s="1" t="n"/>
       <c r="R64" s="1" t="n"/>
+      <c r="S64" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" s="1" t="n"/>
+      <c r="V64" s="1" t="n"/>
+      <c r="W64" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X64" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4962,6 +5688,16 @@
       </c>
       <c r="Q65" s="1" t="n"/>
       <c r="R65" s="1" t="n"/>
+      <c r="S65" s="1" t="n"/>
+      <c r="T65" s="1" t="n"/>
+      <c r="U65" s="1" t="n"/>
+      <c r="V65" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W65" s="1" t="n"/>
+      <c r="X65" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5036,6 +5772,20 @@
       </c>
       <c r="Q66" s="1" t="n"/>
       <c r="R66" s="1" t="n"/>
+      <c r="S66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" s="1" t="n"/>
+      <c r="V66" s="1" t="n"/>
+      <c r="W66" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X66" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5072,6 +5822,16 @@
       <c r="P67" s="1" t="n"/>
       <c r="Q67" s="1" t="n"/>
       <c r="R67" s="1" t="n"/>
+      <c r="S67" s="1" t="n"/>
+      <c r="T67" s="1" t="n"/>
+      <c r="U67" s="1" t="n"/>
+      <c r="V67" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W67" s="1" t="n"/>
+      <c r="X67" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5138,6 +5898,16 @@
       </c>
       <c r="Q68" s="1" t="n"/>
       <c r="R68" s="1" t="n"/>
+      <c r="S68" s="1" t="n"/>
+      <c r="T68" s="1" t="n"/>
+      <c r="U68" s="1" t="n"/>
+      <c r="V68" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W68" s="1" t="n"/>
+      <c r="X68" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5204,6 +5974,16 @@
       </c>
       <c r="Q69" s="1" t="n"/>
       <c r="R69" s="1" t="n"/>
+      <c r="S69" s="1" t="n"/>
+      <c r="T69" s="1" t="n"/>
+      <c r="U69" s="1" t="n"/>
+      <c r="V69" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W69" s="1" t="n"/>
+      <c r="X69" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5272,6 +6052,16 @@
         <v>1</v>
       </c>
       <c r="R70" s="1" t="n"/>
+      <c r="S70" s="1" t="n"/>
+      <c r="T70" s="1" t="n"/>
+      <c r="U70" s="1" t="n"/>
+      <c r="V70" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W70" s="1" t="n"/>
+      <c r="X70" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5340,6 +6130,16 @@
         <v>1</v>
       </c>
       <c r="R71" s="1" t="n"/>
+      <c r="S71" s="1" t="n"/>
+      <c r="T71" s="1" t="n"/>
+      <c r="U71" s="1" t="n"/>
+      <c r="V71" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W71" s="1" t="n"/>
+      <c r="X71" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5412,6 +6212,16 @@
         <v>1</v>
       </c>
       <c r="R72" s="1" t="n"/>
+      <c r="S72" s="1" t="n"/>
+      <c r="T72" s="1" t="n"/>
+      <c r="U72" s="1" t="n"/>
+      <c r="V72" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W72" s="1" t="n"/>
+      <c r="X72" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5488,6 +6298,16 @@
         <v>1</v>
       </c>
       <c r="R73" s="1" t="n"/>
+      <c r="S73" s="1" t="n"/>
+      <c r="T73" s="1" t="n"/>
+      <c r="U73" s="1" t="n"/>
+      <c r="V73" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W73" s="1" t="n"/>
+      <c r="X73" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5556,6 +6376,16 @@
         <v>1</v>
       </c>
       <c r="R74" s="1" t="n"/>
+      <c r="S74" s="1" t="n"/>
+      <c r="T74" s="1" t="n"/>
+      <c r="U74" s="1" t="n"/>
+      <c r="V74" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W74" s="1" t="n"/>
+      <c r="X74" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5628,6 +6458,16 @@
         <v>1</v>
       </c>
       <c r="R75" s="1" t="n"/>
+      <c r="S75" s="1" t="n"/>
+      <c r="T75" s="1" t="n"/>
+      <c r="U75" s="1" t="n"/>
+      <c r="V75" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W75" s="1" t="n"/>
+      <c r="X75" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5700,6 +6540,16 @@
         <v>1</v>
       </c>
       <c r="R76" s="1" t="n"/>
+      <c r="S76" s="1" t="n"/>
+      <c r="T76" s="1" t="n"/>
+      <c r="U76" s="1" t="n"/>
+      <c r="V76" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W76" s="1" t="n"/>
+      <c r="X76" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5772,6 +6622,16 @@
         <v>1</v>
       </c>
       <c r="R77" s="1" t="n"/>
+      <c r="S77" s="1" t="n"/>
+      <c r="T77" s="1" t="n"/>
+      <c r="U77" s="1" t="n"/>
+      <c r="V77" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W77" s="1" t="n"/>
+      <c r="X77" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5848,6 +6708,18 @@
         <v>1</v>
       </c>
       <c r="R78" s="1" t="n"/>
+      <c r="S78" s="1" t="n"/>
+      <c r="T78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" s="1" t="n"/>
+      <c r="V78" s="1" t="n"/>
+      <c r="W78" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X78" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5920,6 +6792,16 @@
         <v>1</v>
       </c>
       <c r="R79" s="1" t="n"/>
+      <c r="S79" s="1" t="n"/>
+      <c r="T79" s="1" t="n"/>
+      <c r="U79" s="1" t="n"/>
+      <c r="V79" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W79" s="1" t="n"/>
+      <c r="X79" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5992,6 +6874,16 @@
         <v>1</v>
       </c>
       <c r="R80" s="1" t="n"/>
+      <c r="S80" s="1" t="n"/>
+      <c r="T80" s="1" t="n"/>
+      <c r="U80" s="1" t="n"/>
+      <c r="V80" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W80" s="1" t="n"/>
+      <c r="X80" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6068,6 +6960,16 @@
         <v>1</v>
       </c>
       <c r="R81" s="1" t="n"/>
+      <c r="S81" s="1" t="n"/>
+      <c r="T81" s="1" t="n"/>
+      <c r="U81" s="1" t="n"/>
+      <c r="V81" s="1" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="W81" s="1" t="n"/>
+      <c r="X81" s="1" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6144,6 +7046,16 @@
         <v>1</v>
       </c>
       <c r="R82" s="1" t="n"/>
+      <c r="S82" s="1" t="n"/>
+      <c r="T82" s="1" t="n"/>
+      <c r="U82" s="1" t="n"/>
+      <c r="V82" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W82" s="1" t="n"/>
+      <c r="X82" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6216,6 +7128,16 @@
         <v>1</v>
       </c>
       <c r="R83" s="1" t="n"/>
+      <c r="S83" s="1" t="n"/>
+      <c r="T83" s="1" t="n"/>
+      <c r="U83" s="1" t="n"/>
+      <c r="V83" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W83" s="1" t="n"/>
+      <c r="X83" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6292,6 +7214,16 @@
         <v>1</v>
       </c>
       <c r="R84" s="1" t="n"/>
+      <c r="S84" s="1" t="n"/>
+      <c r="T84" s="1" t="n"/>
+      <c r="U84" s="1" t="n"/>
+      <c r="V84" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W84" s="1" t="n"/>
+      <c r="X84" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6364,6 +7296,18 @@
         <v>1</v>
       </c>
       <c r="R85" s="1" t="n"/>
+      <c r="S85" s="1" t="n"/>
+      <c r="T85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" s="1" t="n"/>
+      <c r="V85" s="1" t="n"/>
+      <c r="W85" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X85" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6436,6 +7380,16 @@
         <v>1</v>
       </c>
       <c r="R86" s="1" t="n"/>
+      <c r="S86" s="1" t="n"/>
+      <c r="T86" s="1" t="n"/>
+      <c r="U86" s="1" t="n"/>
+      <c r="V86" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W86" s="1" t="n"/>
+      <c r="X86" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6512,6 +7466,16 @@
         <v>1</v>
       </c>
       <c r="R87" s="1" t="n"/>
+      <c r="S87" s="1" t="n"/>
+      <c r="T87" s="1" t="n"/>
+      <c r="U87" s="1" t="n"/>
+      <c r="V87" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W87" s="1" t="n"/>
+      <c r="X87" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6588,6 +7552,16 @@
         <v>1</v>
       </c>
       <c r="R88" s="1" t="n"/>
+      <c r="S88" s="1" t="n"/>
+      <c r="T88" s="1" t="n"/>
+      <c r="U88" s="1" t="n"/>
+      <c r="V88" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W88" s="1" t="n"/>
+      <c r="X88" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6660,6 +7634,16 @@
         <v>1</v>
       </c>
       <c r="R89" s="1" t="n"/>
+      <c r="S89" s="1" t="n"/>
+      <c r="T89" s="1" t="n"/>
+      <c r="U89" s="1" t="n"/>
+      <c r="V89" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W89" s="1" t="n"/>
+      <c r="X89" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6732,6 +7716,16 @@
         <v>1</v>
       </c>
       <c r="R90" s="1" t="n"/>
+      <c r="S90" s="1" t="n"/>
+      <c r="T90" s="1" t="n"/>
+      <c r="U90" s="1" t="n"/>
+      <c r="V90" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W90" s="1" t="n"/>
+      <c r="X90" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6768,6 +7762,16 @@
       <c r="P91" s="1" t="n"/>
       <c r="Q91" s="1" t="n"/>
       <c r="R91" s="1" t="n"/>
+      <c r="S91" s="1" t="n"/>
+      <c r="T91" s="1" t="n"/>
+      <c r="U91" s="1" t="n"/>
+      <c r="V91" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W91" s="1" t="n"/>
+      <c r="X91" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6804,6 +7808,18 @@
       <c r="P92" s="1" t="n"/>
       <c r="Q92" s="1" t="n"/>
       <c r="R92" s="1" t="n"/>
+      <c r="S92" s="1" t="n"/>
+      <c r="T92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" s="1" t="n"/>
+      <c r="V92" s="1" t="n"/>
+      <c r="W92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X92" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6840,6 +7856,20 @@
       <c r="P93" s="1" t="n"/>
       <c r="Q93" s="1" t="n"/>
       <c r="R93" s="1" t="n"/>
+      <c r="S93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" s="1" t="n"/>
+      <c r="V93" s="1" t="n"/>
+      <c r="W93" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X93" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6904,6 +7934,20 @@
       <c r="P94" s="1" t="n"/>
       <c r="Q94" s="1" t="n"/>
       <c r="R94" s="1" t="n"/>
+      <c r="S94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" s="1" t="n"/>
+      <c r="V94" s="1" t="n"/>
+      <c r="W94" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X94" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6978,6 +8022,16 @@
       </c>
       <c r="Q95" s="1" t="n"/>
       <c r="R95" s="1" t="n"/>
+      <c r="S95" s="1" t="n"/>
+      <c r="T95" s="1" t="n"/>
+      <c r="U95" s="1" t="n"/>
+      <c r="V95" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="W95" s="1" t="n"/>
+      <c r="X95" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7052,6 +8106,16 @@
       </c>
       <c r="Q96" s="1" t="n"/>
       <c r="R96" s="1" t="n"/>
+      <c r="S96" s="1" t="n"/>
+      <c r="T96" s="1" t="n"/>
+      <c r="U96" s="1" t="n"/>
+      <c r="V96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W96" s="1" t="n"/>
+      <c r="X96" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7122,6 +8186,16 @@
       </c>
       <c r="Q97" s="1" t="n"/>
       <c r="R97" s="1" t="n"/>
+      <c r="S97" s="1" t="n"/>
+      <c r="T97" s="1" t="n"/>
+      <c r="U97" s="1" t="n"/>
+      <c r="V97" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="W97" s="1" t="n"/>
+      <c r="X97" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7192,6 +8266,20 @@
       <c r="R98" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" s="1" t="n"/>
+      <c r="V98" s="1" t="n"/>
+      <c r="W98" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X98" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7262,6 +8350,20 @@
       <c r="R99" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" s="1" t="n"/>
+      <c r="V99" s="1" t="n"/>
+      <c r="W99" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X99" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7332,6 +8434,20 @@
       <c r="R100" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U100" s="1" t="n"/>
+      <c r="V100" s="1" t="n"/>
+      <c r="W100" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X100" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7406,6 +8522,16 @@
       </c>
       <c r="Q101" s="1" t="n"/>
       <c r="R101" s="1" t="n"/>
+      <c r="S101" s="1" t="n"/>
+      <c r="T101" s="1" t="n"/>
+      <c r="U101" s="1" t="n"/>
+      <c r="V101" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="W101" s="1" t="n"/>
+      <c r="X101" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7476,6 +8602,16 @@
       </c>
       <c r="Q102" s="1" t="n"/>
       <c r="R102" s="1" t="n"/>
+      <c r="S102" s="1" t="n"/>
+      <c r="T102" s="1" t="n"/>
+      <c r="U102" s="1" t="n"/>
+      <c r="V102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W102" s="1" t="n"/>
+      <c r="X102" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7550,6 +8686,20 @@
       <c r="R103" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U103" s="1" t="n"/>
+      <c r="V103" s="1" t="n"/>
+      <c r="W103" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X103" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7624,6 +8774,20 @@
       <c r="R104" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" s="1" t="n"/>
+      <c r="V104" s="1" t="n"/>
+      <c r="W104" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X104" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7698,6 +8862,20 @@
       <c r="R105" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U105" s="1" t="n"/>
+      <c r="V105" s="1" t="n"/>
+      <c r="W105" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X105" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7768,6 +8946,16 @@
       </c>
       <c r="Q106" s="1" t="n"/>
       <c r="R106" s="1" t="n"/>
+      <c r="S106" s="1" t="n"/>
+      <c r="T106" s="1" t="n"/>
+      <c r="U106" s="1" t="n"/>
+      <c r="V106" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="W106" s="1" t="n"/>
+      <c r="X106" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7838,6 +9026,20 @@
       <c r="R107" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U107" s="1" t="n"/>
+      <c r="V107" s="1" t="n"/>
+      <c r="W107" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X107" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7912,6 +9114,20 @@
       <c r="R108" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" s="1" t="n"/>
+      <c r="V108" s="1" t="n"/>
+      <c r="W108" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X108" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7982,6 +9198,20 @@
       <c r="R109" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" s="1" t="n"/>
+      <c r="V109" s="1" t="n"/>
+      <c r="W109" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X109" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8055,6 +9285,20 @@
       <c r="Q110" s="1" t="n"/>
       <c r="R110" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="S110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U110" s="1" t="n"/>
+      <c r="V110" s="1" t="n"/>
+      <c r="W110" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X110" s="1" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="111">
@@ -8092,6 +9336,20 @@
       <c r="P111" s="1" t="n"/>
       <c r="Q111" s="1" t="n"/>
       <c r="R111" s="1" t="n"/>
+      <c r="S111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U111" s="1" t="n"/>
+      <c r="V111" s="1" t="n"/>
+      <c r="W111" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X111" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8128,6 +9386,20 @@
       <c r="P112" s="1" t="n"/>
       <c r="Q112" s="1" t="n"/>
       <c r="R112" s="1" t="n"/>
+      <c r="S112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U112" s="1" t="n"/>
+      <c r="V112" s="1" t="n"/>
+      <c r="W112" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X112" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8164,6 +9436,20 @@
       <c r="P113" s="1" t="n"/>
       <c r="Q113" s="1" t="n"/>
       <c r="R113" s="1" t="n"/>
+      <c r="S113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U113" s="1" t="n"/>
+      <c r="V113" s="1" t="n"/>
+      <c r="W113" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X113" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8200,6 +9486,20 @@
       <c r="P114" s="1" t="n"/>
       <c r="Q114" s="1" t="n"/>
       <c r="R114" s="1" t="n"/>
+      <c r="S114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U114" s="1" t="n"/>
+      <c r="V114" s="1" t="n"/>
+      <c r="W114" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X114" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8270,6 +9570,20 @@
       <c r="R115" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" s="1" t="n"/>
+      <c r="V115" s="1" t="n"/>
+      <c r="W115" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X115" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8340,6 +9654,20 @@
       <c r="R116" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S116" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" s="1" t="n"/>
+      <c r="V116" s="1" t="n"/>
+      <c r="W116" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X116" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8410,6 +9738,20 @@
       <c r="R117" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U117" s="1" t="n"/>
+      <c r="V117" s="1" t="n"/>
+      <c r="W117" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X117" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8484,6 +9826,20 @@
       <c r="R118" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U118" s="1" t="n"/>
+      <c r="V118" s="1" t="n"/>
+      <c r="W118" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X118" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8548,6 +9904,16 @@
       <c r="P119" s="1" t="n"/>
       <c r="Q119" s="1" t="n"/>
       <c r="R119" s="1" t="n"/>
+      <c r="S119" s="1" t="n"/>
+      <c r="T119" s="1" t="n"/>
+      <c r="U119" s="1" t="n"/>
+      <c r="V119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W119" s="1" t="n"/>
+      <c r="X119" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8622,6 +9988,20 @@
       <c r="R120" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S120" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U120" s="1" t="n"/>
+      <c r="V120" s="1" t="n"/>
+      <c r="W120" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X120" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8692,6 +10072,20 @@
       <c r="R121" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S121" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T121" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" s="1" t="n"/>
+      <c r="V121" s="1" t="n"/>
+      <c r="W121" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X121" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8762,6 +10156,20 @@
       <c r="R122" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S122" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T122" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U122" s="1" t="n"/>
+      <c r="V122" s="1" t="n"/>
+      <c r="W122" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X122" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8832,6 +10240,20 @@
       <c r="R123" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S123" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T123" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U123" s="1" t="n"/>
+      <c r="V123" s="1" t="n"/>
+      <c r="W123" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X123" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8906,6 +10328,20 @@
       <c r="R124" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U124" s="1" t="n"/>
+      <c r="V124" s="1" t="n"/>
+      <c r="W124" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X124" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8974,6 +10410,16 @@
       <c r="P125" s="1" t="n"/>
       <c r="Q125" s="1" t="n"/>
       <c r="R125" s="1" t="n"/>
+      <c r="S125" s="1" t="n"/>
+      <c r="T125" s="1" t="n"/>
+      <c r="U125" s="1" t="n"/>
+      <c r="V125" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W125" s="1" t="n"/>
+      <c r="X125" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9048,6 +10494,20 @@
       <c r="R126" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S126" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T126" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U126" s="1" t="n"/>
+      <c r="V126" s="1" t="n"/>
+      <c r="W126" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X126" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9118,6 +10578,20 @@
       <c r="R127" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U127" s="1" t="n"/>
+      <c r="V127" s="1" t="n"/>
+      <c r="W127" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X127" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9192,6 +10666,20 @@
       <c r="R128" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S128" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T128" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" s="1" t="n"/>
+      <c r="V128" s="1" t="n"/>
+      <c r="W128" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X128" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9256,6 +10744,16 @@
       <c r="P129" s="1" t="n"/>
       <c r="Q129" s="1" t="n"/>
       <c r="R129" s="1" t="n"/>
+      <c r="S129" s="1" t="n"/>
+      <c r="T129" s="1" t="n"/>
+      <c r="U129" s="1" t="n"/>
+      <c r="V129" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W129" s="1" t="n"/>
+      <c r="X129" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9320,6 +10818,16 @@
       <c r="P130" s="1" t="n"/>
       <c r="Q130" s="1" t="n"/>
       <c r="R130" s="1" t="n"/>
+      <c r="S130" s="1" t="n"/>
+      <c r="T130" s="1" t="n"/>
+      <c r="U130" s="1" t="n"/>
+      <c r="V130" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W130" s="1" t="n"/>
+      <c r="X130" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9390,6 +10898,20 @@
       <c r="R131" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U131" s="1" t="n"/>
+      <c r="V131" s="1" t="n"/>
+      <c r="W131" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X131" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9458,6 +10980,16 @@
       <c r="P132" s="1" t="n"/>
       <c r="Q132" s="1" t="n"/>
       <c r="R132" s="1" t="n"/>
+      <c r="S132" s="1" t="n"/>
+      <c r="T132" s="1" t="n"/>
+      <c r="U132" s="1" t="n"/>
+      <c r="V132" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W132" s="1" t="n"/>
+      <c r="X132" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9532,6 +11064,20 @@
       <c r="R133" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U133" s="1" t="n"/>
+      <c r="V133" s="1" t="n"/>
+      <c r="W133" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X133" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9600,6 +11146,16 @@
       <c r="P134" s="1" t="n"/>
       <c r="Q134" s="1" t="n"/>
       <c r="R134" s="1" t="n"/>
+      <c r="S134" s="1" t="n"/>
+      <c r="T134" s="1" t="n"/>
+      <c r="U134" s="1" t="n"/>
+      <c r="V134" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W134" s="1" t="n"/>
+      <c r="X134" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9673,6 +11229,20 @@
       <c r="Q135" s="1" t="n"/>
       <c r="R135" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="S135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U135" s="1" t="n"/>
+      <c r="V135" s="1" t="n"/>
+      <c r="W135" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X135" s="1" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="136">
@@ -9710,6 +11280,20 @@
       <c r="P136" s="1" t="n"/>
       <c r="Q136" s="1" t="n"/>
       <c r="R136" s="1" t="n"/>
+      <c r="S136" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T136" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U136" s="1" t="n"/>
+      <c r="V136" s="1" t="n"/>
+      <c r="W136" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X136" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9746,6 +11330,20 @@
       <c r="P137" s="1" t="n"/>
       <c r="Q137" s="1" t="n"/>
       <c r="R137" s="1" t="n"/>
+      <c r="S137" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T137" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U137" s="1" t="n"/>
+      <c r="V137" s="1" t="n"/>
+      <c r="W137" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X137" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9816,6 +11414,20 @@
       <c r="R138" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S138" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T138" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U138" s="1" t="n"/>
+      <c r="V138" s="1" t="n"/>
+      <c r="W138" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X138" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9890,6 +11502,20 @@
       <c r="R139" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S139" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T139" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U139" s="1" t="n"/>
+      <c r="V139" s="1" t="n"/>
+      <c r="W139" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X139" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9954,6 +11580,20 @@
       <c r="P140" s="1" t="n"/>
       <c r="Q140" s="1" t="n"/>
       <c r="R140" s="1" t="n"/>
+      <c r="S140" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T140" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U140" s="1" t="n"/>
+      <c r="V140" s="1" t="n"/>
+      <c r="W140" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X140" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10018,6 +11658,20 @@
       <c r="P141" s="1" t="n"/>
       <c r="Q141" s="1" t="n"/>
       <c r="R141" s="1" t="n"/>
+      <c r="S141" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T141" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U141" s="1" t="n"/>
+      <c r="V141" s="1" t="n"/>
+      <c r="W141" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X141" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10084,6 +11738,16 @@
       </c>
       <c r="Q142" s="1" t="n"/>
       <c r="R142" s="1" t="n"/>
+      <c r="S142" s="1" t="n"/>
+      <c r="T142" s="1" t="n"/>
+      <c r="U142" s="1" t="n"/>
+      <c r="V142" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="W142" s="1" t="n"/>
+      <c r="X142" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10150,6 +11814,16 @@
       </c>
       <c r="Q143" s="1" t="n"/>
       <c r="R143" s="1" t="n"/>
+      <c r="S143" s="1" t="n"/>
+      <c r="T143" s="1" t="n"/>
+      <c r="U143" s="1" t="n"/>
+      <c r="V143" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W143" s="1" t="n"/>
+      <c r="X143" s="1" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10216,6 +11890,16 @@
       </c>
       <c r="Q144" s="1" t="n"/>
       <c r="R144" s="1" t="n"/>
+      <c r="S144" s="1" t="n"/>
+      <c r="T144" s="1" t="n"/>
+      <c r="U144" s="1" t="n"/>
+      <c r="V144" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W144" s="1" t="n"/>
+      <c r="X144" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10282,6 +11966,16 @@
       </c>
       <c r="Q145" s="1" t="n"/>
       <c r="R145" s="1" t="n"/>
+      <c r="S145" s="1" t="n"/>
+      <c r="T145" s="1" t="n"/>
+      <c r="U145" s="1" t="n"/>
+      <c r="V145" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W145" s="1" t="n"/>
+      <c r="X145" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10348,6 +12042,16 @@
       </c>
       <c r="Q146" s="1" t="n"/>
       <c r="R146" s="1" t="n"/>
+      <c r="S146" s="1" t="n"/>
+      <c r="T146" s="1" t="n"/>
+      <c r="U146" s="1" t="n"/>
+      <c r="V146" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="W146" s="1" t="n"/>
+      <c r="X146" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10422,6 +12126,20 @@
       </c>
       <c r="Q147" s="1" t="n"/>
       <c r="R147" s="1" t="n"/>
+      <c r="S147" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T147" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U147" s="1" t="n"/>
+      <c r="V147" s="1" t="n"/>
+      <c r="W147" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X147" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10488,6 +12206,18 @@
       </c>
       <c r="Q148" s="1" t="n"/>
       <c r="R148" s="1" t="n"/>
+      <c r="S148" s="1" t="n"/>
+      <c r="T148" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U148" s="1" t="n"/>
+      <c r="V148" s="1" t="n"/>
+      <c r="W148" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X148" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10554,6 +12284,18 @@
       </c>
       <c r="Q149" s="1" t="n"/>
       <c r="R149" s="1" t="n"/>
+      <c r="S149" s="1" t="n"/>
+      <c r="T149" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U149" s="1" t="n"/>
+      <c r="V149" s="1" t="n"/>
+      <c r="W149" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="X149" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10590,6 +12332,20 @@
       <c r="P150" s="1" t="n"/>
       <c r="Q150" s="1" t="n"/>
       <c r="R150" s="1" t="n"/>
+      <c r="S150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U150" s="1" t="n"/>
+      <c r="V150" s="1" t="n"/>
+      <c r="W150" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X150" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10664,6 +12420,20 @@
       <c r="R151" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S151" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T151" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U151" s="1" t="n"/>
+      <c r="V151" s="1" t="n"/>
+      <c r="W151" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X151" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10734,6 +12504,20 @@
       <c r="R152" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S152" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T152" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U152" s="1" t="n"/>
+      <c r="V152" s="1" t="n"/>
+      <c r="W152" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X152" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10804,6 +12588,16 @@
       </c>
       <c r="Q153" s="1" t="n"/>
       <c r="R153" s="1" t="n"/>
+      <c r="S153" s="1" t="n"/>
+      <c r="T153" s="1" t="n"/>
+      <c r="U153" s="1" t="n"/>
+      <c r="V153" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="W153" s="1" t="n"/>
+      <c r="X153" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10878,6 +12672,18 @@
       </c>
       <c r="Q154" s="1" t="n"/>
       <c r="R154" s="1" t="n"/>
+      <c r="S154" s="1" t="n"/>
+      <c r="T154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U154" s="1" t="n"/>
+      <c r="V154" s="1" t="n"/>
+      <c r="W154" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X154" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10944,6 +12750,16 @@
       </c>
       <c r="Q155" s="1" t="n"/>
       <c r="R155" s="1" t="n"/>
+      <c r="S155" s="1" t="n"/>
+      <c r="T155" s="1" t="n"/>
+      <c r="U155" s="1" t="n"/>
+      <c r="V155" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W155" s="1" t="n"/>
+      <c r="X155" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11018,6 +12834,20 @@
       <c r="R156" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S156" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T156" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U156" s="1" t="n"/>
+      <c r="V156" s="1" t="n"/>
+      <c r="W156" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X156" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11087,6 +12917,20 @@
       <c r="Q157" s="1" t="n"/>
       <c r="R157" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="S157" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T157" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U157" s="1" t="n"/>
+      <c r="V157" s="1" t="n"/>
+      <c r="W157" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X157" s="1" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="158">
@@ -11124,6 +12968,18 @@
       <c r="P158" s="1" t="n"/>
       <c r="Q158" s="1" t="n"/>
       <c r="R158" s="1" t="n"/>
+      <c r="S158" s="1" t="n"/>
+      <c r="T158" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U158" s="1" t="n"/>
+      <c r="V158" s="1" t="n"/>
+      <c r="W158" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="X158" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11194,6 +13050,16 @@
       </c>
       <c r="Q159" s="1" t="n"/>
       <c r="R159" s="1" t="n"/>
+      <c r="S159" s="1" t="n"/>
+      <c r="T159" s="1" t="n"/>
+      <c r="U159" s="1" t="n"/>
+      <c r="V159" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W159" s="1" t="n"/>
+      <c r="X159" s="1" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11264,6 +13130,16 @@
       </c>
       <c r="Q160" s="1" t="n"/>
       <c r="R160" s="1" t="n"/>
+      <c r="S160" s="1" t="n"/>
+      <c r="T160" s="1" t="n"/>
+      <c r="U160" s="1" t="n"/>
+      <c r="V160" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W160" s="1" t="n"/>
+      <c r="X160" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11334,6 +13210,18 @@
       </c>
       <c r="Q161" s="1" t="n"/>
       <c r="R161" s="1" t="n"/>
+      <c r="S161" s="1" t="n"/>
+      <c r="T161" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U161" s="1" t="n"/>
+      <c r="V161" s="1" t="n"/>
+      <c r="W161" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="X161" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11404,6 +13292,16 @@
       </c>
       <c r="Q162" s="1" t="n"/>
       <c r="R162" s="1" t="n"/>
+      <c r="S162" s="1" t="n"/>
+      <c r="T162" s="1" t="n"/>
+      <c r="U162" s="1" t="n"/>
+      <c r="V162" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W162" s="1" t="n"/>
+      <c r="X162" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11478,6 +13376,18 @@
       </c>
       <c r="Q163" s="1" t="n"/>
       <c r="R163" s="1" t="n"/>
+      <c r="S163" s="1" t="n"/>
+      <c r="T163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U163" s="1" t="n"/>
+      <c r="V163" s="1" t="n"/>
+      <c r="W163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X163" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11548,6 +13458,18 @@
       </c>
       <c r="Q164" s="1" t="n"/>
       <c r="R164" s="1" t="n"/>
+      <c r="S164" s="1" t="n"/>
+      <c r="T164" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U164" s="1" t="n"/>
+      <c r="V164" s="1" t="n"/>
+      <c r="W164" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="X164" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11622,6 +13544,18 @@
       </c>
       <c r="Q165" s="1" t="n"/>
       <c r="R165" s="1" t="n"/>
+      <c r="S165" s="1" t="n"/>
+      <c r="T165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U165" s="1" t="n"/>
+      <c r="V165" s="1" t="n"/>
+      <c r="W165" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X165" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11658,6 +13592,18 @@
       <c r="P166" s="1" t="n"/>
       <c r="Q166" s="1" t="n"/>
       <c r="R166" s="1" t="n"/>
+      <c r="S166" s="1" t="n"/>
+      <c r="T166" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U166" s="1" t="n"/>
+      <c r="V166" s="1" t="n"/>
+      <c r="W166" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X166" s="1" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11728,6 +13674,16 @@
       </c>
       <c r="Q167" s="1" t="n"/>
       <c r="R167" s="1" t="n"/>
+      <c r="S167" s="1" t="n"/>
+      <c r="T167" s="1" t="n"/>
+      <c r="U167" s="1" t="n"/>
+      <c r="V167" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W167" s="1" t="n"/>
+      <c r="X167" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11802,6 +13758,20 @@
       </c>
       <c r="Q168" s="1" t="n"/>
       <c r="R168" s="1" t="n"/>
+      <c r="S168" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T168" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U168" s="1" t="n"/>
+      <c r="V168" s="1" t="n"/>
+      <c r="W168" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X168" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11872,6 +13842,16 @@
       </c>
       <c r="Q169" s="1" t="n"/>
       <c r="R169" s="1" t="n"/>
+      <c r="S169" s="1" t="n"/>
+      <c r="T169" s="1" t="n"/>
+      <c r="U169" s="1" t="n"/>
+      <c r="V169" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W169" s="1" t="n"/>
+      <c r="X169" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11942,6 +13922,20 @@
       </c>
       <c r="Q170" s="1" t="n"/>
       <c r="R170" s="1" t="n"/>
+      <c r="S170" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T170" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U170" s="1" t="n"/>
+      <c r="V170" s="1" t="n"/>
+      <c r="W170" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X170" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12012,6 +14006,18 @@
       </c>
       <c r="Q171" s="1" t="n"/>
       <c r="R171" s="1" t="n"/>
+      <c r="S171" s="1" t="n"/>
+      <c r="T171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U171" s="1" t="n"/>
+      <c r="V171" s="1" t="n"/>
+      <c r="W171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X171" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -12048,6 +14054,20 @@
       <c r="P172" s="1" t="n"/>
       <c r="Q172" s="1" t="n"/>
       <c r="R172" s="1" t="n"/>
+      <c r="S172" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T172" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U172" s="1" t="n"/>
+      <c r="V172" s="1" t="n"/>
+      <c r="W172" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X172" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12084,6 +14104,18 @@
       <c r="P173" s="1" t="n"/>
       <c r="Q173" s="1" t="n"/>
       <c r="R173" s="1" t="n"/>
+      <c r="S173" s="1" t="n"/>
+      <c r="T173" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U173" s="1" t="n"/>
+      <c r="V173" s="1" t="n"/>
+      <c r="W173" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X173" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12154,6 +14186,20 @@
       </c>
       <c r="Q174" s="1" t="n"/>
       <c r="R174" s="1" t="n"/>
+      <c r="S174" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T174" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U174" s="1" t="n"/>
+      <c r="V174" s="1" t="n"/>
+      <c r="W174" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X174" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12228,6 +14274,18 @@
       </c>
       <c r="Q175" s="1" t="n"/>
       <c r="R175" s="1" t="n"/>
+      <c r="S175" s="1" t="n"/>
+      <c r="T175" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U175" s="1" t="n"/>
+      <c r="V175" s="1" t="n"/>
+      <c r="W175" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X175" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12298,6 +14356,16 @@
       </c>
       <c r="Q176" s="1" t="n"/>
       <c r="R176" s="1" t="n"/>
+      <c r="S176" s="1" t="n"/>
+      <c r="T176" s="1" t="n"/>
+      <c r="U176" s="1" t="n"/>
+      <c r="V176" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W176" s="1" t="n"/>
+      <c r="X176" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12334,6 +14402,18 @@
       <c r="P177" s="1" t="n"/>
       <c r="Q177" s="1" t="n"/>
       <c r="R177" s="1" t="n"/>
+      <c r="S177" s="1" t="n"/>
+      <c r="T177" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U177" s="1" t="n"/>
+      <c r="V177" s="1" t="n"/>
+      <c r="W177" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X177" s="1" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12408,6 +14488,18 @@
       </c>
       <c r="Q178" s="1" t="n"/>
       <c r="R178" s="1" t="n"/>
+      <c r="S178" s="1" t="n"/>
+      <c r="T178" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U178" s="1" t="n"/>
+      <c r="V178" s="1" t="n"/>
+      <c r="W178" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X178" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12482,6 +14574,18 @@
       </c>
       <c r="Q179" s="1" t="n"/>
       <c r="R179" s="1" t="n"/>
+      <c r="S179" s="1" t="n"/>
+      <c r="T179" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U179" s="1" t="n"/>
+      <c r="V179" s="1" t="n"/>
+      <c r="W179" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X179" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12556,6 +14660,18 @@
       </c>
       <c r="Q180" s="1" t="n"/>
       <c r="R180" s="1" t="n"/>
+      <c r="S180" s="1" t="n"/>
+      <c r="T180" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U180" s="1" t="n"/>
+      <c r="V180" s="1" t="n"/>
+      <c r="W180" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X180" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12630,6 +14746,18 @@
       </c>
       <c r="Q181" s="1" t="n"/>
       <c r="R181" s="1" t="n"/>
+      <c r="S181" s="1" t="n"/>
+      <c r="T181" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U181" s="1" t="n"/>
+      <c r="V181" s="1" t="n"/>
+      <c r="W181" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="X181" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12700,6 +14828,20 @@
       </c>
       <c r="Q182" s="1" t="n"/>
       <c r="R182" s="1" t="n"/>
+      <c r="S182" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T182" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U182" s="1" t="n"/>
+      <c r="V182" s="1" t="n"/>
+      <c r="W182" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X182" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12774,6 +14916,18 @@
       </c>
       <c r="Q183" s="1" t="n"/>
       <c r="R183" s="1" t="n"/>
+      <c r="S183" s="1" t="n"/>
+      <c r="T183" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U183" s="1" t="n"/>
+      <c r="V183" s="1" t="n"/>
+      <c r="W183" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X183" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12848,6 +15002,18 @@
       </c>
       <c r="Q184" s="1" t="n"/>
       <c r="R184" s="1" t="n"/>
+      <c r="S184" s="1" t="n"/>
+      <c r="T184" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U184" s="1" t="n"/>
+      <c r="V184" s="1" t="n"/>
+      <c r="W184" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X184" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12884,6 +15050,18 @@
       <c r="P185" s="1" t="n"/>
       <c r="Q185" s="1" t="n"/>
       <c r="R185" s="1" t="n"/>
+      <c r="S185" s="1" t="n"/>
+      <c r="T185" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U185" s="1" t="n"/>
+      <c r="V185" s="1" t="n"/>
+      <c r="W185" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X185" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12958,6 +15136,18 @@
       </c>
       <c r="Q186" s="1" t="n"/>
       <c r="R186" s="1" t="n"/>
+      <c r="S186" s="1" t="n"/>
+      <c r="T186" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U186" s="1" t="n"/>
+      <c r="V186" s="1" t="n"/>
+      <c r="W186" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="X186" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13028,6 +15218,18 @@
       </c>
       <c r="Q187" s="1" t="n"/>
       <c r="R187" s="1" t="n"/>
+      <c r="S187" s="1" t="n"/>
+      <c r="T187" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U187" s="1" t="n"/>
+      <c r="V187" s="1" t="n"/>
+      <c r="W187" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X187" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13064,6 +15266,18 @@
       <c r="P188" s="1" t="n"/>
       <c r="Q188" s="1" t="n"/>
       <c r="R188" s="1" t="n"/>
+      <c r="S188" s="1" t="n"/>
+      <c r="T188" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U188" s="1" t="n"/>
+      <c r="V188" s="1" t="n"/>
+      <c r="W188" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="X188" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13136,6 +15350,20 @@
       <c r="P189" s="1" t="n"/>
       <c r="Q189" s="1" t="n"/>
       <c r="R189" s="1" t="n"/>
+      <c r="S189" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T189" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U189" s="1" t="n"/>
+      <c r="V189" s="1" t="n"/>
+      <c r="W189" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X189" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13202,6 +15430,16 @@
       </c>
       <c r="Q190" s="1" t="n"/>
       <c r="R190" s="1" t="n"/>
+      <c r="S190" s="1" t="n"/>
+      <c r="T190" s="1" t="n"/>
+      <c r="U190" s="1" t="n"/>
+      <c r="V190" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W190" s="1" t="n"/>
+      <c r="X190" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13270,6 +15508,20 @@
       <c r="P191" s="1" t="n"/>
       <c r="Q191" s="1" t="n"/>
       <c r="R191" s="1" t="n"/>
+      <c r="S191" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T191" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U191" s="1" t="n"/>
+      <c r="V191" s="1" t="n"/>
+      <c r="W191" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X191" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13344,6 +15596,16 @@
       </c>
       <c r="Q192" s="1" t="n"/>
       <c r="R192" s="1" t="n"/>
+      <c r="S192" s="1" t="n"/>
+      <c r="T192" s="1" t="n"/>
+      <c r="U192" s="1" t="n"/>
+      <c r="V192" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="W192" s="1" t="n"/>
+      <c r="X192" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13414,6 +15676,16 @@
       </c>
       <c r="Q193" s="1" t="n"/>
       <c r="R193" s="1" t="n"/>
+      <c r="S193" s="1" t="n"/>
+      <c r="T193" s="1" t="n"/>
+      <c r="U193" s="1" t="n"/>
+      <c r="V193" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W193" s="1" t="n"/>
+      <c r="X193" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13488,6 +15760,18 @@
       </c>
       <c r="Q194" s="1" t="n"/>
       <c r="R194" s="1" t="n"/>
+      <c r="S194" s="1" t="n"/>
+      <c r="T194" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U194" s="1" t="n"/>
+      <c r="V194" s="1" t="n"/>
+      <c r="W194" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="X194" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13560,6 +15844,16 @@
       <c r="P195" s="1" t="n"/>
       <c r="Q195" s="1" t="n"/>
       <c r="R195" s="1" t="n"/>
+      <c r="S195" s="1" t="n"/>
+      <c r="T195" s="1" t="n"/>
+      <c r="U195" s="1" t="n"/>
+      <c r="V195" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W195" s="1" t="n"/>
+      <c r="X195" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13630,6 +15924,16 @@
       </c>
       <c r="Q196" s="1" t="n"/>
       <c r="R196" s="1" t="n"/>
+      <c r="S196" s="1" t="n"/>
+      <c r="T196" s="1" t="n"/>
+      <c r="U196" s="1" t="n"/>
+      <c r="V196" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="W196" s="1" t="n"/>
+      <c r="X196" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13704,6 +16008,18 @@
       </c>
       <c r="Q197" s="1" t="n"/>
       <c r="R197" s="1" t="n"/>
+      <c r="S197" s="1" t="n"/>
+      <c r="T197" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U197" s="1" t="n"/>
+      <c r="V197" s="1" t="n"/>
+      <c r="W197" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X197" s="1" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13778,6 +16094,18 @@
       </c>
       <c r="Q198" s="1" t="n"/>
       <c r="R198" s="1" t="n"/>
+      <c r="S198" s="1" t="n"/>
+      <c r="T198" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U198" s="1" t="n"/>
+      <c r="V198" s="1" t="n"/>
+      <c r="W198" s="1" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X198" s="1" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13838,6 +16166,16 @@
       <c r="P199" s="1" t="n"/>
       <c r="Q199" s="1" t="n"/>
       <c r="R199" s="1" t="n"/>
+      <c r="S199" s="1" t="n"/>
+      <c r="T199" s="1" t="n"/>
+      <c r="U199" s="1" t="n"/>
+      <c r="V199" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W199" s="1" t="n"/>
+      <c r="X199" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13910,6 +16248,18 @@
       <c r="P200" s="1" t="n"/>
       <c r="Q200" s="1" t="n"/>
       <c r="R200" s="1" t="n"/>
+      <c r="S200" s="1" t="n"/>
+      <c r="T200" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U200" s="1" t="n"/>
+      <c r="V200" s="1" t="n"/>
+      <c r="W200" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X200" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13984,6 +16334,16 @@
       </c>
       <c r="Q201" s="1" t="n"/>
       <c r="R201" s="1" t="n"/>
+      <c r="S201" s="1" t="n"/>
+      <c r="T201" s="1" t="n"/>
+      <c r="U201" s="1" t="n"/>
+      <c r="V201" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W201" s="1" t="n"/>
+      <c r="X201" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14058,6 +16418,16 @@
       </c>
       <c r="Q202" s="1" t="n"/>
       <c r="R202" s="1" t="n"/>
+      <c r="S202" s="1" t="n"/>
+      <c r="T202" s="1" t="n"/>
+      <c r="U202" s="1" t="n"/>
+      <c r="V202" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W202" s="1" t="n"/>
+      <c r="X202" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14132,6 +16502,16 @@
       </c>
       <c r="Q203" s="1" t="n"/>
       <c r="R203" s="1" t="n"/>
+      <c r="S203" s="1" t="n"/>
+      <c r="T203" s="1" t="n"/>
+      <c r="U203" s="1" t="n"/>
+      <c r="V203" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W203" s="1" t="n"/>
+      <c r="X203" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -14202,6 +16582,16 @@
       </c>
       <c r="Q204" s="1" t="n"/>
       <c r="R204" s="1" t="n"/>
+      <c r="S204" s="1" t="n"/>
+      <c r="T204" s="1" t="n"/>
+      <c r="U204" s="1" t="n"/>
+      <c r="V204" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W204" s="1" t="n"/>
+      <c r="X204" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -14272,6 +16662,16 @@
       </c>
       <c r="Q205" s="1" t="n"/>
       <c r="R205" s="1" t="n"/>
+      <c r="S205" s="1" t="n"/>
+      <c r="T205" s="1" t="n"/>
+      <c r="U205" s="1" t="n"/>
+      <c r="V205" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W205" s="1" t="n"/>
+      <c r="X205" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14342,6 +16742,16 @@
       </c>
       <c r="Q206" s="1" t="n"/>
       <c r="R206" s="1" t="n"/>
+      <c r="S206" s="1" t="n"/>
+      <c r="T206" s="1" t="n"/>
+      <c r="U206" s="1" t="n"/>
+      <c r="V206" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W206" s="1" t="n"/>
+      <c r="X206" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -14418,6 +16828,16 @@
         <v>1</v>
       </c>
       <c r="R207" s="1" t="n"/>
+      <c r="S207" s="1" t="n"/>
+      <c r="T207" s="1" t="n"/>
+      <c r="U207" s="1" t="n"/>
+      <c r="V207" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="W207" s="1" t="n"/>
+      <c r="X207" s="1" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -14494,6 +16914,16 @@
         <v>1</v>
       </c>
       <c r="R208" s="1" t="n"/>
+      <c r="S208" s="1" t="n"/>
+      <c r="T208" s="1" t="n"/>
+      <c r="U208" s="1" t="n"/>
+      <c r="V208" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="W208" s="1" t="n"/>
+      <c r="X208" s="1" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -14570,6 +17000,16 @@
         <v>1</v>
       </c>
       <c r="R209" s="1" t="n"/>
+      <c r="S209" s="1" t="n"/>
+      <c r="T209" s="1" t="n"/>
+      <c r="U209" s="1" t="n"/>
+      <c r="V209" s="1" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W209" s="1" t="n"/>
+      <c r="X209" s="1" t="n">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -14642,6 +17082,16 @@
         <v>1</v>
       </c>
       <c r="R210" s="1" t="n"/>
+      <c r="S210" s="1" t="n"/>
+      <c r="T210" s="1" t="n"/>
+      <c r="U210" s="1" t="n"/>
+      <c r="V210" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="W210" s="1" t="n"/>
+      <c r="X210" s="1" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -14714,6 +17164,16 @@
         <v>1</v>
       </c>
       <c r="R211" s="1" t="n"/>
+      <c r="S211" s="1" t="n"/>
+      <c r="T211" s="1" t="n"/>
+      <c r="U211" s="1" t="n"/>
+      <c r="V211" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="W211" s="1" t="n"/>
+      <c r="X211" s="1" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -14786,6 +17246,16 @@
         <v>1</v>
       </c>
       <c r="R212" s="1" t="n"/>
+      <c r="S212" s="1" t="n"/>
+      <c r="T212" s="1" t="n"/>
+      <c r="U212" s="1" t="n"/>
+      <c r="V212" s="1" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W212" s="1" t="n"/>
+      <c r="X212" s="1" t="n">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14858,6 +17328,16 @@
       <c r="P213" s="1" t="n"/>
       <c r="Q213" s="1" t="n"/>
       <c r="R213" s="1" t="n"/>
+      <c r="S213" s="1" t="n"/>
+      <c r="T213" s="1" t="n"/>
+      <c r="U213" s="1" t="n"/>
+      <c r="V213" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W213" s="1" t="n"/>
+      <c r="X213" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -14926,6 +17406,16 @@
         <v>1</v>
       </c>
       <c r="R214" s="1" t="n"/>
+      <c r="S214" s="1" t="n"/>
+      <c r="T214" s="1" t="n"/>
+      <c r="U214" s="1" t="n"/>
+      <c r="V214" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W214" s="1" t="n"/>
+      <c r="X214" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -14994,6 +17484,16 @@
         <v>1</v>
       </c>
       <c r="R215" s="1" t="n"/>
+      <c r="S215" s="1" t="n"/>
+      <c r="T215" s="1" t="n"/>
+      <c r="U215" s="1" t="n"/>
+      <c r="V215" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W215" s="1" t="n"/>
+      <c r="X215" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -15062,6 +17562,16 @@
         <v>1</v>
       </c>
       <c r="R216" s="1" t="n"/>
+      <c r="S216" s="1" t="n"/>
+      <c r="T216" s="1" t="n"/>
+      <c r="U216" s="1" t="n"/>
+      <c r="V216" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W216" s="1" t="n"/>
+      <c r="X216" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -15130,6 +17640,16 @@
         <v>1</v>
       </c>
       <c r="R217" s="1" t="n"/>
+      <c r="S217" s="1" t="n"/>
+      <c r="T217" s="1" t="n"/>
+      <c r="U217" s="1" t="n"/>
+      <c r="V217" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W217" s="1" t="n"/>
+      <c r="X217" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15198,6 +17718,16 @@
         <v>1</v>
       </c>
       <c r="R218" s="1" t="n"/>
+      <c r="S218" s="1" t="n"/>
+      <c r="T218" s="1" t="n"/>
+      <c r="U218" s="1" t="n"/>
+      <c r="V218" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W218" s="1" t="n"/>
+      <c r="X218" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -15266,6 +17796,16 @@
         <v>1</v>
       </c>
       <c r="R219" s="1" t="n"/>
+      <c r="S219" s="1" t="n"/>
+      <c r="T219" s="1" t="n"/>
+      <c r="U219" s="1" t="n"/>
+      <c r="V219" s="1" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W219" s="1" t="n"/>
+      <c r="X219" s="1" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -15334,6 +17874,16 @@
         <v>1</v>
       </c>
       <c r="R220" s="1" t="n"/>
+      <c r="S220" s="1" t="n"/>
+      <c r="T220" s="1" t="n"/>
+      <c r="U220" s="1" t="n"/>
+      <c r="V220" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W220" s="1" t="n"/>
+      <c r="X220" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -15402,6 +17952,16 @@
         <v>1</v>
       </c>
       <c r="R221" s="1" t="n"/>
+      <c r="S221" s="1" t="n"/>
+      <c r="T221" s="1" t="n"/>
+      <c r="U221" s="1" t="n"/>
+      <c r="V221" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W221" s="1" t="n"/>
+      <c r="X221" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -15478,6 +18038,16 @@
         <v>1</v>
       </c>
       <c r="R222" s="1" t="n"/>
+      <c r="S222" s="1" t="n"/>
+      <c r="T222" s="1" t="n"/>
+      <c r="U222" s="1" t="n"/>
+      <c r="V222" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W222" s="1" t="n"/>
+      <c r="X222" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -15554,6 +18124,16 @@
         <v>1</v>
       </c>
       <c r="R223" s="1" t="n"/>
+      <c r="S223" s="1" t="n"/>
+      <c r="T223" s="1" t="n"/>
+      <c r="U223" s="1" t="n"/>
+      <c r="V223" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W223" s="1" t="n"/>
+      <c r="X223" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -15630,6 +18210,16 @@
         <v>1</v>
       </c>
       <c r="R224" s="1" t="n"/>
+      <c r="S224" s="1" t="n"/>
+      <c r="T224" s="1" t="n"/>
+      <c r="U224" s="1" t="n"/>
+      <c r="V224" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W224" s="1" t="n"/>
+      <c r="X224" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -15706,6 +18296,16 @@
         <v>1</v>
       </c>
       <c r="R225" s="1" t="n"/>
+      <c r="S225" s="1" t="n"/>
+      <c r="T225" s="1" t="n"/>
+      <c r="U225" s="1" t="n"/>
+      <c r="V225" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W225" s="1" t="n"/>
+      <c r="X225" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -15774,6 +18374,16 @@
         <v>1</v>
       </c>
       <c r="R226" s="1" t="n"/>
+      <c r="S226" s="1" t="n"/>
+      <c r="T226" s="1" t="n"/>
+      <c r="U226" s="1" t="n"/>
+      <c r="V226" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W226" s="1" t="n"/>
+      <c r="X226" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -15850,6 +18460,16 @@
         <v>1</v>
       </c>
       <c r="R227" s="1" t="n"/>
+      <c r="S227" s="1" t="n"/>
+      <c r="T227" s="1" t="n"/>
+      <c r="U227" s="1" t="n"/>
+      <c r="V227" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W227" s="1" t="n"/>
+      <c r="X227" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -15926,6 +18546,16 @@
         <v>1</v>
       </c>
       <c r="R228" s="1" t="n"/>
+      <c r="S228" s="1" t="n"/>
+      <c r="T228" s="1" t="n"/>
+      <c r="U228" s="1" t="n"/>
+      <c r="V228" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W228" s="1" t="n"/>
+      <c r="X228" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -16002,6 +18632,16 @@
         <v>1</v>
       </c>
       <c r="R229" s="1" t="n"/>
+      <c r="S229" s="1" t="n"/>
+      <c r="T229" s="1" t="n"/>
+      <c r="U229" s="1" t="n"/>
+      <c r="V229" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W229" s="1" t="n"/>
+      <c r="X229" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -16078,6 +18718,16 @@
         <v>1</v>
       </c>
       <c r="R230" s="1" t="n"/>
+      <c r="S230" s="1" t="n"/>
+      <c r="T230" s="1" t="n"/>
+      <c r="U230" s="1" t="n"/>
+      <c r="V230" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W230" s="1" t="n"/>
+      <c r="X230" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -16154,6 +18804,16 @@
         <v>1</v>
       </c>
       <c r="R231" s="1" t="n"/>
+      <c r="S231" s="1" t="n"/>
+      <c r="T231" s="1" t="n"/>
+      <c r="U231" s="1" t="n"/>
+      <c r="V231" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W231" s="1" t="n"/>
+      <c r="X231" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -16226,6 +18886,16 @@
         <v>1</v>
       </c>
       <c r="R232" s="1" t="n"/>
+      <c r="S232" s="1" t="n"/>
+      <c r="T232" s="1" t="n"/>
+      <c r="U232" s="1" t="n"/>
+      <c r="V232" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W232" s="1" t="n"/>
+      <c r="X232" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -16298,6 +18968,16 @@
         <v>1</v>
       </c>
       <c r="R233" s="1" t="n"/>
+      <c r="S233" s="1" t="n"/>
+      <c r="T233" s="1" t="n"/>
+      <c r="U233" s="1" t="n"/>
+      <c r="V233" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W233" s="1" t="n"/>
+      <c r="X233" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -16370,6 +19050,16 @@
         <v>1</v>
       </c>
       <c r="R234" s="1" t="n"/>
+      <c r="S234" s="1" t="n"/>
+      <c r="T234" s="1" t="n"/>
+      <c r="U234" s="1" t="n"/>
+      <c r="V234" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W234" s="1" t="n"/>
+      <c r="X234" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -16442,6 +19132,16 @@
         <v>1</v>
       </c>
       <c r="R235" s="1" t="n"/>
+      <c r="S235" s="1" t="n"/>
+      <c r="T235" s="1" t="n"/>
+      <c r="U235" s="1" t="n"/>
+      <c r="V235" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W235" s="1" t="n"/>
+      <c r="X235" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -16514,6 +19214,16 @@
         <v>1</v>
       </c>
       <c r="R236" s="1" t="n"/>
+      <c r="S236" s="1" t="n"/>
+      <c r="T236" s="1" t="n"/>
+      <c r="U236" s="1" t="n"/>
+      <c r="V236" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W236" s="1" t="n"/>
+      <c r="X236" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -16586,6 +19296,16 @@
         <v>1</v>
       </c>
       <c r="R237" s="1" t="n"/>
+      <c r="S237" s="1" t="n"/>
+      <c r="T237" s="1" t="n"/>
+      <c r="U237" s="1" t="n"/>
+      <c r="V237" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W237" s="1" t="n"/>
+      <c r="X237" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -16658,6 +19378,16 @@
         <v>1</v>
       </c>
       <c r="R238" s="1" t="n"/>
+      <c r="S238" s="1" t="n"/>
+      <c r="T238" s="1" t="n"/>
+      <c r="U238" s="1" t="n"/>
+      <c r="V238" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W238" s="1" t="n"/>
+      <c r="X238" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -16730,6 +19460,16 @@
         <v>1</v>
       </c>
       <c r="R239" s="1" t="n"/>
+      <c r="S239" s="1" t="n"/>
+      <c r="T239" s="1" t="n"/>
+      <c r="U239" s="1" t="n"/>
+      <c r="V239" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W239" s="1" t="n"/>
+      <c r="X239" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -16806,6 +19546,18 @@
         <v>1</v>
       </c>
       <c r="R240" s="1" t="n"/>
+      <c r="S240" s="1" t="n"/>
+      <c r="T240" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U240" s="1" t="n"/>
+      <c r="V240" s="1" t="n"/>
+      <c r="W240" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="X240" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -16878,6 +19630,16 @@
         <v>1</v>
       </c>
       <c r="R241" s="1" t="n"/>
+      <c r="S241" s="1" t="n"/>
+      <c r="T241" s="1" t="n"/>
+      <c r="U241" s="1" t="n"/>
+      <c r="V241" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W241" s="1" t="n"/>
+      <c r="X241" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -16950,6 +19712,16 @@
         <v>1</v>
       </c>
       <c r="R242" s="1" t="n"/>
+      <c r="S242" s="1" t="n"/>
+      <c r="T242" s="1" t="n"/>
+      <c r="U242" s="1" t="n"/>
+      <c r="V242" s="1" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W242" s="1" t="n"/>
+      <c r="X242" s="1" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -17026,6 +19798,18 @@
       <c r="R243" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S243" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T243" s="1" t="n"/>
+      <c r="U243" s="1" t="n"/>
+      <c r="V243" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W243" s="1" t="n"/>
+      <c r="X243" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -17102,6 +19886,18 @@
         <v>1</v>
       </c>
       <c r="R244" s="1" t="n"/>
+      <c r="S244" s="1" t="n"/>
+      <c r="T244" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U244" s="1" t="n"/>
+      <c r="V244" s="1" t="n"/>
+      <c r="W244" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="X244" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -17178,6 +19974,16 @@
         <v>1</v>
       </c>
       <c r="R245" s="1" t="n"/>
+      <c r="S245" s="1" t="n"/>
+      <c r="T245" s="1" t="n"/>
+      <c r="U245" s="1" t="n"/>
+      <c r="V245" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W245" s="1" t="n"/>
+      <c r="X245" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -17254,6 +20060,18 @@
       <c r="R246" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S246" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T246" s="1" t="n"/>
+      <c r="U246" s="1" t="n"/>
+      <c r="V246" s="1" t="n">
+        <v>405</v>
+      </c>
+      <c r="W246" s="1" t="n"/>
+      <c r="X246" s="1" t="n">
+        <v>405</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -17330,6 +20148,16 @@
         <v>1</v>
       </c>
       <c r="R247" s="1" t="n"/>
+      <c r="S247" s="1" t="n"/>
+      <c r="T247" s="1" t="n"/>
+      <c r="U247" s="1" t="n"/>
+      <c r="V247" s="1" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W247" s="1" t="n"/>
+      <c r="X247" s="1" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -17406,6 +20234,18 @@
       <c r="R248" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S248" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T248" s="1" t="n"/>
+      <c r="U248" s="1" t="n"/>
+      <c r="V248" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="W248" s="1" t="n"/>
+      <c r="X248" s="1" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -17478,6 +20318,16 @@
         <v>1</v>
       </c>
       <c r="R249" s="1" t="n"/>
+      <c r="S249" s="1" t="n"/>
+      <c r="T249" s="1" t="n"/>
+      <c r="U249" s="1" t="n"/>
+      <c r="V249" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W249" s="1" t="n"/>
+      <c r="X249" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -17550,6 +20400,16 @@
         <v>1</v>
       </c>
       <c r="R250" s="1" t="n"/>
+      <c r="S250" s="1" t="n"/>
+      <c r="T250" s="1" t="n"/>
+      <c r="U250" s="1" t="n"/>
+      <c r="V250" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W250" s="1" t="n"/>
+      <c r="X250" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -17626,6 +20486,18 @@
         <v>1</v>
       </c>
       <c r="R251" s="1" t="n"/>
+      <c r="S251" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T251" s="1" t="n"/>
+      <c r="U251" s="1" t="n"/>
+      <c r="V251" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W251" s="1" t="n"/>
+      <c r="X251" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -17698,6 +20570,16 @@
         <v>1</v>
       </c>
       <c r="R252" s="1" t="n"/>
+      <c r="S252" s="1" t="n"/>
+      <c r="T252" s="1" t="n"/>
+      <c r="U252" s="1" t="n"/>
+      <c r="V252" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W252" s="1" t="n"/>
+      <c r="X252" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -17770,6 +20652,18 @@
       <c r="R253" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S253" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T253" s="1" t="n"/>
+      <c r="U253" s="1" t="n"/>
+      <c r="V253" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W253" s="1" t="n"/>
+      <c r="X253" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -17842,6 +20736,16 @@
         <v>1</v>
       </c>
       <c r="R254" s="1" t="n"/>
+      <c r="S254" s="1" t="n"/>
+      <c r="T254" s="1" t="n"/>
+      <c r="U254" s="1" t="n"/>
+      <c r="V254" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W254" s="1" t="n"/>
+      <c r="X254" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -17914,6 +20818,16 @@
         <v>1</v>
       </c>
       <c r="R255" s="1" t="n"/>
+      <c r="S255" s="1" t="n"/>
+      <c r="T255" s="1" t="n"/>
+      <c r="U255" s="1" t="n"/>
+      <c r="V255" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W255" s="1" t="n"/>
+      <c r="X255" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -17986,6 +20900,16 @@
         <v>1</v>
       </c>
       <c r="R256" s="1" t="n"/>
+      <c r="S256" s="1" t="n"/>
+      <c r="T256" s="1" t="n"/>
+      <c r="U256" s="1" t="n"/>
+      <c r="V256" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W256" s="1" t="n"/>
+      <c r="X256" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -18058,6 +20982,16 @@
         <v>1</v>
       </c>
       <c r="R257" s="1" t="n"/>
+      <c r="S257" s="1" t="n"/>
+      <c r="T257" s="1" t="n"/>
+      <c r="U257" s="1" t="n"/>
+      <c r="V257" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W257" s="1" t="n"/>
+      <c r="X257" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -18130,6 +21064,16 @@
         <v>1</v>
       </c>
       <c r="R258" s="1" t="n"/>
+      <c r="S258" s="1" t="n"/>
+      <c r="T258" s="1" t="n"/>
+      <c r="U258" s="1" t="n"/>
+      <c r="V258" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W258" s="1" t="n"/>
+      <c r="X258" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -18201,6 +21145,18 @@
       <c r="Q259" s="1" t="n"/>
       <c r="R259" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="S259" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T259" s="1" t="n"/>
+      <c r="U259" s="1" t="n"/>
+      <c r="V259" s="1" t="n">
+        <v>405</v>
+      </c>
+      <c r="W259" s="1" t="n"/>
+      <c r="X259" s="1" t="n">
+        <v>405</v>
       </c>
     </row>
     <row r="260">
@@ -18266,6 +21222,16 @@
       <c r="P260" s="1" t="n"/>
       <c r="Q260" s="1" t="n"/>
       <c r="R260" s="1" t="n"/>
+      <c r="S260" s="1" t="n"/>
+      <c r="T260" s="1" t="n"/>
+      <c r="U260" s="1" t="n"/>
+      <c r="V260" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W260" s="1" t="n"/>
+      <c r="X260" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -18330,6 +21296,16 @@
       <c r="P261" s="1" t="n"/>
       <c r="Q261" s="1" t="n"/>
       <c r="R261" s="1" t="n"/>
+      <c r="S261" s="1" t="n"/>
+      <c r="T261" s="1" t="n"/>
+      <c r="U261" s="1" t="n"/>
+      <c r="V261" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="W261" s="1" t="n"/>
+      <c r="X261" s="1" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -18398,6 +21374,16 @@
       <c r="P262" s="1" t="n"/>
       <c r="Q262" s="1" t="n"/>
       <c r="R262" s="1" t="n"/>
+      <c r="S262" s="1" t="n"/>
+      <c r="T262" s="1" t="n"/>
+      <c r="U262" s="1" t="n"/>
+      <c r="V262" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W262" s="1" t="n"/>
+      <c r="X262" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -18434,6 +21420,16 @@
       <c r="P263" s="1" t="n"/>
       <c r="Q263" s="1" t="n"/>
       <c r="R263" s="1" t="n"/>
+      <c r="S263" s="1" t="n"/>
+      <c r="T263" s="1" t="n"/>
+      <c r="U263" s="1" t="n"/>
+      <c r="V263" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="W263" s="1" t="n"/>
+      <c r="X263" s="1" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -18510,6 +21506,20 @@
       <c r="R264" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S264" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T264" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U264" s="1" t="n"/>
+      <c r="V264" s="1" t="n"/>
+      <c r="W264" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X264" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -18586,6 +21596,20 @@
       <c r="R265" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S265" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T265" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U265" s="1" t="n"/>
+      <c r="V265" s="1" t="n"/>
+      <c r="W265" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X265" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -18662,6 +21686,20 @@
       <c r="R266" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U266" s="1" t="n"/>
+      <c r="V266" s="1" t="n"/>
+      <c r="W266" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X266" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -18738,6 +21776,20 @@
       <c r="R267" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S267" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T267" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U267" s="1" t="n"/>
+      <c r="V267" s="1" t="n"/>
+      <c r="W267" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X267" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -18814,6 +21866,16 @@
         <v>1</v>
       </c>
       <c r="R268" s="1" t="n"/>
+      <c r="S268" s="1" t="n"/>
+      <c r="T268" s="1" t="n"/>
+      <c r="U268" s="1" t="n"/>
+      <c r="V268" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="W268" s="1" t="n"/>
+      <c r="X268" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -18890,6 +21952,16 @@
         <v>1</v>
       </c>
       <c r="R269" s="1" t="n"/>
+      <c r="S269" s="1" t="n"/>
+      <c r="T269" s="1" t="n"/>
+      <c r="U269" s="1" t="n"/>
+      <c r="V269" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="W269" s="1" t="n"/>
+      <c r="X269" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -18966,6 +22038,16 @@
         <v>1</v>
       </c>
       <c r="R270" s="1" t="n"/>
+      <c r="S270" s="1" t="n"/>
+      <c r="T270" s="1" t="n"/>
+      <c r="U270" s="1" t="n"/>
+      <c r="V270" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W270" s="1" t="n"/>
+      <c r="X270" s="1" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -19038,6 +22120,20 @@
       <c r="R271" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S271" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T271" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U271" s="1" t="n"/>
+      <c r="V271" s="1" t="n"/>
+      <c r="W271" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X271" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -19110,6 +22206,20 @@
       <c r="R272" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S272" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T272" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U272" s="1" t="n"/>
+      <c r="V272" s="1" t="n"/>
+      <c r="W272" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X272" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -19182,6 +22292,20 @@
       <c r="R273" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S273" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T273" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U273" s="1" t="n"/>
+      <c r="V273" s="1" t="n"/>
+      <c r="W273" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X273" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -19254,6 +22378,20 @@
       <c r="R274" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S274" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T274" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U274" s="1" t="n"/>
+      <c r="V274" s="1" t="n"/>
+      <c r="W274" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X274" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -19330,6 +22468,20 @@
       <c r="R275" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S275" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T275" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U275" s="1" t="n"/>
+      <c r="V275" s="1" t="n"/>
+      <c r="W275" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X275" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -19406,6 +22558,20 @@
       <c r="R276" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S276" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T276" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U276" s="1" t="n"/>
+      <c r="V276" s="1" t="n"/>
+      <c r="W276" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X276" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -19482,6 +22648,20 @@
       <c r="R277" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S277" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T277" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U277" s="1" t="n"/>
+      <c r="V277" s="1" t="n"/>
+      <c r="W277" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X277" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -19554,6 +22734,20 @@
       <c r="R278" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S278" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T278" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U278" s="1" t="n"/>
+      <c r="V278" s="1" t="n"/>
+      <c r="W278" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X278" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -19626,6 +22820,20 @@
       <c r="R279" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S279" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T279" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U279" s="1" t="n"/>
+      <c r="V279" s="1" t="n"/>
+      <c r="W279" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X279" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -19698,6 +22906,20 @@
       <c r="R280" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S280" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T280" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U280" s="1" t="n"/>
+      <c r="V280" s="1" t="n"/>
+      <c r="W280" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X280" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -19770,6 +22992,16 @@
         <v>1</v>
       </c>
       <c r="R281" s="1" t="n"/>
+      <c r="S281" s="1" t="n"/>
+      <c r="T281" s="1" t="n"/>
+      <c r="U281" s="1" t="n"/>
+      <c r="V281" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="W281" s="1" t="n"/>
+      <c r="X281" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -19846,6 +23078,20 @@
       <c r="R282" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S282" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T282" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U282" s="1" t="n"/>
+      <c r="V282" s="1" t="n"/>
+      <c r="W282" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X282" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -19918,6 +23164,16 @@
         <v>1</v>
       </c>
       <c r="R283" s="1" t="n"/>
+      <c r="S283" s="1" t="n"/>
+      <c r="T283" s="1" t="n"/>
+      <c r="U283" s="1" t="n"/>
+      <c r="V283" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="W283" s="1" t="n"/>
+      <c r="X283" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -19990,6 +23246,20 @@
       <c r="R284" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S284" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T284" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U284" s="1" t="n"/>
+      <c r="V284" s="1" t="n"/>
+      <c r="W284" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X284" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -20062,6 +23332,16 @@
         <v>1</v>
       </c>
       <c r="R285" s="1" t="n"/>
+      <c r="S285" s="1" t="n"/>
+      <c r="T285" s="1" t="n"/>
+      <c r="U285" s="1" t="n"/>
+      <c r="V285" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W285" s="1" t="n"/>
+      <c r="X285" s="1" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -20130,6 +23410,20 @@
       <c r="P286" s="1" t="n"/>
       <c r="Q286" s="1" t="n"/>
       <c r="R286" s="1" t="n"/>
+      <c r="S286" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T286" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U286" s="1" t="n"/>
+      <c r="V286" s="1" t="n"/>
+      <c r="W286" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X286" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -20198,6 +23492,20 @@
       <c r="P287" s="1" t="n"/>
       <c r="Q287" s="1" t="n"/>
       <c r="R287" s="1" t="n"/>
+      <c r="S287" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T287" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U287" s="1" t="n"/>
+      <c r="V287" s="1" t="n"/>
+      <c r="W287" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X287" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -20264,6 +23572,16 @@
       </c>
       <c r="Q288" s="1" t="n"/>
       <c r="R288" s="1" t="n"/>
+      <c r="S288" s="1" t="n"/>
+      <c r="T288" s="1" t="n"/>
+      <c r="U288" s="1" t="n"/>
+      <c r="V288" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W288" s="1" t="n"/>
+      <c r="X288" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -20330,6 +23648,16 @@
       </c>
       <c r="Q289" s="1" t="n"/>
       <c r="R289" s="1" t="n"/>
+      <c r="S289" s="1" t="n"/>
+      <c r="T289" s="1" t="n"/>
+      <c r="U289" s="1" t="n"/>
+      <c r="V289" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W289" s="1" t="n"/>
+      <c r="X289" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -20404,6 +23732,18 @@
       </c>
       <c r="Q290" s="1" t="n"/>
       <c r="R290" s="1" t="n"/>
+      <c r="S290" s="1" t="n"/>
+      <c r="T290" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U290" s="1" t="n"/>
+      <c r="V290" s="1" t="n"/>
+      <c r="W290" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="X290" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -20474,6 +23814,16 @@
       </c>
       <c r="Q291" s="1" t="n"/>
       <c r="R291" s="1" t="n"/>
+      <c r="S291" s="1" t="n"/>
+      <c r="T291" s="1" t="n"/>
+      <c r="U291" s="1" t="n"/>
+      <c r="V291" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W291" s="1" t="n"/>
+      <c r="X291" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -20544,6 +23894,16 @@
       </c>
       <c r="Q292" s="1" t="n"/>
       <c r="R292" s="1" t="n"/>
+      <c r="S292" s="1" t="n"/>
+      <c r="T292" s="1" t="n"/>
+      <c r="U292" s="1" t="n"/>
+      <c r="V292" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W292" s="1" t="n"/>
+      <c r="X292" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -20614,6 +23974,18 @@
       </c>
       <c r="Q293" s="1" t="n"/>
       <c r="R293" s="1" t="n"/>
+      <c r="S293" s="1" t="n"/>
+      <c r="T293" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U293" s="1" t="n"/>
+      <c r="V293" s="1" t="n"/>
+      <c r="W293" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="X293" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -20650,6 +24022,16 @@
       <c r="P294" s="1" t="n"/>
       <c r="Q294" s="1" t="n"/>
       <c r="R294" s="1" t="n"/>
+      <c r="S294" s="1" t="n"/>
+      <c r="T294" s="1" t="n"/>
+      <c r="U294" s="1" t="n"/>
+      <c r="V294" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W294" s="1" t="n"/>
+      <c r="X294" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -20686,6 +24068,16 @@
       <c r="P295" s="1" t="n"/>
       <c r="Q295" s="1" t="n"/>
       <c r="R295" s="1" t="n"/>
+      <c r="S295" s="1" t="n"/>
+      <c r="T295" s="1" t="n"/>
+      <c r="U295" s="1" t="n"/>
+      <c r="V295" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W295" s="1" t="n"/>
+      <c r="X295" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -20754,6 +24146,18 @@
       <c r="P296" s="1" t="n"/>
       <c r="Q296" s="1" t="n"/>
       <c r="R296" s="1" t="n"/>
+      <c r="S296" s="1" t="n"/>
+      <c r="T296" s="1" t="n"/>
+      <c r="U296" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V296" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W296" s="1" t="n"/>
+      <c r="X296" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -20822,6 +24226,18 @@
       <c r="P297" s="1" t="n"/>
       <c r="Q297" s="1" t="n"/>
       <c r="R297" s="1" t="n"/>
+      <c r="S297" s="1" t="n"/>
+      <c r="T297" s="1" t="n"/>
+      <c r="U297" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V297" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W297" s="1" t="n"/>
+      <c r="X297" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -20886,6 +24302,16 @@
       <c r="P298" s="1" t="n"/>
       <c r="Q298" s="1" t="n"/>
       <c r="R298" s="1" t="n"/>
+      <c r="S298" s="1" t="n"/>
+      <c r="T298" s="1" t="n"/>
+      <c r="U298" s="1" t="n"/>
+      <c r="V298" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W298" s="1" t="n"/>
+      <c r="X298" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -20950,6 +24376,16 @@
       <c r="P299" s="1" t="n"/>
       <c r="Q299" s="1" t="n"/>
       <c r="R299" s="1" t="n"/>
+      <c r="S299" s="1" t="n"/>
+      <c r="T299" s="1" t="n"/>
+      <c r="U299" s="1" t="n"/>
+      <c r="V299" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="W299" s="1" t="n"/>
+      <c r="X299" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -21018,6 +24454,16 @@
       <c r="P300" s="1" t="n"/>
       <c r="Q300" s="1" t="n"/>
       <c r="R300" s="1" t="n"/>
+      <c r="S300" s="1" t="n"/>
+      <c r="T300" s="1" t="n"/>
+      <c r="U300" s="1" t="n"/>
+      <c r="V300" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W300" s="1" t="n"/>
+      <c r="X300" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -21090,6 +24536,18 @@
       <c r="P301" s="1" t="n"/>
       <c r="Q301" s="1" t="n"/>
       <c r="R301" s="1" t="n"/>
+      <c r="S301" s="1" t="n"/>
+      <c r="T301" s="1" t="n"/>
+      <c r="U301" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V301" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W301" s="1" t="n"/>
+      <c r="X301" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -21158,6 +24616,16 @@
       <c r="P302" s="1" t="n"/>
       <c r="Q302" s="1" t="n"/>
       <c r="R302" s="1" t="n"/>
+      <c r="S302" s="1" t="n"/>
+      <c r="T302" s="1" t="n"/>
+      <c r="U302" s="1" t="n"/>
+      <c r="V302" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="W302" s="1" t="n"/>
+      <c r="X302" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -21230,6 +24698,18 @@
       <c r="P303" s="1" t="n"/>
       <c r="Q303" s="1" t="n"/>
       <c r="R303" s="1" t="n"/>
+      <c r="S303" s="1" t="n"/>
+      <c r="T303" s="1" t="n"/>
+      <c r="U303" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V303" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W303" s="1" t="n"/>
+      <c r="X303" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -21266,6 +24746,16 @@
       <c r="P304" s="1" t="n"/>
       <c r="Q304" s="1" t="n"/>
       <c r="R304" s="1" t="n"/>
+      <c r="S304" s="1" t="n"/>
+      <c r="T304" s="1" t="n"/>
+      <c r="U304" s="1" t="n"/>
+      <c r="V304" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W304" s="1" t="n"/>
+      <c r="X304" s="1" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -21302,6 +24792,20 @@
       <c r="P305" s="1" t="n"/>
       <c r="Q305" s="1" t="n"/>
       <c r="R305" s="1" t="n"/>
+      <c r="S305" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T305" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U305" s="1" t="n"/>
+      <c r="V305" s="1" t="n"/>
+      <c r="W305" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X305" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -21338,6 +24842,16 @@
       <c r="P306" s="1" t="n"/>
       <c r="Q306" s="1" t="n"/>
       <c r="R306" s="1" t="n"/>
+      <c r="S306" s="1" t="n"/>
+      <c r="T306" s="1" t="n"/>
+      <c r="U306" s="1" t="n"/>
+      <c r="V306" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W306" s="1" t="n"/>
+      <c r="X306" s="1" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -21374,6 +24888,20 @@
       <c r="P307" s="1" t="n"/>
       <c r="Q307" s="1" t="n"/>
       <c r="R307" s="1" t="n"/>
+      <c r="S307" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T307" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U307" s="1" t="n"/>
+      <c r="V307" s="1" t="n"/>
+      <c r="W307" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X307" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -21440,6 +24968,16 @@
       </c>
       <c r="Q308" s="1" t="n"/>
       <c r="R308" s="1" t="n"/>
+      <c r="S308" s="1" t="n"/>
+      <c r="T308" s="1" t="n"/>
+      <c r="U308" s="1" t="n"/>
+      <c r="V308" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="W308" s="1" t="n"/>
+      <c r="X308" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -21506,6 +25044,16 @@
       </c>
       <c r="Q309" s="1" t="n"/>
       <c r="R309" s="1" t="n"/>
+      <c r="S309" s="1" t="n"/>
+      <c r="T309" s="1" t="n"/>
+      <c r="U309" s="1" t="n"/>
+      <c r="V309" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W309" s="1" t="n"/>
+      <c r="X309" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -21576,6 +25124,16 @@
       </c>
       <c r="Q310" s="1" t="n"/>
       <c r="R310" s="1" t="n"/>
+      <c r="S310" s="1" t="n"/>
+      <c r="T310" s="1" t="n"/>
+      <c r="U310" s="1" t="n"/>
+      <c r="V310" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W310" s="1" t="n"/>
+      <c r="X310" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -21646,6 +25204,16 @@
       </c>
       <c r="Q311" s="1" t="n"/>
       <c r="R311" s="1" t="n"/>
+      <c r="S311" s="1" t="n"/>
+      <c r="T311" s="1" t="n"/>
+      <c r="U311" s="1" t="n"/>
+      <c r="V311" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="W311" s="1" t="n"/>
+      <c r="X311" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -21682,6 +25250,16 @@
       <c r="P312" s="1" t="n"/>
       <c r="Q312" s="1" t="n"/>
       <c r="R312" s="1" t="n"/>
+      <c r="S312" s="1" t="n"/>
+      <c r="T312" s="1" t="n"/>
+      <c r="U312" s="1" t="n"/>
+      <c r="V312" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W312" s="1" t="n"/>
+      <c r="X312" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -21718,6 +25296,16 @@
       <c r="P313" s="1" t="n"/>
       <c r="Q313" s="1" t="n"/>
       <c r="R313" s="1" t="n"/>
+      <c r="S313" s="1" t="n"/>
+      <c r="T313" s="1" t="n"/>
+      <c r="U313" s="1" t="n"/>
+      <c r="V313" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W313" s="1" t="n"/>
+      <c r="X313" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -21792,6 +25380,18 @@
       </c>
       <c r="Q314" s="1" t="n"/>
       <c r="R314" s="1" t="n"/>
+      <c r="S314" s="1" t="n"/>
+      <c r="T314" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U314" s="1" t="n"/>
+      <c r="V314" s="1" t="n"/>
+      <c r="W314" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="X314" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -21866,6 +25466,18 @@
       </c>
       <c r="Q315" s="1" t="n"/>
       <c r="R315" s="1" t="n"/>
+      <c r="S315" s="1" t="n"/>
+      <c r="T315" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U315" s="1" t="n"/>
+      <c r="V315" s="1" t="n"/>
+      <c r="W315" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X315" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -21932,6 +25544,16 @@
       </c>
       <c r="Q316" s="1" t="n"/>
       <c r="R316" s="1" t="n"/>
+      <c r="S316" s="1" t="n"/>
+      <c r="T316" s="1" t="n"/>
+      <c r="U316" s="1" t="n"/>
+      <c r="V316" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W316" s="1" t="n"/>
+      <c r="X316" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -21998,6 +25620,16 @@
       </c>
       <c r="Q317" s="1" t="n"/>
       <c r="R317" s="1" t="n"/>
+      <c r="S317" s="1" t="n"/>
+      <c r="T317" s="1" t="n"/>
+      <c r="U317" s="1" t="n"/>
+      <c r="V317" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W317" s="1" t="n"/>
+      <c r="X317" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -22072,6 +25704,18 @@
       </c>
       <c r="Q318" s="1" t="n"/>
       <c r="R318" s="1" t="n"/>
+      <c r="S318" s="1" t="n"/>
+      <c r="T318" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U318" s="1" t="n"/>
+      <c r="V318" s="1" t="n"/>
+      <c r="W318" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X318" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -22108,6 +25752,18 @@
       <c r="P319" s="1" t="n"/>
       <c r="Q319" s="1" t="n"/>
       <c r="R319" s="1" t="n"/>
+      <c r="S319" s="1" t="n"/>
+      <c r="T319" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U319" s="1" t="n"/>
+      <c r="V319" s="1" t="n"/>
+      <c r="W319" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X319" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -22144,6 +25800,16 @@
       <c r="P320" s="1" t="n"/>
       <c r="Q320" s="1" t="n"/>
       <c r="R320" s="1" t="n"/>
+      <c r="S320" s="1" t="n"/>
+      <c r="T320" s="1" t="n"/>
+      <c r="U320" s="1" t="n"/>
+      <c r="V320" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W320" s="1" t="n"/>
+      <c r="X320" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -22180,6 +25846,20 @@
       <c r="P321" s="1" t="n"/>
       <c r="Q321" s="1" t="n"/>
       <c r="R321" s="1" t="n"/>
+      <c r="S321" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T321" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U321" s="1" t="n"/>
+      <c r="V321" s="1" t="n"/>
+      <c r="W321" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X321" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -22216,6 +25896,18 @@
       <c r="P322" s="1" t="n"/>
       <c r="Q322" s="1" t="n"/>
       <c r="R322" s="1" t="n"/>
+      <c r="S322" s="1" t="n"/>
+      <c r="T322" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U322" s="1" t="n"/>
+      <c r="V322" s="1" t="n"/>
+      <c r="W322" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X322" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -22282,6 +25974,16 @@
         <v>1</v>
       </c>
       <c r="R323" s="1" t="n"/>
+      <c r="S323" s="1" t="n"/>
+      <c r="T323" s="1" t="n"/>
+      <c r="U323" s="1" t="n"/>
+      <c r="V323" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W323" s="1" t="n"/>
+      <c r="X323" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -22348,6 +26050,16 @@
         <v>1</v>
       </c>
       <c r="R324" s="1" t="n"/>
+      <c r="S324" s="1" t="n"/>
+      <c r="T324" s="1" t="n"/>
+      <c r="U324" s="1" t="n"/>
+      <c r="V324" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W324" s="1" t="n"/>
+      <c r="X324" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -22414,6 +26126,16 @@
         <v>1</v>
       </c>
       <c r="R325" s="1" t="n"/>
+      <c r="S325" s="1" t="n"/>
+      <c r="T325" s="1" t="n"/>
+      <c r="U325" s="1" t="n"/>
+      <c r="V325" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W325" s="1" t="n"/>
+      <c r="X325" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -22488,6 +26210,16 @@
         <v>1</v>
       </c>
       <c r="R326" s="1" t="n"/>
+      <c r="S326" s="1" t="n"/>
+      <c r="T326" s="1" t="n"/>
+      <c r="U326" s="1" t="n"/>
+      <c r="V326" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="W326" s="1" t="n"/>
+      <c r="X326" s="1" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -22554,6 +26286,16 @@
         <v>1</v>
       </c>
       <c r="R327" s="1" t="n"/>
+      <c r="S327" s="1" t="n"/>
+      <c r="T327" s="1" t="n"/>
+      <c r="U327" s="1" t="n"/>
+      <c r="V327" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W327" s="1" t="n"/>
+      <c r="X327" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -22620,6 +26362,16 @@
         <v>1</v>
       </c>
       <c r="R328" s="1" t="n"/>
+      <c r="S328" s="1" t="n"/>
+      <c r="T328" s="1" t="n"/>
+      <c r="U328" s="1" t="n"/>
+      <c r="V328" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W328" s="1" t="n"/>
+      <c r="X328" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -22694,6 +26446,16 @@
         <v>1</v>
       </c>
       <c r="R329" s="1" t="n"/>
+      <c r="S329" s="1" t="n"/>
+      <c r="T329" s="1" t="n"/>
+      <c r="U329" s="1" t="n"/>
+      <c r="V329" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W329" s="1" t="n"/>
+      <c r="X329" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -22760,6 +26522,16 @@
         <v>1</v>
       </c>
       <c r="R330" s="1" t="n"/>
+      <c r="S330" s="1" t="n"/>
+      <c r="T330" s="1" t="n"/>
+      <c r="U330" s="1" t="n"/>
+      <c r="V330" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W330" s="1" t="n"/>
+      <c r="X330" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -22826,6 +26598,16 @@
         <v>1</v>
       </c>
       <c r="R331" s="1" t="n"/>
+      <c r="S331" s="1" t="n"/>
+      <c r="T331" s="1" t="n"/>
+      <c r="U331" s="1" t="n"/>
+      <c r="V331" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W331" s="1" t="n"/>
+      <c r="X331" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -22900,6 +26682,16 @@
         <v>1</v>
       </c>
       <c r="R332" s="1" t="n"/>
+      <c r="S332" s="1" t="n"/>
+      <c r="T332" s="1" t="n"/>
+      <c r="U332" s="1" t="n"/>
+      <c r="V332" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="W332" s="1" t="n"/>
+      <c r="X332" s="1" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -22970,6 +26762,16 @@
         <v>1</v>
       </c>
       <c r="R333" s="1" t="n"/>
+      <c r="S333" s="1" t="n"/>
+      <c r="T333" s="1" t="n"/>
+      <c r="U333" s="1" t="n"/>
+      <c r="V333" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W333" s="1" t="n"/>
+      <c r="X333" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -23040,6 +26842,16 @@
         <v>1</v>
       </c>
       <c r="R334" s="1" t="n"/>
+      <c r="S334" s="1" t="n"/>
+      <c r="T334" s="1" t="n"/>
+      <c r="U334" s="1" t="n"/>
+      <c r="V334" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W334" s="1" t="n"/>
+      <c r="X334" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -23110,6 +26922,16 @@
         <v>1</v>
       </c>
       <c r="R335" s="1" t="n"/>
+      <c r="S335" s="1" t="n"/>
+      <c r="T335" s="1" t="n"/>
+      <c r="U335" s="1" t="n"/>
+      <c r="V335" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W335" s="1" t="n"/>
+      <c r="X335" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -23180,6 +27002,16 @@
         <v>1</v>
       </c>
       <c r="R336" s="1" t="n"/>
+      <c r="S336" s="1" t="n"/>
+      <c r="T336" s="1" t="n"/>
+      <c r="U336" s="1" t="n"/>
+      <c r="V336" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W336" s="1" t="n"/>
+      <c r="X336" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -23250,6 +27082,16 @@
         <v>1</v>
       </c>
       <c r="R337" s="1" t="n"/>
+      <c r="S337" s="1" t="n"/>
+      <c r="T337" s="1" t="n"/>
+      <c r="U337" s="1" t="n"/>
+      <c r="V337" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W337" s="1" t="n"/>
+      <c r="X337" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -23320,6 +27162,16 @@
         <v>1</v>
       </c>
       <c r="R338" s="1" t="n"/>
+      <c r="S338" s="1" t="n"/>
+      <c r="T338" s="1" t="n"/>
+      <c r="U338" s="1" t="n"/>
+      <c r="V338" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W338" s="1" t="n"/>
+      <c r="X338" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -23390,6 +27242,16 @@
         <v>1</v>
       </c>
       <c r="R339" s="1" t="n"/>
+      <c r="S339" s="1" t="n"/>
+      <c r="T339" s="1" t="n"/>
+      <c r="U339" s="1" t="n"/>
+      <c r="V339" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W339" s="1" t="n"/>
+      <c r="X339" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -23460,6 +27322,16 @@
         <v>1</v>
       </c>
       <c r="R340" s="1" t="n"/>
+      <c r="S340" s="1" t="n"/>
+      <c r="T340" s="1" t="n"/>
+      <c r="U340" s="1" t="n"/>
+      <c r="V340" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W340" s="1" t="n"/>
+      <c r="X340" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -23530,6 +27402,16 @@
         <v>1</v>
       </c>
       <c r="R341" s="1" t="n"/>
+      <c r="S341" s="1" t="n"/>
+      <c r="T341" s="1" t="n"/>
+      <c r="U341" s="1" t="n"/>
+      <c r="V341" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W341" s="1" t="n"/>
+      <c r="X341" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -23600,6 +27482,16 @@
         <v>1</v>
       </c>
       <c r="R342" s="1" t="n"/>
+      <c r="S342" s="1" t="n"/>
+      <c r="T342" s="1" t="n"/>
+      <c r="U342" s="1" t="n"/>
+      <c r="V342" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W342" s="1" t="n"/>
+      <c r="X342" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -23670,6 +27562,16 @@
         <v>1</v>
       </c>
       <c r="R343" s="1" t="n"/>
+      <c r="S343" s="1" t="n"/>
+      <c r="T343" s="1" t="n"/>
+      <c r="U343" s="1" t="n"/>
+      <c r="V343" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W343" s="1" t="n"/>
+      <c r="X343" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -23740,6 +27642,16 @@
         <v>1</v>
       </c>
       <c r="R344" s="1" t="n"/>
+      <c r="S344" s="1" t="n"/>
+      <c r="T344" s="1" t="n"/>
+      <c r="U344" s="1" t="n"/>
+      <c r="V344" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W344" s="1" t="n"/>
+      <c r="X344" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -23810,6 +27722,16 @@
         <v>1</v>
       </c>
       <c r="R345" s="1" t="n"/>
+      <c r="S345" s="1" t="n"/>
+      <c r="T345" s="1" t="n"/>
+      <c r="U345" s="1" t="n"/>
+      <c r="V345" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W345" s="1" t="n"/>
+      <c r="X345" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -23880,6 +27802,16 @@
         <v>1</v>
       </c>
       <c r="R346" s="1" t="n"/>
+      <c r="S346" s="1" t="n"/>
+      <c r="T346" s="1" t="n"/>
+      <c r="U346" s="1" t="n"/>
+      <c r="V346" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="W346" s="1" t="n"/>
+      <c r="X346" s="1" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -23950,6 +27882,16 @@
         <v>1</v>
       </c>
       <c r="R347" s="1" t="n"/>
+      <c r="S347" s="1" t="n"/>
+      <c r="T347" s="1" t="n"/>
+      <c r="U347" s="1" t="n"/>
+      <c r="V347" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W347" s="1" t="n"/>
+      <c r="X347" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -24020,6 +27962,16 @@
         <v>1</v>
       </c>
       <c r="R348" s="1" t="n"/>
+      <c r="S348" s="1" t="n"/>
+      <c r="T348" s="1" t="n"/>
+      <c r="U348" s="1" t="n"/>
+      <c r="V348" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W348" s="1" t="n"/>
+      <c r="X348" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -24090,6 +28042,16 @@
         <v>1</v>
       </c>
       <c r="R349" s="1" t="n"/>
+      <c r="S349" s="1" t="n"/>
+      <c r="T349" s="1" t="n"/>
+      <c r="U349" s="1" t="n"/>
+      <c r="V349" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="W349" s="1" t="n"/>
+      <c r="X349" s="1" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -24160,6 +28122,16 @@
         <v>1</v>
       </c>
       <c r="R350" s="1" t="n"/>
+      <c r="S350" s="1" t="n"/>
+      <c r="T350" s="1" t="n"/>
+      <c r="U350" s="1" t="n"/>
+      <c r="V350" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="W350" s="1" t="n"/>
+      <c r="X350" s="1" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -24230,6 +28202,16 @@
         <v>1</v>
       </c>
       <c r="R351" s="1" t="n"/>
+      <c r="S351" s="1" t="n"/>
+      <c r="T351" s="1" t="n"/>
+      <c r="U351" s="1" t="n"/>
+      <c r="V351" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W351" s="1" t="n"/>
+      <c r="X351" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -24300,6 +28282,16 @@
         <v>1</v>
       </c>
       <c r="R352" s="1" t="n"/>
+      <c r="S352" s="1" t="n"/>
+      <c r="T352" s="1" t="n"/>
+      <c r="U352" s="1" t="n"/>
+      <c r="V352" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W352" s="1" t="n"/>
+      <c r="X352" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -24370,6 +28362,16 @@
         <v>1</v>
       </c>
       <c r="R353" s="1" t="n"/>
+      <c r="S353" s="1" t="n"/>
+      <c r="T353" s="1" t="n"/>
+      <c r="U353" s="1" t="n"/>
+      <c r="V353" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W353" s="1" t="n"/>
+      <c r="X353" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -24440,6 +28442,16 @@
         <v>1</v>
       </c>
       <c r="R354" s="1" t="n"/>
+      <c r="S354" s="1" t="n"/>
+      <c r="T354" s="1" t="n"/>
+      <c r="U354" s="1" t="n"/>
+      <c r="V354" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W354" s="1" t="n"/>
+      <c r="X354" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -24510,6 +28522,16 @@
         <v>1</v>
       </c>
       <c r="R355" s="1" t="n"/>
+      <c r="S355" s="1" t="n"/>
+      <c r="T355" s="1" t="n"/>
+      <c r="U355" s="1" t="n"/>
+      <c r="V355" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W355" s="1" t="n"/>
+      <c r="X355" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -24580,6 +28602,16 @@
         <v>1</v>
       </c>
       <c r="R356" s="1" t="n"/>
+      <c r="S356" s="1" t="n"/>
+      <c r="T356" s="1" t="n"/>
+      <c r="U356" s="1" t="n"/>
+      <c r="V356" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W356" s="1" t="n"/>
+      <c r="X356" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -24650,6 +28682,16 @@
         <v>1</v>
       </c>
       <c r="R357" s="1" t="n"/>
+      <c r="S357" s="1" t="n"/>
+      <c r="T357" s="1" t="n"/>
+      <c r="U357" s="1" t="n"/>
+      <c r="V357" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W357" s="1" t="n"/>
+      <c r="X357" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -24720,6 +28762,16 @@
         <v>1</v>
       </c>
       <c r="R358" s="1" t="n"/>
+      <c r="S358" s="1" t="n"/>
+      <c r="T358" s="1" t="n"/>
+      <c r="U358" s="1" t="n"/>
+      <c r="V358" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W358" s="1" t="n"/>
+      <c r="X358" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -24794,6 +28846,18 @@
         <v>1</v>
       </c>
       <c r="R359" s="1" t="n"/>
+      <c r="S359" s="1" t="n"/>
+      <c r="T359" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U359" s="1" t="n"/>
+      <c r="V359" s="1" t="n"/>
+      <c r="W359" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X359" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -24864,6 +28928,16 @@
         <v>1</v>
       </c>
       <c r="R360" s="1" t="n"/>
+      <c r="S360" s="1" t="n"/>
+      <c r="T360" s="1" t="n"/>
+      <c r="U360" s="1" t="n"/>
+      <c r="V360" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W360" s="1" t="n"/>
+      <c r="X360" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -24934,6 +29008,16 @@
         <v>1</v>
       </c>
       <c r="R361" s="1" t="n"/>
+      <c r="S361" s="1" t="n"/>
+      <c r="T361" s="1" t="n"/>
+      <c r="U361" s="1" t="n"/>
+      <c r="V361" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="W361" s="1" t="n"/>
+      <c r="X361" s="1" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -25004,6 +29088,16 @@
         <v>1</v>
       </c>
       <c r="R362" s="1" t="n"/>
+      <c r="S362" s="1" t="n"/>
+      <c r="T362" s="1" t="n"/>
+      <c r="U362" s="1" t="n"/>
+      <c r="V362" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W362" s="1" t="n"/>
+      <c r="X362" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -25074,6 +29168,16 @@
         <v>1</v>
       </c>
       <c r="R363" s="1" t="n"/>
+      <c r="S363" s="1" t="n"/>
+      <c r="T363" s="1" t="n"/>
+      <c r="U363" s="1" t="n"/>
+      <c r="V363" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W363" s="1" t="n"/>
+      <c r="X363" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -25110,6 +29214,18 @@
       <c r="P364" s="1" t="n"/>
       <c r="Q364" s="1" t="n"/>
       <c r="R364" s="1" t="n"/>
+      <c r="S364" s="1" t="n"/>
+      <c r="T364" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U364" s="1" t="n"/>
+      <c r="V364" s="1" t="n"/>
+      <c r="W364" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X364" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -25180,6 +29296,16 @@
         <v>1</v>
       </c>
       <c r="R365" s="1" t="n"/>
+      <c r="S365" s="1" t="n"/>
+      <c r="T365" s="1" t="n"/>
+      <c r="U365" s="1" t="n"/>
+      <c r="V365" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W365" s="1" t="n"/>
+      <c r="X365" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -25250,6 +29376,16 @@
         <v>1</v>
       </c>
       <c r="R366" s="1" t="n"/>
+      <c r="S366" s="1" t="n"/>
+      <c r="T366" s="1" t="n"/>
+      <c r="U366" s="1" t="n"/>
+      <c r="V366" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="W366" s="1" t="n"/>
+      <c r="X366" s="1" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -25324,6 +29460,18 @@
         <v>1</v>
       </c>
       <c r="R367" s="1" t="n"/>
+      <c r="S367" s="1" t="n"/>
+      <c r="T367" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U367" s="1" t="n"/>
+      <c r="V367" s="1" t="n"/>
+      <c r="W367" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X367" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -25394,6 +29542,16 @@
         <v>1</v>
       </c>
       <c r="R368" s="1" t="n"/>
+      <c r="S368" s="1" t="n"/>
+      <c r="T368" s="1" t="n"/>
+      <c r="U368" s="1" t="n"/>
+      <c r="V368" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W368" s="1" t="n"/>
+      <c r="X368" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -25464,6 +29622,16 @@
         <v>1</v>
       </c>
       <c r="R369" s="1" t="n"/>
+      <c r="S369" s="1" t="n"/>
+      <c r="T369" s="1" t="n"/>
+      <c r="U369" s="1" t="n"/>
+      <c r="V369" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W369" s="1" t="n"/>
+      <c r="X369" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -25534,6 +29702,16 @@
         <v>1</v>
       </c>
       <c r="R370" s="1" t="n"/>
+      <c r="S370" s="1" t="n"/>
+      <c r="T370" s="1" t="n"/>
+      <c r="U370" s="1" t="n"/>
+      <c r="V370" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W370" s="1" t="n"/>
+      <c r="X370" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -25606,6 +29784,16 @@
       <c r="P371" s="1" t="n"/>
       <c r="Q371" s="1" t="n"/>
       <c r="R371" s="1" t="n"/>
+      <c r="S371" s="1" t="n"/>
+      <c r="T371" s="1" t="n"/>
+      <c r="U371" s="1" t="n"/>
+      <c r="V371" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="W371" s="1" t="n"/>
+      <c r="X371" s="1" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -25676,6 +29864,16 @@
         <v>1</v>
       </c>
       <c r="R372" s="1" t="n"/>
+      <c r="S372" s="1" t="n"/>
+      <c r="T372" s="1" t="n"/>
+      <c r="U372" s="1" t="n"/>
+      <c r="V372" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="W372" s="1" t="n"/>
+      <c r="X372" s="1" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -25746,6 +29944,16 @@
         <v>1</v>
       </c>
       <c r="R373" s="1" t="n"/>
+      <c r="S373" s="1" t="n"/>
+      <c r="T373" s="1" t="n"/>
+      <c r="U373" s="1" t="n"/>
+      <c r="V373" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W373" s="1" t="n"/>
+      <c r="X373" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -25816,6 +30024,16 @@
         <v>1</v>
       </c>
       <c r="R374" s="1" t="n"/>
+      <c r="S374" s="1" t="n"/>
+      <c r="T374" s="1" t="n"/>
+      <c r="U374" s="1" t="n"/>
+      <c r="V374" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W374" s="1" t="n"/>
+      <c r="X374" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -25890,6 +30108,18 @@
         <v>1</v>
       </c>
       <c r="R375" s="1" t="n"/>
+      <c r="S375" s="1" t="n"/>
+      <c r="T375" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U375" s="1" t="n"/>
+      <c r="V375" s="1" t="n"/>
+      <c r="W375" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X375" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -25964,6 +30194,18 @@
         <v>1</v>
       </c>
       <c r="R376" s="1" t="n"/>
+      <c r="S376" s="1" t="n"/>
+      <c r="T376" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U376" s="1" t="n"/>
+      <c r="V376" s="1" t="n"/>
+      <c r="W376" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X376" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -26038,6 +30280,18 @@
         <v>1</v>
       </c>
       <c r="R377" s="1" t="n"/>
+      <c r="S377" s="1" t="n"/>
+      <c r="T377" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U377" s="1" t="n"/>
+      <c r="V377" s="1" t="n"/>
+      <c r="W377" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X377" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -26108,6 +30362,16 @@
         <v>1</v>
       </c>
       <c r="R378" s="1" t="n"/>
+      <c r="S378" s="1" t="n"/>
+      <c r="T378" s="1" t="n"/>
+      <c r="U378" s="1" t="n"/>
+      <c r="V378" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="W378" s="1" t="n"/>
+      <c r="X378" s="1" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -26144,6 +30408,14 @@
       <c r="P379" s="1" t="n"/>
       <c r="Q379" s="1" t="n"/>
       <c r="R379" s="1" t="n"/>
+      <c r="S379" s="1" t="n"/>
+      <c r="T379" s="1" t="n"/>
+      <c r="U379" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V379" s="1" t="n"/>
+      <c r="W379" s="1" t="n"/>
+      <c r="X379" s="1" t="n"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -26218,6 +30490,18 @@
         <v>1</v>
       </c>
       <c r="R380" s="1" t="n"/>
+      <c r="S380" s="1" t="n"/>
+      <c r="T380" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U380" s="1" t="n"/>
+      <c r="V380" s="1" t="n"/>
+      <c r="W380" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X380" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -26292,6 +30576,18 @@
         <v>1</v>
       </c>
       <c r="R381" s="1" t="n"/>
+      <c r="S381" s="1" t="n"/>
+      <c r="T381" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U381" s="1" t="n"/>
+      <c r="V381" s="1" t="n"/>
+      <c r="W381" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X381" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -26362,6 +30658,16 @@
         <v>1</v>
       </c>
       <c r="R382" s="1" t="n"/>
+      <c r="S382" s="1" t="n"/>
+      <c r="T382" s="1" t="n"/>
+      <c r="U382" s="1" t="n"/>
+      <c r="V382" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W382" s="1" t="n"/>
+      <c r="X382" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -26430,6 +30736,16 @@
       <c r="P383" s="1" t="n"/>
       <c r="Q383" s="1" t="n"/>
       <c r="R383" s="1" t="n"/>
+      <c r="S383" s="1" t="n"/>
+      <c r="T383" s="1" t="n"/>
+      <c r="U383" s="1" t="n"/>
+      <c r="V383" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="W383" s="1" t="n"/>
+      <c r="X383" s="1" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -26500,6 +30816,16 @@
         <v>1</v>
       </c>
       <c r="R384" s="1" t="n"/>
+      <c r="S384" s="1" t="n"/>
+      <c r="T384" s="1" t="n"/>
+      <c r="U384" s="1" t="n"/>
+      <c r="V384" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W384" s="1" t="n"/>
+      <c r="X384" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -26570,6 +30896,16 @@
         <v>1</v>
       </c>
       <c r="R385" s="1" t="n"/>
+      <c r="S385" s="1" t="n"/>
+      <c r="T385" s="1" t="n"/>
+      <c r="U385" s="1" t="n"/>
+      <c r="V385" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W385" s="1" t="n"/>
+      <c r="X385" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -26644,6 +30980,18 @@
         <v>1</v>
       </c>
       <c r="R386" s="1" t="n"/>
+      <c r="S386" s="1" t="n"/>
+      <c r="T386" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U386" s="1" t="n"/>
+      <c r="V386" s="1" t="n"/>
+      <c r="W386" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X386" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -26718,6 +31066,18 @@
         <v>1</v>
       </c>
       <c r="R387" s="1" t="n"/>
+      <c r="S387" s="1" t="n"/>
+      <c r="T387" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U387" s="1" t="n"/>
+      <c r="V387" s="1" t="n"/>
+      <c r="W387" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X387" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -26788,6 +31148,16 @@
         <v>1</v>
       </c>
       <c r="R388" s="1" t="n"/>
+      <c r="S388" s="1" t="n"/>
+      <c r="T388" s="1" t="n"/>
+      <c r="U388" s="1" t="n"/>
+      <c r="V388" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W388" s="1" t="n"/>
+      <c r="X388" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -26858,6 +31228,16 @@
         <v>1</v>
       </c>
       <c r="R389" s="1" t="n"/>
+      <c r="S389" s="1" t="n"/>
+      <c r="T389" s="1" t="n"/>
+      <c r="U389" s="1" t="n"/>
+      <c r="V389" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W389" s="1" t="n"/>
+      <c r="X389" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -26894,6 +31274,14 @@
       <c r="P390" s="1" t="n"/>
       <c r="Q390" s="1" t="n"/>
       <c r="R390" s="1" t="n"/>
+      <c r="S390" s="1" t="n"/>
+      <c r="T390" s="1" t="n"/>
+      <c r="U390" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V390" s="1" t="n"/>
+      <c r="W390" s="1" t="n"/>
+      <c r="X390" s="1" t="n"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -26968,6 +31356,18 @@
         <v>1</v>
       </c>
       <c r="R391" s="1" t="n"/>
+      <c r="S391" s="1" t="n"/>
+      <c r="T391" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U391" s="1" t="n"/>
+      <c r="V391" s="1" t="n"/>
+      <c r="W391" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="X391" s="1" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -27004,6 +31404,14 @@
       <c r="P392" s="1" t="n"/>
       <c r="Q392" s="1" t="n"/>
       <c r="R392" s="1" t="n"/>
+      <c r="S392" s="1" t="n"/>
+      <c r="T392" s="1" t="n"/>
+      <c r="U392" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V392" s="1" t="n"/>
+      <c r="W392" s="1" t="n"/>
+      <c r="X392" s="1" t="n"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -27074,6 +31482,16 @@
         <v>1</v>
       </c>
       <c r="R393" s="1" t="n"/>
+      <c r="S393" s="1" t="n"/>
+      <c r="T393" s="1" t="n"/>
+      <c r="U393" s="1" t="n"/>
+      <c r="V393" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W393" s="1" t="n"/>
+      <c r="X393" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -27144,6 +31562,16 @@
         <v>1</v>
       </c>
       <c r="R394" s="1" t="n"/>
+      <c r="S394" s="1" t="n"/>
+      <c r="T394" s="1" t="n"/>
+      <c r="U394" s="1" t="n"/>
+      <c r="V394" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W394" s="1" t="n"/>
+      <c r="X394" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -27180,6 +31608,14 @@
       <c r="P395" s="1" t="n"/>
       <c r="Q395" s="1" t="n"/>
       <c r="R395" s="1" t="n"/>
+      <c r="S395" s="1" t="n"/>
+      <c r="T395" s="1" t="n"/>
+      <c r="U395" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V395" s="1" t="n"/>
+      <c r="W395" s="1" t="n"/>
+      <c r="X395" s="1" t="n"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -27250,6 +31686,16 @@
         <v>1</v>
       </c>
       <c r="R396" s="1" t="n"/>
+      <c r="S396" s="1" t="n"/>
+      <c r="T396" s="1" t="n"/>
+      <c r="U396" s="1" t="n"/>
+      <c r="V396" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W396" s="1" t="n"/>
+      <c r="X396" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -27320,6 +31766,16 @@
         <v>1</v>
       </c>
       <c r="R397" s="1" t="n"/>
+      <c r="S397" s="1" t="n"/>
+      <c r="T397" s="1" t="n"/>
+      <c r="U397" s="1" t="n"/>
+      <c r="V397" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W397" s="1" t="n"/>
+      <c r="X397" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -27390,6 +31846,16 @@
         <v>1</v>
       </c>
       <c r="R398" s="1" t="n"/>
+      <c r="S398" s="1" t="n"/>
+      <c r="T398" s="1" t="n"/>
+      <c r="U398" s="1" t="n"/>
+      <c r="V398" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W398" s="1" t="n"/>
+      <c r="X398" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -27460,6 +31926,16 @@
         <v>1</v>
       </c>
       <c r="R399" s="1" t="n"/>
+      <c r="S399" s="1" t="n"/>
+      <c r="T399" s="1" t="n"/>
+      <c r="U399" s="1" t="n"/>
+      <c r="V399" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W399" s="1" t="n"/>
+      <c r="X399" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -27530,6 +32006,16 @@
         <v>1</v>
       </c>
       <c r="R400" s="1" t="n"/>
+      <c r="S400" s="1" t="n"/>
+      <c r="T400" s="1" t="n"/>
+      <c r="U400" s="1" t="n"/>
+      <c r="V400" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W400" s="1" t="n"/>
+      <c r="X400" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -27600,6 +32086,16 @@
         <v>1</v>
       </c>
       <c r="R401" s="1" t="n"/>
+      <c r="S401" s="1" t="n"/>
+      <c r="T401" s="1" t="n"/>
+      <c r="U401" s="1" t="n"/>
+      <c r="V401" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="W401" s="1" t="n"/>
+      <c r="X401" s="1" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -27670,6 +32166,16 @@
         <v>1</v>
       </c>
       <c r="R402" s="1" t="n"/>
+      <c r="S402" s="1" t="n"/>
+      <c r="T402" s="1" t="n"/>
+      <c r="U402" s="1" t="n"/>
+      <c r="V402" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="W402" s="1" t="n"/>
+      <c r="X402" s="1" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -27740,6 +32246,16 @@
         <v>1</v>
       </c>
       <c r="R403" s="1" t="n"/>
+      <c r="S403" s="1" t="n"/>
+      <c r="T403" s="1" t="n"/>
+      <c r="U403" s="1" t="n"/>
+      <c r="V403" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="W403" s="1" t="n"/>
+      <c r="X403" s="1" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -27810,6 +32326,16 @@
         <v>1</v>
       </c>
       <c r="R404" s="1" t="n"/>
+      <c r="S404" s="1" t="n"/>
+      <c r="T404" s="1" t="n"/>
+      <c r="U404" s="1" t="n"/>
+      <c r="V404" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W404" s="1" t="n"/>
+      <c r="X404" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -27880,6 +32406,16 @@
         <v>1</v>
       </c>
       <c r="R405" s="1" t="n"/>
+      <c r="S405" s="1" t="n"/>
+      <c r="T405" s="1" t="n"/>
+      <c r="U405" s="1" t="n"/>
+      <c r="V405" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W405" s="1" t="n"/>
+      <c r="X405" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -27948,6 +32484,16 @@
         <v>1</v>
       </c>
       <c r="R406" s="1" t="n"/>
+      <c r="S406" s="1" t="n"/>
+      <c r="T406" s="1" t="n"/>
+      <c r="U406" s="1" t="n"/>
+      <c r="V406" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W406" s="1" t="n"/>
+      <c r="X406" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -28016,6 +32562,16 @@
         <v>1</v>
       </c>
       <c r="R407" s="1" t="n"/>
+      <c r="S407" s="1" t="n"/>
+      <c r="T407" s="1" t="n"/>
+      <c r="U407" s="1" t="n"/>
+      <c r="V407" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="W407" s="1" t="n"/>
+      <c r="X407" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -28084,6 +32640,16 @@
         <v>1</v>
       </c>
       <c r="R408" s="1" t="n"/>
+      <c r="S408" s="1" t="n"/>
+      <c r="T408" s="1" t="n"/>
+      <c r="U408" s="1" t="n"/>
+      <c r="V408" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W408" s="1" t="n"/>
+      <c r="X408" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -28152,6 +32718,16 @@
         <v>1</v>
       </c>
       <c r="R409" s="1" t="n"/>
+      <c r="S409" s="1" t="n"/>
+      <c r="T409" s="1" t="n"/>
+      <c r="U409" s="1" t="n"/>
+      <c r="V409" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="W409" s="1" t="n"/>
+      <c r="X409" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -28220,6 +32796,16 @@
         <v>1</v>
       </c>
       <c r="R410" s="1" t="n"/>
+      <c r="S410" s="1" t="n"/>
+      <c r="T410" s="1" t="n"/>
+      <c r="U410" s="1" t="n"/>
+      <c r="V410" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="W410" s="1" t="n"/>
+      <c r="X410" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -28288,6 +32874,18 @@
         <v>1</v>
       </c>
       <c r="R411" s="1" t="n"/>
+      <c r="S411" s="1" t="n"/>
+      <c r="T411" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U411" s="1" t="n"/>
+      <c r="V411" s="1" t="n"/>
+      <c r="W411" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X411" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -28356,6 +32954,16 @@
         <v>1</v>
       </c>
       <c r="R412" s="1" t="n"/>
+      <c r="S412" s="1" t="n"/>
+      <c r="T412" s="1" t="n"/>
+      <c r="U412" s="1" t="n"/>
+      <c r="V412" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="W412" s="1" t="n"/>
+      <c r="X412" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -28432,6 +33040,16 @@
         <v>1</v>
       </c>
       <c r="R413" s="1" t="n"/>
+      <c r="S413" s="1" t="n"/>
+      <c r="T413" s="1" t="n"/>
+      <c r="U413" s="1" t="n"/>
+      <c r="V413" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="W413" s="1" t="n"/>
+      <c r="X413" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -28504,6 +33122,16 @@
         <v>1</v>
       </c>
       <c r="R414" s="1" t="n"/>
+      <c r="S414" s="1" t="n"/>
+      <c r="T414" s="1" t="n"/>
+      <c r="U414" s="1" t="n"/>
+      <c r="V414" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="W414" s="1" t="n"/>
+      <c r="X414" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -28576,6 +33204,16 @@
         <v>1</v>
       </c>
       <c r="R415" s="1" t="n"/>
+      <c r="S415" s="1" t="n"/>
+      <c r="T415" s="1" t="n"/>
+      <c r="U415" s="1" t="n"/>
+      <c r="V415" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W415" s="1" t="n"/>
+      <c r="X415" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -28652,6 +33290,16 @@
         <v>1</v>
       </c>
       <c r="R416" s="1" t="n"/>
+      <c r="S416" s="1" t="n"/>
+      <c r="T416" s="1" t="n"/>
+      <c r="U416" s="1" t="n"/>
+      <c r="V416" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W416" s="1" t="n"/>
+      <c r="X416" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -28728,6 +33376,16 @@
         <v>1</v>
       </c>
       <c r="R417" s="1" t="n"/>
+      <c r="S417" s="1" t="n"/>
+      <c r="T417" s="1" t="n"/>
+      <c r="U417" s="1" t="n"/>
+      <c r="V417" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W417" s="1" t="n"/>
+      <c r="X417" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -28804,6 +33462,16 @@
         <v>1</v>
       </c>
       <c r="R418" s="1" t="n"/>
+      <c r="S418" s="1" t="n"/>
+      <c r="T418" s="1" t="n"/>
+      <c r="U418" s="1" t="n"/>
+      <c r="V418" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="W418" s="1" t="n"/>
+      <c r="X418" s="1" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -28876,6 +33544,18 @@
       <c r="R419" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S419" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T419" s="1" t="n"/>
+      <c r="U419" s="1" t="n"/>
+      <c r="V419" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W419" s="1" t="n"/>
+      <c r="X419" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -28948,6 +33628,16 @@
         <v>1</v>
       </c>
       <c r="R420" s="1" t="n"/>
+      <c r="S420" s="1" t="n"/>
+      <c r="T420" s="1" t="n"/>
+      <c r="U420" s="1" t="n"/>
+      <c r="V420" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W420" s="1" t="n"/>
+      <c r="X420" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -29020,6 +33710,18 @@
         <v>1</v>
       </c>
       <c r="R421" s="1" t="n"/>
+      <c r="S421" s="1" t="n"/>
+      <c r="T421" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U421" s="1" t="n"/>
+      <c r="V421" s="1" t="n"/>
+      <c r="W421" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X421" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -29092,6 +33794,18 @@
       <c r="R422" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S422" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T422" s="1" t="n"/>
+      <c r="U422" s="1" t="n"/>
+      <c r="V422" s="1" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W422" s="1" t="n"/>
+      <c r="X422" s="1" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -29168,6 +33882,18 @@
       <c r="R423" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S423" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T423" s="1" t="n"/>
+      <c r="U423" s="1" t="n"/>
+      <c r="V423" s="1" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W423" s="1" t="n"/>
+      <c r="X423" s="1" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -29244,6 +33970,18 @@
       <c r="R424" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S424" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T424" s="1" t="n"/>
+      <c r="U424" s="1" t="n"/>
+      <c r="V424" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W424" s="1" t="n"/>
+      <c r="X424" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -29316,6 +34054,18 @@
       <c r="R425" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S425" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T425" s="1" t="n"/>
+      <c r="U425" s="1" t="n"/>
+      <c r="V425" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W425" s="1" t="n"/>
+      <c r="X425" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -29392,6 +34142,18 @@
       <c r="R426" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S426" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T426" s="1" t="n"/>
+      <c r="U426" s="1" t="n"/>
+      <c r="V426" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W426" s="1" t="n"/>
+      <c r="X426" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -29464,6 +34226,16 @@
         <v>1</v>
       </c>
       <c r="R427" s="1" t="n"/>
+      <c r="S427" s="1" t="n"/>
+      <c r="T427" s="1" t="n"/>
+      <c r="U427" s="1" t="n"/>
+      <c r="V427" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="W427" s="1" t="n"/>
+      <c r="X427" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -29540,6 +34312,16 @@
         <v>1</v>
       </c>
       <c r="R428" s="1" t="n"/>
+      <c r="S428" s="1" t="n"/>
+      <c r="T428" s="1" t="n"/>
+      <c r="U428" s="1" t="n"/>
+      <c r="V428" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="W428" s="1" t="n"/>
+      <c r="X428" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -29616,6 +34398,16 @@
         <v>1</v>
       </c>
       <c r="R429" s="1" t="n"/>
+      <c r="S429" s="1" t="n"/>
+      <c r="T429" s="1" t="n"/>
+      <c r="U429" s="1" t="n"/>
+      <c r="V429" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="W429" s="1" t="n"/>
+      <c r="X429" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -29688,6 +34480,16 @@
         <v>1</v>
       </c>
       <c r="R430" s="1" t="n"/>
+      <c r="S430" s="1" t="n"/>
+      <c r="T430" s="1" t="n"/>
+      <c r="U430" s="1" t="n"/>
+      <c r="V430" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W430" s="1" t="n"/>
+      <c r="X430" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -29760,6 +34562,16 @@
         <v>1</v>
       </c>
       <c r="R431" s="1" t="n"/>
+      <c r="S431" s="1" t="n"/>
+      <c r="T431" s="1" t="n"/>
+      <c r="U431" s="1" t="n"/>
+      <c r="V431" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="W431" s="1" t="n"/>
+      <c r="X431" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -29832,6 +34644,16 @@
         <v>1</v>
       </c>
       <c r="R432" s="1" t="n"/>
+      <c r="S432" s="1" t="n"/>
+      <c r="T432" s="1" t="n"/>
+      <c r="U432" s="1" t="n"/>
+      <c r="V432" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="W432" s="1" t="n"/>
+      <c r="X432" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -29904,6 +34726,16 @@
         <v>1</v>
       </c>
       <c r="R433" s="1" t="n"/>
+      <c r="S433" s="1" t="n"/>
+      <c r="T433" s="1" t="n"/>
+      <c r="U433" s="1" t="n"/>
+      <c r="V433" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W433" s="1" t="n"/>
+      <c r="X433" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -29976,6 +34808,16 @@
         <v>1</v>
       </c>
       <c r="R434" s="1" t="n"/>
+      <c r="S434" s="1" t="n"/>
+      <c r="T434" s="1" t="n"/>
+      <c r="U434" s="1" t="n"/>
+      <c r="V434" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="W434" s="1" t="n"/>
+      <c r="X434" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -30048,6 +34890,16 @@
         <v>1</v>
       </c>
       <c r="R435" s="1" t="n"/>
+      <c r="S435" s="1" t="n"/>
+      <c r="T435" s="1" t="n"/>
+      <c r="U435" s="1" t="n"/>
+      <c r="V435" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="W435" s="1" t="n"/>
+      <c r="X435" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -30120,6 +34972,16 @@
         <v>1</v>
       </c>
       <c r="R436" s="1" t="n"/>
+      <c r="S436" s="1" t="n"/>
+      <c r="T436" s="1" t="n"/>
+      <c r="U436" s="1" t="n"/>
+      <c r="V436" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="W436" s="1" t="n"/>
+      <c r="X436" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -30188,6 +35050,18 @@
       <c r="P437" s="1" t="n"/>
       <c r="Q437" s="1" t="n"/>
       <c r="R437" s="1" t="n"/>
+      <c r="S437" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T437" s="1" t="n"/>
+      <c r="U437" s="1" t="n"/>
+      <c r="V437" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W437" s="1" t="n"/>
+      <c r="X437" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -30262,6 +35136,16 @@
       <c r="P438" s="1" t="n"/>
       <c r="Q438" s="1" t="n"/>
       <c r="R438" s="1" t="n"/>
+      <c r="S438" s="1" t="n"/>
+      <c r="T438" s="1" t="n"/>
+      <c r="U438" s="1" t="n"/>
+      <c r="V438" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="W438" s="1" t="n"/>
+      <c r="X438" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -30336,6 +35220,16 @@
       <c r="P439" s="1" t="n"/>
       <c r="Q439" s="1" t="n"/>
       <c r="R439" s="1" t="n"/>
+      <c r="S439" s="1" t="n"/>
+      <c r="T439" s="1" t="n"/>
+      <c r="U439" s="1" t="n"/>
+      <c r="V439" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W439" s="1" t="n"/>
+      <c r="X439" s="1" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -30402,6 +35296,16 @@
       <c r="P440" s="1" t="n"/>
       <c r="Q440" s="1" t="n"/>
       <c r="R440" s="1" t="n"/>
+      <c r="S440" s="1" t="n"/>
+      <c r="T440" s="1" t="n"/>
+      <c r="U440" s="1" t="n"/>
+      <c r="V440" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="W440" s="1" t="n"/>
+      <c r="X440" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -30476,6 +35380,16 @@
       <c r="P441" s="1" t="n"/>
       <c r="Q441" s="1" t="n"/>
       <c r="R441" s="1" t="n"/>
+      <c r="S441" s="1" t="n"/>
+      <c r="T441" s="1" t="n"/>
+      <c r="U441" s="1" t="n"/>
+      <c r="V441" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="W441" s="1" t="n"/>
+      <c r="X441" s="1" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -30550,6 +35464,16 @@
       <c r="P442" s="1" t="n"/>
       <c r="Q442" s="1" t="n"/>
       <c r="R442" s="1" t="n"/>
+      <c r="S442" s="1" t="n"/>
+      <c r="T442" s="1" t="n"/>
+      <c r="U442" s="1" t="n"/>
+      <c r="V442" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W442" s="1" t="n"/>
+      <c r="X442" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -30616,6 +35540,16 @@
       <c r="P443" s="1" t="n"/>
       <c r="Q443" s="1" t="n"/>
       <c r="R443" s="1" t="n"/>
+      <c r="S443" s="1" t="n"/>
+      <c r="T443" s="1" t="n"/>
+      <c r="U443" s="1" t="n"/>
+      <c r="V443" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W443" s="1" t="n"/>
+      <c r="X443" s="1" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -30682,6 +35616,16 @@
       <c r="P444" s="1" t="n"/>
       <c r="Q444" s="1" t="n"/>
       <c r="R444" s="1" t="n"/>
+      <c r="S444" s="1" t="n"/>
+      <c r="T444" s="1" t="n"/>
+      <c r="U444" s="1" t="n"/>
+      <c r="V444" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="W444" s="1" t="n"/>
+      <c r="X444" s="1" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -30748,6 +35692,16 @@
       <c r="P445" s="1" t="n"/>
       <c r="Q445" s="1" t="n"/>
       <c r="R445" s="1" t="n"/>
+      <c r="S445" s="1" t="n"/>
+      <c r="T445" s="1" t="n"/>
+      <c r="U445" s="1" t="n"/>
+      <c r="V445" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W445" s="1" t="n"/>
+      <c r="X445" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -30814,6 +35768,16 @@
       </c>
       <c r="Q446" s="1" t="n"/>
       <c r="R446" s="1" t="n"/>
+      <c r="S446" s="1" t="n"/>
+      <c r="T446" s="1" t="n"/>
+      <c r="U446" s="1" t="n"/>
+      <c r="V446" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W446" s="1" t="n"/>
+      <c r="X446" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -30880,6 +35844,16 @@
       </c>
       <c r="Q447" s="1" t="n"/>
       <c r="R447" s="1" t="n"/>
+      <c r="S447" s="1" t="n"/>
+      <c r="T447" s="1" t="n"/>
+      <c r="U447" s="1" t="n"/>
+      <c r="V447" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W447" s="1" t="n"/>
+      <c r="X447" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -30954,6 +35928,18 @@
       </c>
       <c r="Q448" s="1" t="n"/>
       <c r="R448" s="1" t="n"/>
+      <c r="S448" s="1" t="n"/>
+      <c r="T448" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U448" s="1" t="n"/>
+      <c r="V448" s="1" t="n"/>
+      <c r="W448" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="X448" s="1" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -31024,6 +36010,16 @@
       </c>
       <c r="Q449" s="1" t="n"/>
       <c r="R449" s="1" t="n"/>
+      <c r="S449" s="1" t="n"/>
+      <c r="T449" s="1" t="n"/>
+      <c r="U449" s="1" t="n"/>
+      <c r="V449" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W449" s="1" t="n"/>
+      <c r="X449" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -31094,6 +36090,16 @@
       </c>
       <c r="Q450" s="1" t="n"/>
       <c r="R450" s="1" t="n"/>
+      <c r="S450" s="1" t="n"/>
+      <c r="T450" s="1" t="n"/>
+      <c r="U450" s="1" t="n"/>
+      <c r="V450" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="W450" s="1" t="n"/>
+      <c r="X450" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -31164,6 +36170,16 @@
       </c>
       <c r="Q451" s="1" t="n"/>
       <c r="R451" s="1" t="n"/>
+      <c r="S451" s="1" t="n"/>
+      <c r="T451" s="1" t="n"/>
+      <c r="U451" s="1" t="n"/>
+      <c r="V451" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="W451" s="1" t="n"/>
+      <c r="X451" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -31234,6 +36250,18 @@
       </c>
       <c r="Q452" s="1" t="n"/>
       <c r="R452" s="1" t="n"/>
+      <c r="S452" s="1" t="n"/>
+      <c r="T452" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U452" s="1" t="n"/>
+      <c r="V452" s="1" t="n"/>
+      <c r="W452" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="X452" s="1" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -31298,6 +36326,16 @@
       <c r="P453" s="1" t="n"/>
       <c r="Q453" s="1" t="n"/>
       <c r="R453" s="1" t="n"/>
+      <c r="S453" s="1" t="n"/>
+      <c r="T453" s="1" t="n"/>
+      <c r="U453" s="1" t="n"/>
+      <c r="V453" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W453" s="1" t="n"/>
+      <c r="X453" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -31362,6 +36400,16 @@
       <c r="P454" s="1" t="n"/>
       <c r="Q454" s="1" t="n"/>
       <c r="R454" s="1" t="n"/>
+      <c r="S454" s="1" t="n"/>
+      <c r="T454" s="1" t="n"/>
+      <c r="U454" s="1" t="n"/>
+      <c r="V454" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W454" s="1" t="n"/>
+      <c r="X454" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -31426,6 +36474,16 @@
       <c r="P455" s="1" t="n"/>
       <c r="Q455" s="1" t="n"/>
       <c r="R455" s="1" t="n"/>
+      <c r="S455" s="1" t="n"/>
+      <c r="T455" s="1" t="n"/>
+      <c r="U455" s="1" t="n"/>
+      <c r="V455" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W455" s="1" t="n"/>
+      <c r="X455" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -31494,6 +36552,16 @@
       <c r="P456" s="1" t="n"/>
       <c r="Q456" s="1" t="n"/>
       <c r="R456" s="1" t="n"/>
+      <c r="S456" s="1" t="n"/>
+      <c r="T456" s="1" t="n"/>
+      <c r="U456" s="1" t="n"/>
+      <c r="V456" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W456" s="1" t="n"/>
+      <c r="X456" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -31562,6 +36630,16 @@
       <c r="P457" s="1" t="n"/>
       <c r="Q457" s="1" t="n"/>
       <c r="R457" s="1" t="n"/>
+      <c r="S457" s="1" t="n"/>
+      <c r="T457" s="1" t="n"/>
+      <c r="U457" s="1" t="n"/>
+      <c r="V457" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W457" s="1" t="n"/>
+      <c r="X457" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -31626,6 +36704,16 @@
       <c r="P458" s="1" t="n"/>
       <c r="Q458" s="1" t="n"/>
       <c r="R458" s="1" t="n"/>
+      <c r="S458" s="1" t="n"/>
+      <c r="T458" s="1" t="n"/>
+      <c r="U458" s="1" t="n"/>
+      <c r="V458" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W458" s="1" t="n"/>
+      <c r="X458" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -31690,6 +36778,18 @@
       <c r="P459" s="1" t="n"/>
       <c r="Q459" s="1" t="n"/>
       <c r="R459" s="1" t="n"/>
+      <c r="S459" s="1" t="n"/>
+      <c r="T459" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U459" s="1" t="n"/>
+      <c r="V459" s="1" t="n"/>
+      <c r="W459" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X459" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -31758,6 +36858,16 @@
       <c r="P460" s="1" t="n"/>
       <c r="Q460" s="1" t="n"/>
       <c r="R460" s="1" t="n"/>
+      <c r="S460" s="1" t="n"/>
+      <c r="T460" s="1" t="n"/>
+      <c r="U460" s="1" t="n"/>
+      <c r="V460" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W460" s="1" t="n"/>
+      <c r="X460" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -31822,6 +36932,18 @@
       <c r="P461" s="1" t="n"/>
       <c r="Q461" s="1" t="n"/>
       <c r="R461" s="1" t="n"/>
+      <c r="S461" s="1" t="n"/>
+      <c r="T461" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U461" s="1" t="n"/>
+      <c r="V461" s="1" t="n"/>
+      <c r="W461" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X461" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -31890,6 +37012,18 @@
       <c r="P462" s="1" t="n"/>
       <c r="Q462" s="1" t="n"/>
       <c r="R462" s="1" t="n"/>
+      <c r="S462" s="1" t="n"/>
+      <c r="T462" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U462" s="1" t="n"/>
+      <c r="V462" s="1" t="n"/>
+      <c r="W462" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X462" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -31958,6 +37092,18 @@
       <c r="P463" s="1" t="n"/>
       <c r="Q463" s="1" t="n"/>
       <c r="R463" s="1" t="n"/>
+      <c r="S463" s="1" t="n"/>
+      <c r="T463" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U463" s="1" t="n"/>
+      <c r="V463" s="1" t="n"/>
+      <c r="W463" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X463" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -32026,6 +37172,16 @@
       <c r="P464" s="1" t="n"/>
       <c r="Q464" s="1" t="n"/>
       <c r="R464" s="1" t="n"/>
+      <c r="S464" s="1" t="n"/>
+      <c r="T464" s="1" t="n"/>
+      <c r="U464" s="1" t="n"/>
+      <c r="V464" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W464" s="1" t="n"/>
+      <c r="X464" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -32062,6 +37218,18 @@
       <c r="P465" s="1" t="n"/>
       <c r="Q465" s="1" t="n"/>
       <c r="R465" s="1" t="n"/>
+      <c r="S465" s="1" t="n"/>
+      <c r="T465" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U465" s="1" t="n"/>
+      <c r="V465" s="1" t="n"/>
+      <c r="W465" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X465" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -32126,6 +37294,18 @@
       <c r="P466" s="1" t="n"/>
       <c r="Q466" s="1" t="n"/>
       <c r="R466" s="1" t="n"/>
+      <c r="S466" s="1" t="n"/>
+      <c r="T466" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U466" s="1" t="n"/>
+      <c r="V466" s="1" t="n"/>
+      <c r="W466" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X466" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -32194,6 +37374,18 @@
       <c r="P467" s="1" t="n"/>
       <c r="Q467" s="1" t="n"/>
       <c r="R467" s="1" t="n"/>
+      <c r="S467" s="1" t="n"/>
+      <c r="T467" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U467" s="1" t="n"/>
+      <c r="V467" s="1" t="n"/>
+      <c r="W467" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="X467" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -32230,6 +37422,18 @@
       <c r="P468" s="1" t="n"/>
       <c r="Q468" s="1" t="n"/>
       <c r="R468" s="1" t="n"/>
+      <c r="S468" s="1" t="n"/>
+      <c r="T468" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U468" s="1" t="n"/>
+      <c r="V468" s="1" t="n"/>
+      <c r="W468" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X468" s="1" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -32304,6 +37508,16 @@
       </c>
       <c r="Q469" s="1" t="n"/>
       <c r="R469" s="1" t="n"/>
+      <c r="S469" s="1" t="n"/>
+      <c r="T469" s="1" t="n"/>
+      <c r="U469" s="1" t="n"/>
+      <c r="V469" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W469" s="1" t="n"/>
+      <c r="X469" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -32378,6 +37592,16 @@
       </c>
       <c r="Q470" s="1" t="n"/>
       <c r="R470" s="1" t="n"/>
+      <c r="S470" s="1" t="n"/>
+      <c r="T470" s="1" t="n"/>
+      <c r="U470" s="1" t="n"/>
+      <c r="V470" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W470" s="1" t="n"/>
+      <c r="X470" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -32448,6 +37672,16 @@
       </c>
       <c r="Q471" s="1" t="n"/>
       <c r="R471" s="1" t="n"/>
+      <c r="S471" s="1" t="n"/>
+      <c r="T471" s="1" t="n"/>
+      <c r="U471" s="1" t="n"/>
+      <c r="V471" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W471" s="1" t="n"/>
+      <c r="X471" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -32522,6 +37756,16 @@
       </c>
       <c r="Q472" s="1" t="n"/>
       <c r="R472" s="1" t="n"/>
+      <c r="S472" s="1" t="n"/>
+      <c r="T472" s="1" t="n"/>
+      <c r="U472" s="1" t="n"/>
+      <c r="V472" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W472" s="1" t="n"/>
+      <c r="X472" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -32592,6 +37836,16 @@
       </c>
       <c r="Q473" s="1" t="n"/>
       <c r="R473" s="1" t="n"/>
+      <c r="S473" s="1" t="n"/>
+      <c r="T473" s="1" t="n"/>
+      <c r="U473" s="1" t="n"/>
+      <c r="V473" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W473" s="1" t="n"/>
+      <c r="X473" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -32666,6 +37920,18 @@
       </c>
       <c r="Q474" s="1" t="n"/>
       <c r="R474" s="1" t="n"/>
+      <c r="S474" s="1" t="n"/>
+      <c r="T474" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U474" s="1" t="n"/>
+      <c r="V474" s="1" t="n"/>
+      <c r="W474" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X474" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -32736,6 +38002,16 @@
       </c>
       <c r="Q475" s="1" t="n"/>
       <c r="R475" s="1" t="n"/>
+      <c r="S475" s="1" t="n"/>
+      <c r="T475" s="1" t="n"/>
+      <c r="U475" s="1" t="n"/>
+      <c r="V475" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W475" s="1" t="n"/>
+      <c r="X475" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -32810,6 +38086,16 @@
       </c>
       <c r="Q476" s="1" t="n"/>
       <c r="R476" s="1" t="n"/>
+      <c r="S476" s="1" t="n"/>
+      <c r="T476" s="1" t="n"/>
+      <c r="U476" s="1" t="n"/>
+      <c r="V476" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W476" s="1" t="n"/>
+      <c r="X476" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -32884,6 +38170,18 @@
       </c>
       <c r="Q477" s="1" t="n"/>
       <c r="R477" s="1" t="n"/>
+      <c r="S477" s="1" t="n"/>
+      <c r="T477" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U477" s="1" t="n"/>
+      <c r="V477" s="1" t="n"/>
+      <c r="W477" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X477" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -32954,6 +38252,16 @@
       </c>
       <c r="Q478" s="1" t="n"/>
       <c r="R478" s="1" t="n"/>
+      <c r="S478" s="1" t="n"/>
+      <c r="T478" s="1" t="n"/>
+      <c r="U478" s="1" t="n"/>
+      <c r="V478" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W478" s="1" t="n"/>
+      <c r="X478" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -33028,6 +38336,16 @@
       </c>
       <c r="Q479" s="1" t="n"/>
       <c r="R479" s="1" t="n"/>
+      <c r="S479" s="1" t="n"/>
+      <c r="T479" s="1" t="n"/>
+      <c r="U479" s="1" t="n"/>
+      <c r="V479" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W479" s="1" t="n"/>
+      <c r="X479" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -33098,6 +38416,16 @@
       </c>
       <c r="Q480" s="1" t="n"/>
       <c r="R480" s="1" t="n"/>
+      <c r="S480" s="1" t="n"/>
+      <c r="T480" s="1" t="n"/>
+      <c r="U480" s="1" t="n"/>
+      <c r="V480" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W480" s="1" t="n"/>
+      <c r="X480" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -33168,6 +38496,18 @@
       </c>
       <c r="Q481" s="1" t="n"/>
       <c r="R481" s="1" t="n"/>
+      <c r="S481" s="1" t="n"/>
+      <c r="T481" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U481" s="1" t="n"/>
+      <c r="V481" s="1" t="n"/>
+      <c r="W481" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X481" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -33204,6 +38544,18 @@
       <c r="P482" s="1" t="n"/>
       <c r="Q482" s="1" t="n"/>
       <c r="R482" s="1" t="n"/>
+      <c r="S482" s="1" t="n"/>
+      <c r="T482" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U482" s="1" t="n"/>
+      <c r="V482" s="1" t="n"/>
+      <c r="W482" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X482" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -33240,6 +38592,18 @@
       <c r="P483" s="1" t="n"/>
       <c r="Q483" s="1" t="n"/>
       <c r="R483" s="1" t="n"/>
+      <c r="S483" s="1" t="n"/>
+      <c r="T483" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U483" s="1" t="n"/>
+      <c r="V483" s="1" t="n"/>
+      <c r="W483" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X483" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -33276,6 +38640,20 @@
       <c r="P484" s="1" t="n"/>
       <c r="Q484" s="1" t="n"/>
       <c r="R484" s="1" t="n"/>
+      <c r="S484" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T484" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U484" s="1" t="n"/>
+      <c r="V484" s="1" t="n"/>
+      <c r="W484" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X484" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -33312,6 +38690,20 @@
       <c r="P485" s="1" t="n"/>
       <c r="Q485" s="1" t="n"/>
       <c r="R485" s="1" t="n"/>
+      <c r="S485" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T485" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U485" s="1" t="n"/>
+      <c r="V485" s="1" t="n"/>
+      <c r="W485" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X485" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -33382,6 +38774,18 @@
       </c>
       <c r="Q486" s="1" t="n"/>
       <c r="R486" s="1" t="n"/>
+      <c r="S486" s="1" t="n"/>
+      <c r="T486" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U486" s="1" t="n"/>
+      <c r="V486" s="1" t="n"/>
+      <c r="W486" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X486" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -33454,6 +38858,16 @@
       <c r="P487" s="1" t="n"/>
       <c r="Q487" s="1" t="n"/>
       <c r="R487" s="1" t="n"/>
+      <c r="S487" s="1" t="n"/>
+      <c r="T487" s="1" t="n"/>
+      <c r="U487" s="1" t="n"/>
+      <c r="V487" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="W487" s="1" t="n"/>
+      <c r="X487" s="1" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -33520,6 +38934,16 @@
       <c r="P488" s="1" t="n"/>
       <c r="Q488" s="1" t="n"/>
       <c r="R488" s="1" t="n"/>
+      <c r="S488" s="1" t="n"/>
+      <c r="T488" s="1" t="n"/>
+      <c r="U488" s="1" t="n"/>
+      <c r="V488" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W488" s="1" t="n"/>
+      <c r="X488" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -33586,6 +39010,16 @@
       <c r="P489" s="1" t="n"/>
       <c r="Q489" s="1" t="n"/>
       <c r="R489" s="1" t="n"/>
+      <c r="S489" s="1" t="n"/>
+      <c r="T489" s="1" t="n"/>
+      <c r="U489" s="1" t="n"/>
+      <c r="V489" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W489" s="1" t="n"/>
+      <c r="X489" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -33652,6 +39086,16 @@
       <c r="P490" s="1" t="n"/>
       <c r="Q490" s="1" t="n"/>
       <c r="R490" s="1" t="n"/>
+      <c r="S490" s="1" t="n"/>
+      <c r="T490" s="1" t="n"/>
+      <c r="U490" s="1" t="n"/>
+      <c r="V490" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W490" s="1" t="n"/>
+      <c r="X490" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -33722,6 +39166,16 @@
       <c r="P491" s="1" t="n"/>
       <c r="Q491" s="1" t="n"/>
       <c r="R491" s="1" t="n"/>
+      <c r="S491" s="1" t="n"/>
+      <c r="T491" s="1" t="n"/>
+      <c r="U491" s="1" t="n"/>
+      <c r="V491" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="W491" s="1" t="n"/>
+      <c r="X491" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -33792,6 +39246,16 @@
       <c r="P492" s="1" t="n"/>
       <c r="Q492" s="1" t="n"/>
       <c r="R492" s="1" t="n"/>
+      <c r="S492" s="1" t="n"/>
+      <c r="T492" s="1" t="n"/>
+      <c r="U492" s="1" t="n"/>
+      <c r="V492" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W492" s="1" t="n"/>
+      <c r="X492" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -33862,6 +39326,16 @@
       <c r="P493" s="1" t="n"/>
       <c r="Q493" s="1" t="n"/>
       <c r="R493" s="1" t="n"/>
+      <c r="S493" s="1" t="n"/>
+      <c r="T493" s="1" t="n"/>
+      <c r="U493" s="1" t="n"/>
+      <c r="V493" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="W493" s="1" t="n"/>
+      <c r="X493" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -33936,6 +39410,16 @@
       </c>
       <c r="Q494" s="1" t="n"/>
       <c r="R494" s="1" t="n"/>
+      <c r="S494" s="1" t="n"/>
+      <c r="T494" s="1" t="n"/>
+      <c r="U494" s="1" t="n"/>
+      <c r="V494" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W494" s="1" t="n"/>
+      <c r="X494" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -34006,6 +39490,20 @@
       <c r="R495" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S495" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T495" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U495" s="1" t="n"/>
+      <c r="V495" s="1" t="n"/>
+      <c r="W495" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X495" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -34080,6 +39578,20 @@
       <c r="R496" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S496" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T496" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U496" s="1" t="n"/>
+      <c r="V496" s="1" t="n"/>
+      <c r="W496" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="X496" s="1" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -34154,6 +39666,16 @@
       </c>
       <c r="Q497" s="1" t="n"/>
       <c r="R497" s="1" t="n"/>
+      <c r="S497" s="1" t="n"/>
+      <c r="T497" s="1" t="n"/>
+      <c r="U497" s="1" t="n"/>
+      <c r="V497" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W497" s="1" t="n"/>
+      <c r="X497" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -34224,6 +39746,16 @@
       </c>
       <c r="Q498" s="1" t="n"/>
       <c r="R498" s="1" t="n"/>
+      <c r="S498" s="1" t="n"/>
+      <c r="T498" s="1" t="n"/>
+      <c r="U498" s="1" t="n"/>
+      <c r="V498" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W498" s="1" t="n"/>
+      <c r="X498" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -34298,6 +39830,20 @@
       <c r="R499" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S499" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T499" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U499" s="1" t="n"/>
+      <c r="V499" s="1" t="n"/>
+      <c r="W499" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="X499" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -34368,6 +39914,16 @@
       </c>
       <c r="Q500" s="1" t="n"/>
       <c r="R500" s="1" t="n"/>
+      <c r="S500" s="1" t="n"/>
+      <c r="T500" s="1" t="n"/>
+      <c r="U500" s="1" t="n"/>
+      <c r="V500" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W500" s="1" t="n"/>
+      <c r="X500" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -34438,6 +39994,20 @@
       <c r="R501" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S501" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T501" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U501" s="1" t="n"/>
+      <c r="V501" s="1" t="n"/>
+      <c r="W501" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="X501" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -34512,6 +40082,16 @@
       </c>
       <c r="Q502" s="1" t="n"/>
       <c r="R502" s="1" t="n"/>
+      <c r="S502" s="1" t="n"/>
+      <c r="T502" s="1" t="n"/>
+      <c r="U502" s="1" t="n"/>
+      <c r="V502" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W502" s="1" t="n"/>
+      <c r="X502" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -34582,6 +40162,16 @@
       </c>
       <c r="Q503" s="1" t="n"/>
       <c r="R503" s="1" t="n"/>
+      <c r="S503" s="1" t="n"/>
+      <c r="T503" s="1" t="n"/>
+      <c r="U503" s="1" t="n"/>
+      <c r="V503" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="W503" s="1" t="n"/>
+      <c r="X503" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -34656,6 +40246,20 @@
       </c>
       <c r="Q504" s="1" t="n"/>
       <c r="R504" s="1" t="n"/>
+      <c r="S504" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T504" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U504" s="1" t="n"/>
+      <c r="V504" s="1" t="n"/>
+      <c r="W504" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X504" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -34730,6 +40334,20 @@
       </c>
       <c r="Q505" s="1" t="n"/>
       <c r="R505" s="1" t="n"/>
+      <c r="S505" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T505" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U505" s="1" t="n"/>
+      <c r="V505" s="1" t="n"/>
+      <c r="W505" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X505" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -34800,6 +40418,20 @@
       </c>
       <c r="Q506" s="1" t="n"/>
       <c r="R506" s="1" t="n"/>
+      <c r="S506" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T506" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U506" s="1" t="n"/>
+      <c r="V506" s="1" t="n"/>
+      <c r="W506" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X506" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -34870,6 +40502,20 @@
       </c>
       <c r="Q507" s="1" t="n"/>
       <c r="R507" s="1" t="n"/>
+      <c r="S507" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T507" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U507" s="1" t="n"/>
+      <c r="V507" s="1" t="n"/>
+      <c r="W507" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X507" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -34940,6 +40586,20 @@
       <c r="R508" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S508" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T508" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U508" s="1" t="n"/>
+      <c r="V508" s="1" t="n"/>
+      <c r="W508" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X508" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -35012,6 +40672,20 @@
       <c r="P509" s="1" t="n"/>
       <c r="Q509" s="1" t="n"/>
       <c r="R509" s="1" t="n"/>
+      <c r="S509" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T509" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U509" s="1" t="n"/>
+      <c r="V509" s="1" t="n"/>
+      <c r="W509" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X509" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -35082,6 +40756,20 @@
       <c r="R510" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S510" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T510" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U510" s="1" t="n"/>
+      <c r="V510" s="1" t="n"/>
+      <c r="W510" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X510" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -35154,6 +40842,20 @@
       <c r="P511" s="1" t="n"/>
       <c r="Q511" s="1" t="n"/>
       <c r="R511" s="1" t="n"/>
+      <c r="S511" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T511" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U511" s="1" t="n"/>
+      <c r="V511" s="1" t="n"/>
+      <c r="W511" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X511" s="1" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -35228,6 +40930,16 @@
         <v>1</v>
       </c>
       <c r="R512" s="1" t="n"/>
+      <c r="S512" s="1" t="n"/>
+      <c r="T512" s="1" t="n"/>
+      <c r="U512" s="1" t="n"/>
+      <c r="V512" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W512" s="1" t="n"/>
+      <c r="X512" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -35302,6 +41014,16 @@
         <v>1</v>
       </c>
       <c r="R513" s="1" t="n"/>
+      <c r="S513" s="1" t="n"/>
+      <c r="T513" s="1" t="n"/>
+      <c r="U513" s="1" t="n"/>
+      <c r="V513" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W513" s="1" t="n"/>
+      <c r="X513" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -35372,6 +41094,16 @@
         <v>1</v>
       </c>
       <c r="R514" s="1" t="n"/>
+      <c r="S514" s="1" t="n"/>
+      <c r="T514" s="1" t="n"/>
+      <c r="U514" s="1" t="n"/>
+      <c r="V514" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="W514" s="1" t="n"/>
+      <c r="X514" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -35442,6 +41174,16 @@
         <v>1</v>
       </c>
       <c r="R515" s="1" t="n"/>
+      <c r="S515" s="1" t="n"/>
+      <c r="T515" s="1" t="n"/>
+      <c r="U515" s="1" t="n"/>
+      <c r="V515" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W515" s="1" t="n"/>
+      <c r="X515" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
